--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$119</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,6 +204,20 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -212,14 +226,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -233,11 +247,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -248,17 +270,47 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -273,52 +325,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -327,14 +334,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,19 +362,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +458,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,151 +524,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,10 +573,8 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -587,6 +585,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -606,11 +619,37 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -629,190 +668,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1486,7 +1486,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E119"/>
+  <dimension ref="A1:E120"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -3044,8 +3044,16 @@
         <v>3908080</v>
       </c>
     </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="1">
+        <v>46281</v>
+      </c>
+      <c r="B120" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E118">
+  <autoFilter ref="A1:E119">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12450" activeTab="2"/>
+    <workbookView windowWidth="15285" windowHeight="11220" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$118</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -211,36 +211,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -255,23 +235,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -285,23 +258,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -324,8 +287,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -346,6 +339,13 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -362,19 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,7 +380,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,19 +422,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,7 +458,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,109 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,11 +580,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -636,6 +642,15 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -648,23 +663,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,154 +674,150 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -846,12 +842,12 @@
     <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
     <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
     <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="20% - アクセント 4" xfId="7" builtinId="42"/>
+    <cellStyle name="メモ" xfId="8" builtinId="10"/>
+    <cellStyle name="パーセント" xfId="9" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="10" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="11" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="12" builtinId="9"/>
     <cellStyle name="良い" xfId="13" builtinId="26"/>
     <cellStyle name="警告文" xfId="14" builtinId="11"/>
     <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
@@ -1190,152 +1186,152 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.25" spans="1:1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="8"/>
+      <c r="A2" s="6"/>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="6" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="8"/>
+      <c r="A5" s="6"/>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="8"/>
+      <c r="A12" s="6"/>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="8"/>
+      <c r="A16" s="6"/>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="6" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="6" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="6" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="6" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="8"/>
+      <c r="A27" s="6"/>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="6" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="6" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1355,127 +1351,127 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="3" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="3" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="5"/>
+      <c r="A16" s="3"/>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="5"/>
+      <c r="A17" s="3"/>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="5"/>
+      <c r="A18" s="3"/>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="5"/>
+      <c r="A19" s="3"/>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="5"/>
+      <c r="A20" s="3"/>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="5"/>
+      <c r="A21" s="3"/>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="5"/>
+      <c r="A22" s="3"/>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="5"/>
+      <c r="A23" s="3"/>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="5"/>
+      <c r="A24" s="3"/>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="5"/>
+      <c r="A25" s="3"/>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="5"/>
+      <c r="A26" s="3"/>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="5"/>
+      <c r="A27" s="3"/>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="5"/>
+      <c r="A28" s="3"/>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="5"/>
+      <c r="A29" s="3"/>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="5"/>
+      <c r="A30" s="3"/>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="5"/>
+      <c r="A31" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1486,1578 +1482,6337 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E120"/>
+  <dimension ref="A1:E801"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="14" style="1" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="4">
+      <c r="A2" s="2">
         <v>45306</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" s="6">
+      <c r="B2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="4">
         <v>628500</v>
       </c>
-      <c r="D2" s="6"/>
-      <c r="E2" s="5"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="3"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="4">
+      <c r="A3" s="2">
         <v>45317</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3" s="6">
+      <c r="B3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="4">
         <v>2214576</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="5"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="3"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="4">
+      <c r="A4" s="2">
         <v>45327</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="6">
+      <c r="B4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="4">
         <v>1020000</v>
       </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="5"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="4">
+      <c r="A5" s="2">
         <v>45353</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="6">
+      <c r="B5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="4">
         <v>6604416</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="5"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="3"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="4">
+      <c r="A6" s="2">
         <v>45383</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="6">
+      <c r="B6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="4">
         <v>1839840</v>
       </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="5"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="3"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="4">
+      <c r="A7" s="2">
         <v>45401</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="6">
+      <c r="B7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="4">
         <v>6525792</v>
       </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="5"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="3"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="4">
+      <c r="A8" s="2">
         <v>45405</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="6">
+      <c r="B8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="4">
         <v>4402944</v>
       </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="5"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="3"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="4">
+      <c r="A9" s="2">
         <v>45428</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="6">
+      <c r="B9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="4">
         <v>1839840</v>
       </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="5"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="3"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="4">
+      <c r="A10" s="2">
         <v>45429</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="6">
+      <c r="B10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="4">
         <v>6525792</v>
       </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="5"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="3"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="4">
+      <c r="A11" s="2">
         <v>45432</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="6">
+      <c r="B11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="4">
         <v>2159136</v>
       </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="5"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="3"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="4">
+      <c r="A12" s="2">
         <v>45433</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="6">
+      <c r="B12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="4">
         <v>6525792</v>
       </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="5"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="3"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="4">
+      <c r="A13" s="2">
         <v>45478</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="6">
+      <c r="B13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="4">
         <v>2846952</v>
       </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="5"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="3"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="4">
+      <c r="A14" s="2">
         <v>45482</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="6">
+      <c r="B14" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="4">
         <v>2201472</v>
       </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="5"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="4">
+      <c r="A15" s="2">
         <v>45492</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="6">
+      <c r="B15" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="4">
         <v>8642592</v>
       </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="5"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="3"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="4">
+      <c r="A16" s="2">
         <v>45506</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" s="6">
+      <c r="B16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="4">
         <v>6525792</v>
       </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="5"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="3"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="4">
+      <c r="A17" s="2">
         <v>45523</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C17" s="6">
+      <c r="B17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="4">
         <v>8642592</v>
       </c>
-      <c r="D17" s="6"/>
-      <c r="E17" s="5"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="3"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="4">
+      <c r="A18" s="2">
         <v>45524</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="6">
+      <c r="B18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="4">
         <v>2116800</v>
       </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="5"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="3"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="4">
+      <c r="A19" s="2">
         <v>45573</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="6">
+      <c r="B19" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="4">
         <v>6525792</v>
       </c>
-      <c r="D19" s="6"/>
-      <c r="E19" s="5"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="3"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="4">
+      <c r="A20" s="2">
         <v>45576</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C20" s="6">
+      <c r="B20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="4">
         <v>21891</v>
       </c>
-      <c r="D20" s="6"/>
-      <c r="E20" s="5"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="3"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="4">
+      <c r="A21" s="2">
         <v>45603</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" s="6">
+      <c r="B21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="4">
         <v>5287500</v>
       </c>
-      <c r="D21" s="6"/>
-      <c r="E21" s="5"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="3"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="4">
+      <c r="A22" s="2">
         <v>45604</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" s="6">
+      <c r="B22" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="4">
         <v>3725520</v>
       </c>
-      <c r="D22" s="6"/>
-      <c r="E22" s="5"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="3"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="4">
+      <c r="A23" s="2">
         <v>45614</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="6">
+      <c r="B23" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="4">
         <v>6525792</v>
       </c>
-      <c r="D23" s="6"/>
-      <c r="E23" s="5"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="3"/>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="4">
+      <c r="A24" s="2">
         <v>45616</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C24" s="6">
+      <c r="B24" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" s="4">
         <v>125280</v>
       </c>
-      <c r="D24" s="6"/>
-      <c r="E24" s="5"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="3"/>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="4">
+      <c r="A25" s="2">
         <v>45622</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C25" s="6">
+      <c r="B25" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" s="4">
         <v>711840</v>
       </c>
-      <c r="D25" s="6"/>
-      <c r="E25" s="5"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="3"/>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="4">
+      <c r="A26" s="2">
         <v>45623</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C26" s="6">
+      <c r="B26" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="4">
         <v>677160</v>
       </c>
-      <c r="D26" s="6"/>
-      <c r="E26" s="5"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="3"/>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="4">
+      <c r="A27" s="2">
         <v>45629</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C27" s="6">
+      <c r="B27" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" s="4">
         <v>7281612</v>
       </c>
-      <c r="D27" s="6"/>
-      <c r="E27" s="5"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="3"/>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="4">
+      <c r="A28" s="2">
         <v>45638</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C28" s="6">
+      <c r="B28" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="4">
         <v>1347360</v>
       </c>
-      <c r="D28" s="6"/>
-      <c r="E28" s="5"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="3"/>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="4">
+      <c r="A29" s="2">
         <v>45639</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C29" s="6">
+      <c r="B29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="4">
         <v>791200</v>
       </c>
-      <c r="D29" s="6"/>
-      <c r="E29" s="5"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="3"/>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="4">
+      <c r="A30" s="2">
         <v>45646</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C30" s="6">
+      <c r="B30" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" s="4">
         <v>2201472</v>
       </c>
-      <c r="D30" s="6"/>
-      <c r="E30" s="5"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="3"/>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="4">
+      <c r="A31" s="2">
         <v>45649</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C31" s="6">
+      <c r="B31" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="4">
         <v>6746757</v>
       </c>
-      <c r="D31" s="6"/>
-      <c r="E31" s="5"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="3"/>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="4">
+      <c r="A32" s="2">
         <v>45653</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C32" s="6">
+      <c r="B32" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="4">
         <v>220965</v>
       </c>
-      <c r="D32" s="6"/>
-      <c r="E32" s="5"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="3"/>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="4">
+      <c r="A33" s="2">
         <v>45663</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C33" s="6">
+      <c r="B33" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" s="4">
         <v>782000</v>
       </c>
-      <c r="D33" s="6"/>
-      <c r="E33" s="5"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="3"/>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="4">
+      <c r="A34" s="2">
         <v>45681</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C34" s="6">
+      <c r="B34" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" s="4">
         <v>6525792</v>
       </c>
-      <c r="D34" s="6"/>
-      <c r="E34" s="5"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="3"/>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="4">
+      <c r="A35" s="2">
         <v>45684</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C35" s="6">
+      <c r="B35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C35" s="4">
         <v>6525792</v>
       </c>
-      <c r="D35" s="6"/>
-      <c r="E35" s="5"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="3"/>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="4">
+      <c r="A36" s="2">
         <v>45685</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C36" s="6">
+      <c r="B36" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" s="4">
         <v>2089340</v>
       </c>
-      <c r="D36" s="6"/>
-      <c r="E36" s="5"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="3"/>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="4">
+      <c r="A37" s="2">
         <v>45687</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C37" s="6">
+      <c r="B37" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" s="4">
         <v>6525792</v>
       </c>
-      <c r="D37" s="6"/>
-      <c r="E37" s="5"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="3"/>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="4">
+      <c r="A38" s="2">
         <v>45698</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C38" s="6">
+      <c r="B38" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C38" s="4">
         <v>6525792</v>
       </c>
-      <c r="D38" s="6"/>
-      <c r="E38" s="5"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="3"/>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="4">
+      <c r="A39" s="2">
         <v>45705</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C39" s="6">
+      <c r="B39" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C39" s="4">
         <v>1374780</v>
       </c>
-      <c r="D39" s="6"/>
-      <c r="E39" s="5"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="3"/>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="4">
+      <c r="A40" s="2">
         <v>45713</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C40" s="6">
+      <c r="B40" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C40" s="4">
         <v>6525792</v>
       </c>
-      <c r="D40" s="6"/>
-      <c r="E40" s="5"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="3"/>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="4">
+      <c r="A41" s="2">
         <v>45716</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C41" s="6">
+      <c r="B41" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41" s="4">
         <v>6525792</v>
       </c>
-      <c r="D41" s="6"/>
-      <c r="E41" s="5"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="3"/>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="4">
+      <c r="A42" s="2">
         <v>45722</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C42" s="6">
+      <c r="B42" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C42" s="4">
         <v>6525792</v>
       </c>
-      <c r="D42" s="6"/>
-      <c r="E42" s="5"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="3"/>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="4">
+      <c r="A43" s="2">
         <v>45723</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C43" s="6">
+      <c r="B43" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C43" s="4">
         <v>6525792</v>
       </c>
-      <c r="D43" s="6"/>
-      <c r="E43" s="5"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="3"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="4">
+      <c r="A44" s="2">
         <v>45733</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C44" s="6">
+      <c r="B44" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C44" s="4">
         <v>6729888</v>
       </c>
-      <c r="D44" s="6"/>
-      <c r="E44" s="5"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="3"/>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="4">
+      <c r="A45" s="2">
         <v>45734</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C45" s="6">
+      <c r="B45" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C45" s="4">
         <v>6525792</v>
       </c>
-      <c r="D45" s="6"/>
-      <c r="E45" s="5"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="3"/>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="4">
+      <c r="A46" s="2">
         <v>45735</v>
       </c>
-      <c r="B46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C46" s="6">
+      <c r="B46" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C46" s="4">
         <v>5510592</v>
       </c>
-      <c r="D46" s="6"/>
-      <c r="E46" s="5"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="3"/>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="4">
+      <c r="A47" s="2">
         <v>45737</v>
       </c>
-      <c r="B47" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C47" s="6">
+      <c r="B47" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C47" s="4">
         <v>5510592</v>
       </c>
-      <c r="D47" s="6"/>
-      <c r="E47" s="5"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="3"/>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="4">
+      <c r="A48" s="2">
         <v>45740</v>
       </c>
-      <c r="B48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C48" s="6">
+      <c r="B48" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C48" s="4">
         <v>6525792</v>
       </c>
-      <c r="D48" s="6"/>
-      <c r="E48" s="5"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="3"/>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="4">
+      <c r="A49" s="2">
         <v>45743</v>
       </c>
-      <c r="B49" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C49" s="6">
+      <c r="B49" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C49" s="4">
         <v>705600</v>
       </c>
-      <c r="D49" s="6"/>
-      <c r="E49" s="5"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="3"/>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="4">
+      <c r="A50" s="2">
         <v>45756</v>
       </c>
-      <c r="B50" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C50" s="6">
+      <c r="B50" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C50" s="4">
         <v>369600</v>
       </c>
-      <c r="D50" s="6"/>
-      <c r="E50" s="5"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="3"/>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="4">
+      <c r="A51" s="2">
         <v>45818</v>
       </c>
-      <c r="B51" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C51" s="6">
+      <c r="B51" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C51" s="4">
         <v>539068</v>
       </c>
-      <c r="D51" s="6"/>
-      <c r="E51" s="5"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="3"/>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="4">
+      <c r="A52" s="2">
         <v>45819</v>
       </c>
-      <c r="B52" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C52" s="6">
+      <c r="B52" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="4">
         <v>5420540</v>
       </c>
-      <c r="D52" s="6"/>
-      <c r="E52" s="5"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="3"/>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="4">
+      <c r="A53" s="2">
         <v>45826</v>
       </c>
-      <c r="B53" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C53" s="6">
+      <c r="B53" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C53" s="4">
         <v>1870608</v>
       </c>
-      <c r="D53" s="6"/>
-      <c r="E53" s="5"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="3"/>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="4">
+      <c r="A54" s="2">
         <v>45835</v>
       </c>
-      <c r="B54" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C54" s="6">
+      <c r="B54" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C54" s="4">
         <v>1806150</v>
       </c>
-      <c r="D54" s="6"/>
-      <c r="E54" s="5"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="3"/>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="4">
+      <c r="A55" s="2">
         <v>45842</v>
       </c>
-      <c r="B55" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C55" s="6">
+      <c r="B55" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C55" s="4">
         <v>814800</v>
       </c>
-      <c r="D55" s="6"/>
-      <c r="E55" s="5"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="3"/>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="4">
+      <c r="A56" s="2">
         <v>45857</v>
       </c>
-      <c r="B56" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C56" s="6">
+      <c r="B56" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C56" s="4">
         <v>220008</v>
       </c>
-      <c r="D56" s="6"/>
-      <c r="E56" s="5"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="3"/>
     </row>
     <row r="57" spans="1:5">
-      <c r="A57" s="4">
+      <c r="A57" s="2">
         <v>45867</v>
       </c>
-      <c r="B57" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C57" s="6">
+      <c r="B57" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C57" s="4">
         <v>350208</v>
       </c>
-      <c r="D57" s="6"/>
-      <c r="E57" s="5"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="3"/>
     </row>
     <row r="58" spans="1:5">
-      <c r="A58" s="4">
+      <c r="A58" s="2">
         <v>45879</v>
       </c>
-      <c r="B58" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C58" s="6">
+      <c r="B58" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C58" s="4">
         <v>1338240</v>
       </c>
-      <c r="D58" s="6"/>
-      <c r="E58" s="5"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="3"/>
     </row>
     <row r="59" spans="1:5">
-      <c r="A59" s="4">
+      <c r="A59" s="2">
         <v>45889</v>
       </c>
-      <c r="B59" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C59" s="6">
+      <c r="B59" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C59" s="4">
         <v>2386080</v>
       </c>
-      <c r="D59" s="6"/>
-      <c r="E59" s="5"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="3"/>
     </row>
     <row r="60" spans="1:5">
-      <c r="A60" s="4">
+      <c r="A60" s="2">
         <v>45895</v>
       </c>
-      <c r="B60" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C60" s="6">
+      <c r="B60" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C60" s="4">
         <v>350208</v>
       </c>
-      <c r="D60" s="6"/>
-      <c r="E60" s="5"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="3"/>
     </row>
     <row r="61" spans="1:5">
-      <c r="A61" s="4">
+      <c r="A61" s="2">
         <v>45923</v>
       </c>
-      <c r="B61" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C61" s="6">
+      <c r="B61" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C61" s="4">
         <v>700416</v>
       </c>
-      <c r="D61" s="6"/>
-      <c r="E61" s="5"/>
+      <c r="D61" s="4"/>
+      <c r="E61" s="3"/>
     </row>
     <row r="62" spans="1:5">
-      <c r="A62" s="4">
+      <c r="A62" s="2">
         <v>45937</v>
       </c>
-      <c r="B62" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C62" s="6">
+      <c r="B62" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C62" s="4">
         <v>1811350</v>
       </c>
-      <c r="D62" s="6"/>
-      <c r="E62" s="5"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="3"/>
     </row>
     <row r="63" spans="1:5">
-      <c r="A63" s="4">
+      <c r="A63" s="2">
         <v>45940</v>
       </c>
-      <c r="B63" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C63" s="6">
+      <c r="B63" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C63" s="4">
         <v>700416</v>
       </c>
-      <c r="D63" s="6"/>
-      <c r="E63" s="5"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="3"/>
     </row>
     <row r="64" spans="1:5">
-      <c r="A64" s="4">
+      <c r="A64" s="2">
         <v>45961</v>
       </c>
-      <c r="B64" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C64" s="6">
+      <c r="B64" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C64" s="4">
         <v>2714400</v>
       </c>
-      <c r="D64" s="6"/>
-      <c r="E64" s="5"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="3"/>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="4">
+      <c r="A65" s="2">
         <v>45966</v>
       </c>
-      <c r="B65" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C65" s="6">
+      <c r="B65" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C65" s="4">
         <v>3762000</v>
       </c>
-      <c r="D65" s="6"/>
-      <c r="E65" s="5"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="3"/>
     </row>
     <row r="66" spans="1:5">
-      <c r="A66" s="4">
+      <c r="A66" s="2">
         <v>45971</v>
       </c>
-      <c r="B66" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C66" s="6">
+      <c r="B66" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C66" s="4">
         <v>1504800</v>
       </c>
-      <c r="D66" s="6"/>
-      <c r="E66" s="5"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="3"/>
     </row>
     <row r="67" spans="1:5">
-      <c r="A67" s="4">
+      <c r="A67" s="2">
         <v>45994</v>
       </c>
-      <c r="B67" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C67" s="6">
+      <c r="B67" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C67" s="4">
         <v>5552976</v>
       </c>
-      <c r="D67" s="6"/>
-      <c r="E67" s="5"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="3"/>
     </row>
     <row r="68" spans="1:5">
-      <c r="A68" s="4">
+      <c r="A68" s="2">
         <v>45999</v>
       </c>
-      <c r="B68" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C68" s="6">
+      <c r="B68" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C68" s="4">
         <v>572400</v>
       </c>
-      <c r="D68" s="6"/>
-      <c r="E68" s="5"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="3"/>
     </row>
     <row r="69" spans="1:5">
-      <c r="A69" s="4">
+      <c r="A69" s="2">
         <v>46014</v>
       </c>
-      <c r="B69" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C69" s="6">
+      <c r="B69" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C69" s="4">
         <v>610750</v>
       </c>
-      <c r="D69" s="6"/>
-      <c r="E69" s="5"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="3"/>
     </row>
     <row r="70" spans="1:5">
-      <c r="A70" s="4">
+      <c r="A70" s="2">
         <v>46056</v>
       </c>
-      <c r="B70" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C70" s="6">
+      <c r="B70" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C70" s="4">
         <v>260064</v>
       </c>
-      <c r="D70" s="6"/>
-      <c r="E70" s="5"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="3"/>
     </row>
     <row r="71" spans="1:5">
-      <c r="A71" s="4">
+      <c r="A71" s="2">
         <v>46069</v>
       </c>
-      <c r="B71" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C71" s="6">
+      <c r="B71" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C71" s="4">
         <v>636000</v>
       </c>
-      <c r="D71" s="6"/>
-      <c r="E71" s="5"/>
+      <c r="D71" s="4"/>
+      <c r="E71" s="3"/>
     </row>
     <row r="72" spans="1:5">
-      <c r="A72" s="4">
+      <c r="A72" s="2">
         <v>46073</v>
       </c>
-      <c r="B72" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C72" s="6">
+      <c r="B72" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C72" s="4">
         <v>636000</v>
       </c>
-      <c r="D72" s="6"/>
-      <c r="E72" s="5"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="3"/>
     </row>
     <row r="73" spans="1:5">
-      <c r="A73" s="4">
+      <c r="A73" s="2">
         <v>46074</v>
       </c>
-      <c r="B73" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C73" s="6">
+      <c r="B73" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C73" s="4">
         <v>636000</v>
       </c>
-      <c r="D73" s="6"/>
-      <c r="E73" s="5"/>
+      <c r="D73" s="4"/>
+      <c r="E73" s="3"/>
     </row>
     <row r="74" spans="1:5">
-      <c r="A74" s="4">
+      <c r="A74" s="2">
         <v>46080</v>
       </c>
-      <c r="B74" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C74" s="6">
+      <c r="B74" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C74" s="4">
         <v>636000</v>
       </c>
-      <c r="D74" s="6"/>
-      <c r="E74" s="5"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="3"/>
     </row>
     <row r="75" spans="1:5">
-      <c r="A75" s="4">
+      <c r="A75" s="2">
         <v>46081</v>
       </c>
-      <c r="B75" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C75" s="6">
+      <c r="B75" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C75" s="4">
         <v>636000</v>
       </c>
-      <c r="D75" s="6"/>
-      <c r="E75" s="5"/>
+      <c r="D75" s="4"/>
+      <c r="E75" s="3"/>
     </row>
     <row r="76" spans="1:5">
-      <c r="A76" s="4">
+      <c r="A76" s="2">
         <v>46084</v>
       </c>
-      <c r="B76" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C76" s="6">
+      <c r="B76" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C76" s="4">
         <v>257084</v>
       </c>
-      <c r="D76" s="6"/>
-      <c r="E76" s="5"/>
+      <c r="D76" s="4"/>
+      <c r="E76" s="3"/>
     </row>
     <row r="77" spans="1:5">
-      <c r="A77" s="4">
+      <c r="A77" s="2">
         <v>46085</v>
       </c>
-      <c r="B77" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C77" s="6">
+      <c r="B77" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C77" s="4">
         <v>636000</v>
       </c>
-      <c r="D77" s="6"/>
-      <c r="E77" s="5"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="3"/>
     </row>
     <row r="78" spans="1:5">
-      <c r="A78" s="4">
+      <c r="A78" s="2">
         <v>46087</v>
       </c>
-      <c r="B78" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C78" s="6">
+      <c r="B78" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C78" s="4">
         <v>636000</v>
       </c>
-      <c r="D78" s="6"/>
-      <c r="E78" s="5"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="3"/>
     </row>
     <row r="79" spans="1:5">
-      <c r="A79" s="4">
+      <c r="A79" s="2">
         <v>46088</v>
       </c>
-      <c r="B79" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C79" s="6">
+      <c r="B79" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C79" s="4">
         <v>636000</v>
       </c>
-      <c r="D79" s="6"/>
-      <c r="E79" s="5"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="3"/>
     </row>
     <row r="80" spans="1:5">
-      <c r="A80" s="4">
+      <c r="A80" s="2">
         <v>46126</v>
       </c>
-      <c r="B80" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C80" s="6">
+      <c r="B80" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C80" s="4">
         <v>15012598</v>
       </c>
-      <c r="D80" s="6"/>
-      <c r="E80" s="5"/>
+      <c r="D80" s="4"/>
+      <c r="E80" s="3"/>
     </row>
     <row r="81" spans="1:5">
-      <c r="A81" s="4">
+      <c r="A81" s="2">
         <v>46134</v>
       </c>
-      <c r="B81" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C81" s="6">
+      <c r="B81" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C81" s="4">
         <v>7506299</v>
       </c>
-      <c r="D81" s="6"/>
-      <c r="E81" s="5"/>
+      <c r="D81" s="4"/>
+      <c r="E81" s="3"/>
     </row>
     <row r="82" spans="1:5">
-      <c r="A82" s="4">
+      <c r="A82" s="2">
         <v>46140</v>
       </c>
-      <c r="B82" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C82" s="6">
+      <c r="B82" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C82" s="4">
         <v>7506299</v>
       </c>
-      <c r="D82" s="6"/>
-      <c r="E82" s="5"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="3"/>
     </row>
     <row r="83" spans="1:5">
-      <c r="A83" s="4">
+      <c r="A83" s="2">
         <v>46157</v>
       </c>
-      <c r="B83" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C83" s="6">
+      <c r="B83" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C83" s="4">
         <v>2103200</v>
       </c>
-      <c r="D83" s="6"/>
-      <c r="E83" s="5"/>
+      <c r="D83" s="4"/>
+      <c r="E83" s="3"/>
     </row>
     <row r="84" spans="1:5">
-      <c r="A84" s="4">
+      <c r="A84" s="2">
         <v>46175</v>
       </c>
-      <c r="B84" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C84" s="6">
+      <c r="B84" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C84" s="4">
         <v>974640</v>
       </c>
-      <c r="D84" s="6"/>
-      <c r="E84" s="5"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="3"/>
     </row>
     <row r="85" spans="1:5">
-      <c r="A85" s="4">
+      <c r="A85" s="2">
         <v>46179</v>
       </c>
-      <c r="B85" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C85" s="6">
+      <c r="B85" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C85" s="4">
         <v>497904</v>
       </c>
-      <c r="D85" s="6"/>
-      <c r="E85" s="5"/>
+      <c r="D85" s="4"/>
+      <c r="E85" s="3"/>
     </row>
     <row r="86" spans="1:5">
-      <c r="A86" s="4">
+      <c r="A86" s="2">
         <v>46181</v>
       </c>
-      <c r="B86" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C86" s="6">
+      <c r="B86" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C86" s="4">
         <v>519552</v>
       </c>
-      <c r="D86" s="6"/>
-      <c r="E86" s="5"/>
+      <c r="D86" s="4"/>
+      <c r="E86" s="3"/>
     </row>
     <row r="87" spans="1:5">
-      <c r="A87" s="4">
+      <c r="A87" s="2">
         <v>46184</v>
       </c>
-      <c r="B87" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C87" s="6">
+      <c r="B87" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C87" s="4">
         <v>519552</v>
       </c>
-      <c r="D87" s="6"/>
-      <c r="E87" s="5"/>
+      <c r="D87" s="4"/>
+      <c r="E87" s="3"/>
     </row>
     <row r="88" spans="1:5">
-      <c r="A88" s="4">
+      <c r="A88" s="2">
         <v>46185</v>
       </c>
-      <c r="B88" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C88" s="6">
+      <c r="B88" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C88" s="4">
         <v>1039104</v>
       </c>
-      <c r="D88" s="6"/>
-      <c r="E88" s="5"/>
+      <c r="D88" s="4"/>
+      <c r="E88" s="3"/>
     </row>
     <row r="89" spans="1:5">
-      <c r="A89" s="4">
+      <c r="A89" s="2">
         <v>46189</v>
       </c>
-      <c r="B89" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C89" s="6">
+      <c r="B89" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C89" s="4">
         <v>1039104</v>
       </c>
-      <c r="D89" s="6"/>
-      <c r="E89" s="5"/>
+      <c r="D89" s="4"/>
+      <c r="E89" s="3"/>
     </row>
     <row r="90" spans="1:5">
-      <c r="A90" s="4">
+      <c r="A90" s="2">
         <v>46196</v>
       </c>
-      <c r="B90" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C90" s="6">
+      <c r="B90" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C90" s="4">
         <v>1039104</v>
       </c>
-      <c r="D90" s="6"/>
-      <c r="E90" s="5"/>
+      <c r="D90" s="4"/>
+      <c r="E90" s="3"/>
     </row>
     <row r="91" spans="1:5">
-      <c r="A91" s="4">
+      <c r="A91" s="2">
         <v>46197</v>
       </c>
-      <c r="B91" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C91" s="6">
+      <c r="B91" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C91" s="4">
         <v>1039104</v>
       </c>
-      <c r="D91" s="6"/>
-      <c r="E91" s="5"/>
+      <c r="D91" s="4"/>
+      <c r="E91" s="3"/>
     </row>
     <row r="92" spans="1:5">
-      <c r="A92" s="4">
+      <c r="A92" s="2">
         <v>46205</v>
       </c>
-      <c r="B92" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C92" s="6">
+      <c r="B92" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C92" s="4">
         <v>488510</v>
       </c>
-      <c r="D92" s="6"/>
-      <c r="E92" s="5"/>
+      <c r="D92" s="4"/>
+      <c r="E92" s="3"/>
     </row>
     <row r="93" spans="1:5">
-      <c r="A93" s="4">
+      <c r="A93" s="2">
         <v>46212</v>
       </c>
-      <c r="B93" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C93" s="6">
+      <c r="B93" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C93" s="4">
         <v>488510</v>
       </c>
-      <c r="D93" s="6"/>
-      <c r="E93" s="5"/>
+      <c r="D93" s="4"/>
+      <c r="E93" s="3"/>
     </row>
     <row r="94" spans="1:5">
-      <c r="A94" s="4">
+      <c r="A94" s="2">
         <v>46214</v>
       </c>
-      <c r="B94" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C94" s="6">
+      <c r="B94" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C94" s="4">
         <v>802200</v>
       </c>
-      <c r="D94" s="6"/>
-      <c r="E94" s="5"/>
+      <c r="D94" s="4"/>
+      <c r="E94" s="3"/>
     </row>
     <row r="95" spans="1:5">
-      <c r="A95" s="4">
+      <c r="A95" s="2">
         <v>46216</v>
       </c>
-      <c r="B95" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C95" s="6">
+      <c r="B95" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C95" s="4">
         <v>7508592</v>
       </c>
-      <c r="D95" s="6"/>
-      <c r="E95" s="5"/>
+      <c r="D95" s="4"/>
+      <c r="E95" s="3"/>
     </row>
     <row r="96" spans="1:5">
-      <c r="A96" s="4">
+      <c r="A96" s="2">
         <v>46219</v>
       </c>
-      <c r="B96" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C96" s="6">
+      <c r="B96" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C96" s="4">
         <v>15012598</v>
       </c>
-      <c r="D96" s="6"/>
-      <c r="E96" s="5"/>
+      <c r="D96" s="4"/>
+      <c r="E96" s="3"/>
     </row>
     <row r="97" spans="1:5">
-      <c r="A97" s="4">
+      <c r="A97" s="2">
         <v>46227</v>
       </c>
-      <c r="B97" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C97" s="6">
+      <c r="B97" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C97" s="4">
         <v>2291300</v>
       </c>
-      <c r="D97" s="6"/>
-      <c r="E97" s="5"/>
+      <c r="D97" s="4"/>
+      <c r="E97" s="3"/>
     </row>
     <row r="98" spans="1:5">
-      <c r="A98" s="4">
+      <c r="A98" s="2">
         <v>46239</v>
       </c>
-      <c r="B98" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C98" s="6">
+      <c r="B98" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C98" s="4">
         <v>802200</v>
       </c>
-      <c r="D98" s="6"/>
-      <c r="E98" s="5"/>
+      <c r="D98" s="4"/>
+      <c r="E98" s="3"/>
     </row>
     <row r="99" spans="1:5">
-      <c r="A99" s="4">
+      <c r="A99" s="2">
         <v>46241</v>
       </c>
-      <c r="B99" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C99" s="6">
+      <c r="B99" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C99" s="4">
         <v>7508592</v>
       </c>
-      <c r="D99" s="6"/>
-      <c r="E99" s="5"/>
+      <c r="D99" s="4"/>
+      <c r="E99" s="3"/>
     </row>
     <row r="100" spans="1:5">
-      <c r="A100" s="4">
+      <c r="A100" s="2">
         <v>46244</v>
       </c>
-      <c r="B100" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C100" s="6">
+      <c r="B100" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C100" s="4">
         <v>2291300</v>
       </c>
-      <c r="D100" s="6"/>
-      <c r="E100" s="5"/>
+      <c r="D100" s="4"/>
+      <c r="E100" s="3"/>
     </row>
     <row r="101" spans="1:5">
-      <c r="A101" s="4">
+      <c r="A101" s="2">
         <v>46246</v>
       </c>
-      <c r="B101" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C101" s="6">
+      <c r="B101" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C101" s="4">
         <v>802200</v>
       </c>
-      <c r="D101" s="6"/>
-      <c r="E101" s="5"/>
+      <c r="D101" s="4"/>
+      <c r="E101" s="3"/>
     </row>
     <row r="102" spans="1:5">
-      <c r="A102" s="4">
+      <c r="A102" s="2">
         <v>46248</v>
       </c>
-      <c r="B102" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C102" s="6">
+      <c r="B102" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C102" s="4">
         <v>15012598</v>
       </c>
-      <c r="D102" s="6"/>
-      <c r="E102" s="5"/>
+      <c r="D102" s="4"/>
+      <c r="E102" s="3"/>
     </row>
     <row r="103" spans="1:5">
-      <c r="A103" s="4">
+      <c r="A103" s="2">
         <v>46249</v>
       </c>
-      <c r="B103" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C103" s="6">
+      <c r="B103" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C103" s="4">
         <v>802200</v>
       </c>
-      <c r="D103" s="6"/>
-      <c r="E103" s="5"/>
+      <c r="D103" s="4"/>
+      <c r="E103" s="3"/>
     </row>
     <row r="104" spans="1:5">
-      <c r="A104" s="4">
+      <c r="A104" s="2">
         <v>46252</v>
       </c>
-      <c r="B104" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C104" s="6">
+      <c r="B104" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C104" s="4">
         <v>7508592</v>
       </c>
-      <c r="D104" s="6"/>
-      <c r="E104" s="5"/>
+      <c r="D104" s="4"/>
+      <c r="E104" s="3"/>
     </row>
     <row r="105" spans="1:5">
-      <c r="A105" s="4">
+      <c r="A105" s="2">
         <v>46256</v>
       </c>
-      <c r="B105" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C105" s="6">
+      <c r="B105" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C105" s="4">
         <v>2311200</v>
       </c>
-      <c r="D105" s="6"/>
-      <c r="E105" s="5"/>
+      <c r="D105" s="4"/>
+      <c r="E105" s="3"/>
     </row>
     <row r="106" spans="1:5">
-      <c r="A106" s="4">
+      <c r="A106" s="2">
         <v>46258</v>
       </c>
-      <c r="B106" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C106" s="6">
+      <c r="B106" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C106" s="4">
         <v>5678840</v>
       </c>
-      <c r="D106" s="6"/>
-      <c r="E106" s="5"/>
+      <c r="D106" s="4"/>
+      <c r="E106" s="3"/>
     </row>
     <row r="107" spans="1:5">
-      <c r="A107" s="4">
+      <c r="A107" s="2">
         <v>46259</v>
       </c>
-      <c r="B107" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C107" s="6">
+      <c r="B107" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C107" s="4">
         <v>9864192</v>
       </c>
-      <c r="D107" s="6"/>
-      <c r="E107" s="5"/>
+      <c r="D107" s="4"/>
+      <c r="E107" s="3"/>
     </row>
     <row r="108" spans="1:5">
-      <c r="A108" s="4">
+      <c r="A108" s="2">
         <v>46260</v>
       </c>
-      <c r="B108" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C108" s="6">
+      <c r="B108" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C108" s="4">
         <v>2482920</v>
       </c>
-      <c r="D108" s="6"/>
-      <c r="E108" s="5"/>
+      <c r="D108" s="4"/>
+      <c r="E108" s="3"/>
     </row>
     <row r="109" spans="1:5">
-      <c r="A109" s="4">
+      <c r="A109" s="2">
         <v>46262</v>
       </c>
-      <c r="B109" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C109" s="6">
+      <c r="B109" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C109" s="4">
         <v>15518432</v>
       </c>
-      <c r="D109" s="6"/>
-      <c r="E109" s="5"/>
+      <c r="D109" s="4"/>
+      <c r="E109" s="3"/>
     </row>
     <row r="110" spans="1:5">
-      <c r="A110" s="4">
+      <c r="A110" s="2">
         <v>46263</v>
       </c>
-      <c r="B110" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C110" s="6">
+      <c r="B110" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C110" s="4">
         <v>405300</v>
       </c>
-      <c r="D110" s="6"/>
-      <c r="E110" s="5"/>
+      <c r="D110" s="4"/>
+      <c r="E110" s="3"/>
     </row>
     <row r="111" spans="1:5">
-      <c r="A111" s="4">
+      <c r="A111" s="2">
         <v>46265</v>
       </c>
-      <c r="B111" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C111" s="6">
+      <c r="B111" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C111" s="4">
         <v>1604400</v>
       </c>
-      <c r="D111" s="6"/>
-      <c r="E111" s="5"/>
+      <c r="D111" s="4"/>
+      <c r="E111" s="3"/>
     </row>
     <row r="112" spans="1:5">
-      <c r="A112" s="4">
+      <c r="A112" s="2">
         <v>46266</v>
       </c>
-      <c r="B112" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C112" s="6">
+      <c r="B112" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C112" s="4">
         <v>7508592</v>
       </c>
-      <c r="D112" s="6"/>
-      <c r="E112" s="5"/>
+      <c r="D112" s="4"/>
+      <c r="E112" s="3"/>
     </row>
     <row r="113" spans="1:5">
-      <c r="A113" s="4">
+      <c r="A113" s="2">
         <v>46267</v>
       </c>
-      <c r="B113" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C113" s="6">
+      <c r="B113" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C113" s="4">
         <v>1954040</v>
       </c>
-      <c r="D113" s="6"/>
-      <c r="E113" s="5"/>
+      <c r="D113" s="4"/>
+      <c r="E113" s="3"/>
     </row>
     <row r="114" spans="1:5">
-      <c r="A114" s="4">
+      <c r="A114" s="2">
         <v>46269</v>
       </c>
-      <c r="B114" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C114" s="6">
+      <c r="B114" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C114" s="4">
         <v>9937899</v>
       </c>
-      <c r="D114" s="6"/>
-      <c r="E114" s="5"/>
+      <c r="D114" s="4"/>
+      <c r="E114" s="3"/>
     </row>
     <row r="115" spans="1:5">
-      <c r="A115" s="4">
+      <c r="A115" s="2">
         <v>46270</v>
       </c>
-      <c r="B115" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C115" s="6">
+      <c r="B115" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C115" s="4">
         <v>1215900</v>
       </c>
-      <c r="D115" s="6"/>
-      <c r="E115" s="5"/>
+      <c r="D115" s="4"/>
+      <c r="E115" s="3"/>
     </row>
     <row r="116" spans="1:5">
-      <c r="A116" s="4">
+      <c r="A116" s="2">
         <v>46274</v>
       </c>
-      <c r="B116" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C116" s="6">
+      <c r="B116" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C116" s="4">
         <v>15012598</v>
       </c>
-      <c r="D116" s="6"/>
-      <c r="E116" s="5"/>
+      <c r="D116" s="4"/>
+      <c r="E116" s="3"/>
     </row>
     <row r="117" spans="1:5">
-      <c r="A117" s="4">
+      <c r="A117" s="2">
         <v>46276</v>
       </c>
-      <c r="B117" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C117" s="6">
+      <c r="B117" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C117" s="4">
         <v>9462632</v>
       </c>
-      <c r="D117" s="6"/>
-      <c r="E117" s="5"/>
+      <c r="D117" s="4"/>
+      <c r="E117" s="3"/>
     </row>
     <row r="118" spans="1:5">
-      <c r="A118" s="4">
+      <c r="A118" s="2">
         <v>46279</v>
       </c>
-      <c r="B118" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C118" s="6">
+      <c r="B118" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C118" s="4">
         <v>8131384</v>
       </c>
-      <c r="D118" s="6"/>
-      <c r="E118" s="5"/>
-    </row>
-    <row r="119" spans="1:3">
-      <c r="A119" s="1">
-        <v>46280</v>
-      </c>
-      <c r="B119" t="s">
-        <v>41</v>
-      </c>
-      <c r="C119">
-        <v>3908080</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2">
-      <c r="A120" s="1">
-        <v>46281</v>
-      </c>
-      <c r="B120" t="s">
-        <v>41</v>
-      </c>
+      <c r="D118" s="4"/>
+      <c r="E118" s="3"/>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" s="2"/>
+      <c r="B119" s="3"/>
+      <c r="C119" s="4"/>
+      <c r="D119" s="4"/>
+      <c r="E119" s="3"/>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120" s="2"/>
+      <c r="B120" s="3"/>
+      <c r="C120" s="4"/>
+      <c r="D120" s="4"/>
+      <c r="E120" s="3"/>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121" s="2"/>
+      <c r="B121" s="3"/>
+      <c r="C121" s="4"/>
+      <c r="D121" s="4"/>
+      <c r="E121" s="3"/>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122" s="2"/>
+      <c r="B122" s="3"/>
+      <c r="C122" s="4"/>
+      <c r="D122" s="4"/>
+      <c r="E122" s="3"/>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123" s="2"/>
+      <c r="B123" s="3"/>
+      <c r="C123" s="4"/>
+      <c r="D123" s="4"/>
+      <c r="E123" s="3"/>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124" s="2"/>
+      <c r="B124" s="3"/>
+      <c r="C124" s="4"/>
+      <c r="D124" s="4"/>
+      <c r="E124" s="3"/>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125" s="2"/>
+      <c r="B125" s="3"/>
+      <c r="C125" s="4"/>
+      <c r="D125" s="4"/>
+      <c r="E125" s="3"/>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126" s="2"/>
+      <c r="B126" s="3"/>
+      <c r="C126" s="4"/>
+      <c r="D126" s="4"/>
+      <c r="E126" s="3"/>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127" s="2"/>
+      <c r="B127" s="3"/>
+      <c r="C127" s="4"/>
+      <c r="D127" s="4"/>
+      <c r="E127" s="3"/>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128" s="2"/>
+      <c r="B128" s="3"/>
+      <c r="C128" s="4"/>
+      <c r="D128" s="4"/>
+      <c r="E128" s="3"/>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="A129" s="2"/>
+      <c r="B129" s="3"/>
+      <c r="C129" s="4"/>
+      <c r="D129" s="4"/>
+      <c r="E129" s="3"/>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130" s="2"/>
+      <c r="B130" s="3"/>
+      <c r="C130" s="4"/>
+      <c r="D130" s="4"/>
+      <c r="E130" s="3"/>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131" s="2"/>
+      <c r="B131" s="3"/>
+      <c r="C131" s="4"/>
+      <c r="D131" s="4"/>
+      <c r="E131" s="3"/>
+    </row>
+    <row r="132" spans="1:5">
+      <c r="A132" s="2"/>
+      <c r="B132" s="3"/>
+      <c r="C132" s="4"/>
+      <c r="D132" s="4"/>
+      <c r="E132" s="3"/>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133" s="2"/>
+      <c r="B133" s="3"/>
+      <c r="C133" s="4"/>
+      <c r="D133" s="4"/>
+      <c r="E133" s="3"/>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134" s="2"/>
+      <c r="B134" s="3"/>
+      <c r="C134" s="4"/>
+      <c r="D134" s="4"/>
+      <c r="E134" s="3"/>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135" s="2"/>
+      <c r="B135" s="3"/>
+      <c r="C135" s="4"/>
+      <c r="D135" s="4"/>
+      <c r="E135" s="3"/>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136" s="2"/>
+      <c r="B136" s="3"/>
+      <c r="C136" s="4"/>
+      <c r="D136" s="4"/>
+      <c r="E136" s="3"/>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137" s="2"/>
+      <c r="B137" s="3"/>
+      <c r="C137" s="4"/>
+      <c r="D137" s="4"/>
+      <c r="E137" s="3"/>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138" s="2"/>
+      <c r="B138" s="3"/>
+      <c r="C138" s="4"/>
+      <c r="D138" s="4"/>
+      <c r="E138" s="3"/>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139" s="2"/>
+      <c r="B139" s="3"/>
+      <c r="C139" s="4"/>
+      <c r="D139" s="4"/>
+      <c r="E139" s="3"/>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140" s="2"/>
+      <c r="B140" s="3"/>
+      <c r="C140" s="4"/>
+      <c r="D140" s="4"/>
+      <c r="E140" s="3"/>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" s="2"/>
+      <c r="B141" s="3"/>
+      <c r="C141" s="4"/>
+      <c r="D141" s="4"/>
+      <c r="E141" s="3"/>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" s="2"/>
+      <c r="B142" s="3"/>
+      <c r="C142" s="4"/>
+      <c r="D142" s="4"/>
+      <c r="E142" s="3"/>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" s="2"/>
+      <c r="B143" s="3"/>
+      <c r="C143" s="4"/>
+      <c r="D143" s="4"/>
+      <c r="E143" s="3"/>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" s="2"/>
+      <c r="B144" s="3"/>
+      <c r="C144" s="4"/>
+      <c r="D144" s="4"/>
+      <c r="E144" s="3"/>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" s="2"/>
+      <c r="B145" s="3"/>
+      <c r="C145" s="4"/>
+      <c r="D145" s="4"/>
+      <c r="E145" s="3"/>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" s="2"/>
+      <c r="B146" s="3"/>
+      <c r="C146" s="4"/>
+      <c r="D146" s="4"/>
+      <c r="E146" s="3"/>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147" s="2"/>
+      <c r="B147" s="3"/>
+      <c r="C147" s="4"/>
+      <c r="D147" s="4"/>
+      <c r="E147" s="3"/>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148" s="2"/>
+      <c r="B148" s="3"/>
+      <c r="C148" s="4"/>
+      <c r="D148" s="4"/>
+      <c r="E148" s="3"/>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149" s="2"/>
+      <c r="B149" s="3"/>
+      <c r="C149" s="4"/>
+      <c r="D149" s="4"/>
+      <c r="E149" s="3"/>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150" s="2"/>
+      <c r="B150" s="3"/>
+      <c r="C150" s="4"/>
+      <c r="D150" s="4"/>
+      <c r="E150" s="3"/>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151" s="2"/>
+      <c r="B151" s="3"/>
+      <c r="C151" s="4"/>
+      <c r="D151" s="4"/>
+      <c r="E151" s="3"/>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" s="2"/>
+      <c r="B152" s="3"/>
+      <c r="C152" s="4"/>
+      <c r="D152" s="4"/>
+      <c r="E152" s="3"/>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153" s="2"/>
+      <c r="B153" s="3"/>
+      <c r="C153" s="4"/>
+      <c r="D153" s="4"/>
+      <c r="E153" s="3"/>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154" s="2"/>
+      <c r="B154" s="3"/>
+      <c r="C154" s="4"/>
+      <c r="D154" s="4"/>
+      <c r="E154" s="3"/>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155" s="2"/>
+      <c r="B155" s="3"/>
+      <c r="C155" s="4"/>
+      <c r="D155" s="4"/>
+      <c r="E155" s="3"/>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156" s="2"/>
+      <c r="B156" s="3"/>
+      <c r="C156" s="4"/>
+      <c r="D156" s="4"/>
+      <c r="E156" s="3"/>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157" s="2"/>
+      <c r="B157" s="3"/>
+      <c r="C157" s="4"/>
+      <c r="D157" s="4"/>
+      <c r="E157" s="3"/>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158" s="2"/>
+      <c r="B158" s="3"/>
+      <c r="C158" s="4"/>
+      <c r="D158" s="4"/>
+      <c r="E158" s="3"/>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159" s="2"/>
+      <c r="B159" s="3"/>
+      <c r="C159" s="4"/>
+      <c r="D159" s="4"/>
+      <c r="E159" s="3"/>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160" s="2"/>
+      <c r="B160" s="3"/>
+      <c r="C160" s="4"/>
+      <c r="D160" s="4"/>
+      <c r="E160" s="3"/>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="A161" s="2"/>
+      <c r="B161" s="3"/>
+      <c r="C161" s="4"/>
+      <c r="D161" s="4"/>
+      <c r="E161" s="3"/>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="A162" s="2"/>
+      <c r="B162" s="3"/>
+      <c r="C162" s="4"/>
+      <c r="D162" s="4"/>
+      <c r="E162" s="3"/>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163" s="2"/>
+      <c r="B163" s="3"/>
+      <c r="C163" s="4"/>
+      <c r="D163" s="4"/>
+      <c r="E163" s="3"/>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="A164" s="2"/>
+      <c r="B164" s="3"/>
+      <c r="C164" s="4"/>
+      <c r="D164" s="4"/>
+      <c r="E164" s="3"/>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165" s="2"/>
+      <c r="B165" s="3"/>
+      <c r="C165" s="4"/>
+      <c r="D165" s="4"/>
+      <c r="E165" s="3"/>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166" s="2"/>
+      <c r="B166" s="3"/>
+      <c r="C166" s="4"/>
+      <c r="D166" s="4"/>
+      <c r="E166" s="3"/>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167" s="2"/>
+      <c r="B167" s="3"/>
+      <c r="C167" s="4"/>
+      <c r="D167" s="4"/>
+      <c r="E167" s="3"/>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168" s="2"/>
+      <c r="B168" s="3"/>
+      <c r="C168" s="4"/>
+      <c r="D168" s="4"/>
+      <c r="E168" s="3"/>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169" s="2"/>
+      <c r="B169" s="3"/>
+      <c r="C169" s="4"/>
+      <c r="D169" s="4"/>
+      <c r="E169" s="3"/>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170" s="2"/>
+      <c r="B170" s="3"/>
+      <c r="C170" s="4"/>
+      <c r="D170" s="4"/>
+      <c r="E170" s="3"/>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171" s="2"/>
+      <c r="B171" s="3"/>
+      <c r="C171" s="4"/>
+      <c r="D171" s="4"/>
+      <c r="E171" s="3"/>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172" s="2"/>
+      <c r="B172" s="3"/>
+      <c r="C172" s="4"/>
+      <c r="D172" s="4"/>
+      <c r="E172" s="3"/>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173" s="2"/>
+      <c r="B173" s="3"/>
+      <c r="C173" s="4"/>
+      <c r="D173" s="4"/>
+      <c r="E173" s="3"/>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174" s="2"/>
+      <c r="B174" s="3"/>
+      <c r="C174" s="4"/>
+      <c r="D174" s="4"/>
+      <c r="E174" s="3"/>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175" s="2"/>
+      <c r="B175" s="3"/>
+      <c r="C175" s="4"/>
+      <c r="D175" s="4"/>
+      <c r="E175" s="3"/>
+    </row>
+    <row r="176" spans="1:5">
+      <c r="A176" s="2"/>
+      <c r="B176" s="3"/>
+      <c r="C176" s="4"/>
+      <c r="D176" s="4"/>
+      <c r="E176" s="3"/>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177" s="2"/>
+      <c r="B177" s="3"/>
+      <c r="C177" s="4"/>
+      <c r="D177" s="4"/>
+      <c r="E177" s="3"/>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178" s="2"/>
+      <c r="B178" s="3"/>
+      <c r="C178" s="4"/>
+      <c r="D178" s="4"/>
+      <c r="E178" s="3"/>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179" s="2"/>
+      <c r="B179" s="3"/>
+      <c r="C179" s="4"/>
+      <c r="D179" s="4"/>
+      <c r="E179" s="3"/>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180" s="2"/>
+      <c r="B180" s="3"/>
+      <c r="C180" s="4"/>
+      <c r="D180" s="4"/>
+      <c r="E180" s="3"/>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181" s="2"/>
+      <c r="B181" s="3"/>
+      <c r="C181" s="4"/>
+      <c r="D181" s="4"/>
+      <c r="E181" s="3"/>
+    </row>
+    <row r="182" spans="1:5">
+      <c r="A182" s="2"/>
+      <c r="B182" s="3"/>
+      <c r="C182" s="4"/>
+      <c r="D182" s="4"/>
+      <c r="E182" s="3"/>
+    </row>
+    <row r="183" spans="1:5">
+      <c r="A183" s="2"/>
+      <c r="B183" s="3"/>
+      <c r="C183" s="4"/>
+      <c r="D183" s="4"/>
+      <c r="E183" s="3"/>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="A184" s="2"/>
+      <c r="B184" s="3"/>
+      <c r="C184" s="4"/>
+      <c r="D184" s="4"/>
+      <c r="E184" s="3"/>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185" s="2"/>
+      <c r="B185" s="3"/>
+      <c r="C185" s="4"/>
+      <c r="D185" s="4"/>
+      <c r="E185" s="3"/>
+    </row>
+    <row r="186" spans="1:5">
+      <c r="A186" s="2"/>
+      <c r="B186" s="3"/>
+      <c r="C186" s="4"/>
+      <c r="D186" s="4"/>
+      <c r="E186" s="3"/>
+    </row>
+    <row r="187" spans="1:5">
+      <c r="A187" s="2"/>
+      <c r="B187" s="3"/>
+      <c r="C187" s="4"/>
+      <c r="D187" s="4"/>
+      <c r="E187" s="3"/>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="A188" s="2"/>
+      <c r="B188" s="3"/>
+      <c r="C188" s="4"/>
+      <c r="D188" s="4"/>
+      <c r="E188" s="3"/>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="A189" s="2"/>
+      <c r="B189" s="3"/>
+      <c r="C189" s="4"/>
+      <c r="D189" s="4"/>
+      <c r="E189" s="3"/>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190" s="2"/>
+      <c r="B190" s="3"/>
+      <c r="C190" s="4"/>
+      <c r="D190" s="4"/>
+      <c r="E190" s="3"/>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191" s="2"/>
+      <c r="B191" s="3"/>
+      <c r="C191" s="4"/>
+      <c r="D191" s="4"/>
+      <c r="E191" s="3"/>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192" s="2"/>
+      <c r="B192" s="3"/>
+      <c r="C192" s="4"/>
+      <c r="D192" s="4"/>
+      <c r="E192" s="3"/>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="A193" s="2"/>
+      <c r="B193" s="3"/>
+      <c r="C193" s="4"/>
+      <c r="D193" s="4"/>
+      <c r="E193" s="3"/>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194" s="2"/>
+      <c r="B194" s="3"/>
+      <c r="C194" s="4"/>
+      <c r="D194" s="4"/>
+      <c r="E194" s="3"/>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195" s="2"/>
+      <c r="B195" s="3"/>
+      <c r="C195" s="4"/>
+      <c r="D195" s="4"/>
+      <c r="E195" s="3"/>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" s="2"/>
+      <c r="B196" s="3"/>
+      <c r="C196" s="4"/>
+      <c r="D196" s="4"/>
+      <c r="E196" s="3"/>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" s="2"/>
+      <c r="B197" s="3"/>
+      <c r="C197" s="4"/>
+      <c r="D197" s="4"/>
+      <c r="E197" s="3"/>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" s="2"/>
+      <c r="B198" s="3"/>
+      <c r="C198" s="4"/>
+      <c r="D198" s="4"/>
+      <c r="E198" s="3"/>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" s="2"/>
+      <c r="B199" s="3"/>
+      <c r="C199" s="4"/>
+      <c r="D199" s="4"/>
+      <c r="E199" s="3"/>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" s="2"/>
+      <c r="B200" s="3"/>
+      <c r="C200" s="4"/>
+      <c r="D200" s="4"/>
+      <c r="E200" s="3"/>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" s="2"/>
+      <c r="B201" s="3"/>
+      <c r="C201" s="4"/>
+      <c r="D201" s="4"/>
+      <c r="E201" s="3"/>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" s="2"/>
+      <c r="B202" s="3"/>
+      <c r="C202" s="4"/>
+      <c r="D202" s="4"/>
+      <c r="E202" s="3"/>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" s="2"/>
+      <c r="B203" s="3"/>
+      <c r="C203" s="4"/>
+      <c r="D203" s="4"/>
+      <c r="E203" s="3"/>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" s="2"/>
+      <c r="B204" s="3"/>
+      <c r="C204" s="4"/>
+      <c r="D204" s="4"/>
+      <c r="E204" s="3"/>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" s="2"/>
+      <c r="B205" s="3"/>
+      <c r="C205" s="4"/>
+      <c r="D205" s="4"/>
+      <c r="E205" s="3"/>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" s="2"/>
+      <c r="B206" s="3"/>
+      <c r="C206" s="4"/>
+      <c r="D206" s="4"/>
+      <c r="E206" s="3"/>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" s="2"/>
+      <c r="B207" s="3"/>
+      <c r="C207" s="4"/>
+      <c r="D207" s="4"/>
+      <c r="E207" s="3"/>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" s="2"/>
+      <c r="B208" s="3"/>
+      <c r="C208" s="4"/>
+      <c r="D208" s="4"/>
+      <c r="E208" s="3"/>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" s="2"/>
+      <c r="B209" s="3"/>
+      <c r="C209" s="4"/>
+      <c r="D209" s="4"/>
+      <c r="E209" s="3"/>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" s="2"/>
+      <c r="B210" s="3"/>
+      <c r="C210" s="4"/>
+      <c r="D210" s="4"/>
+      <c r="E210" s="3"/>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" s="2"/>
+      <c r="B211" s="3"/>
+      <c r="C211" s="4"/>
+      <c r="D211" s="4"/>
+      <c r="E211" s="3"/>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" s="2"/>
+      <c r="B212" s="3"/>
+      <c r="C212" s="4"/>
+      <c r="D212" s="4"/>
+      <c r="E212" s="3"/>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" s="2"/>
+      <c r="B213" s="3"/>
+      <c r="C213" s="4"/>
+      <c r="D213" s="4"/>
+      <c r="E213" s="3"/>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" s="2"/>
+      <c r="B214" s="3"/>
+      <c r="C214" s="4"/>
+      <c r="D214" s="4"/>
+      <c r="E214" s="3"/>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" s="2"/>
+      <c r="B215" s="3"/>
+      <c r="C215" s="4"/>
+      <c r="D215" s="4"/>
+      <c r="E215" s="3"/>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" s="2"/>
+      <c r="B216" s="3"/>
+      <c r="C216" s="4"/>
+      <c r="D216" s="4"/>
+      <c r="E216" s="3"/>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" s="2"/>
+      <c r="B217" s="3"/>
+      <c r="C217" s="4"/>
+      <c r="D217" s="4"/>
+      <c r="E217" s="3"/>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218" s="2"/>
+      <c r="B218" s="3"/>
+      <c r="C218" s="4"/>
+      <c r="D218" s="4"/>
+      <c r="E218" s="3"/>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219" s="2"/>
+      <c r="B219" s="3"/>
+      <c r="C219" s="4"/>
+      <c r="D219" s="4"/>
+      <c r="E219" s="3"/>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220" s="2"/>
+      <c r="B220" s="3"/>
+      <c r="C220" s="4"/>
+      <c r="D220" s="4"/>
+      <c r="E220" s="3"/>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221" s="2"/>
+      <c r="B221" s="3"/>
+      <c r="C221" s="4"/>
+      <c r="D221" s="4"/>
+      <c r="E221" s="3"/>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222" s="2"/>
+      <c r="B222" s="3"/>
+      <c r="C222" s="4"/>
+      <c r="D222" s="4"/>
+      <c r="E222" s="3"/>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223" s="2"/>
+      <c r="B223" s="3"/>
+      <c r="C223" s="4"/>
+      <c r="D223" s="4"/>
+      <c r="E223" s="3"/>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224" s="2"/>
+      <c r="B224" s="3"/>
+      <c r="C224" s="4"/>
+      <c r="D224" s="4"/>
+      <c r="E224" s="3"/>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225" s="2"/>
+      <c r="B225" s="3"/>
+      <c r="C225" s="4"/>
+      <c r="D225" s="4"/>
+      <c r="E225" s="3"/>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226" s="2"/>
+      <c r="B226" s="3"/>
+      <c r="C226" s="4"/>
+      <c r="D226" s="4"/>
+      <c r="E226" s="3"/>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227" s="2"/>
+      <c r="B227" s="3"/>
+      <c r="C227" s="4"/>
+      <c r="D227" s="4"/>
+      <c r="E227" s="3"/>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228" s="2"/>
+      <c r="B228" s="3"/>
+      <c r="C228" s="4"/>
+      <c r="D228" s="4"/>
+      <c r="E228" s="3"/>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229" s="2"/>
+      <c r="B229" s="3"/>
+      <c r="C229" s="4"/>
+      <c r="D229" s="4"/>
+      <c r="E229" s="3"/>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230" s="2"/>
+      <c r="B230" s="3"/>
+      <c r="C230" s="4"/>
+      <c r="D230" s="4"/>
+      <c r="E230" s="3"/>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231" s="2"/>
+      <c r="B231" s="3"/>
+      <c r="C231" s="4"/>
+      <c r="D231" s="4"/>
+      <c r="E231" s="3"/>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232" s="2"/>
+      <c r="B232" s="3"/>
+      <c r="C232" s="4"/>
+      <c r="D232" s="4"/>
+      <c r="E232" s="3"/>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233" s="2"/>
+      <c r="B233" s="3"/>
+      <c r="C233" s="4"/>
+      <c r="D233" s="4"/>
+      <c r="E233" s="3"/>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234" s="2"/>
+      <c r="B234" s="3"/>
+      <c r="C234" s="4"/>
+      <c r="D234" s="4"/>
+      <c r="E234" s="3"/>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235" s="2"/>
+      <c r="B235" s="3"/>
+      <c r="C235" s="4"/>
+      <c r="D235" s="4"/>
+      <c r="E235" s="3"/>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236" s="2"/>
+      <c r="B236" s="3"/>
+      <c r="C236" s="4"/>
+      <c r="D236" s="4"/>
+      <c r="E236" s="3"/>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237" s="2"/>
+      <c r="B237" s="3"/>
+      <c r="C237" s="4"/>
+      <c r="D237" s="4"/>
+      <c r="E237" s="3"/>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238" s="2"/>
+      <c r="B238" s="3"/>
+      <c r="C238" s="4"/>
+      <c r="D238" s="4"/>
+      <c r="E238" s="3"/>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239" s="2"/>
+      <c r="B239" s="3"/>
+      <c r="C239" s="4"/>
+      <c r="D239" s="4"/>
+      <c r="E239" s="3"/>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240" s="2"/>
+      <c r="B240" s="3"/>
+      <c r="C240" s="4"/>
+      <c r="D240" s="4"/>
+      <c r="E240" s="3"/>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241" s="2"/>
+      <c r="B241" s="3"/>
+      <c r="C241" s="4"/>
+      <c r="D241" s="4"/>
+      <c r="E241" s="3"/>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242" s="2"/>
+      <c r="B242" s="3"/>
+      <c r="C242" s="4"/>
+      <c r="D242" s="4"/>
+      <c r="E242" s="3"/>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243" s="2"/>
+      <c r="B243" s="3"/>
+      <c r="C243" s="4"/>
+      <c r="D243" s="4"/>
+      <c r="E243" s="3"/>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" s="2"/>
+      <c r="B244" s="3"/>
+      <c r="C244" s="4"/>
+      <c r="D244" s="4"/>
+      <c r="E244" s="3"/>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" s="2"/>
+      <c r="B245" s="3"/>
+      <c r="C245" s="4"/>
+      <c r="D245" s="4"/>
+      <c r="E245" s="3"/>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" s="2"/>
+      <c r="B246" s="3"/>
+      <c r="C246" s="4"/>
+      <c r="D246" s="4"/>
+      <c r="E246" s="3"/>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" s="2"/>
+      <c r="B247" s="3"/>
+      <c r="C247" s="4"/>
+      <c r="D247" s="4"/>
+      <c r="E247" s="3"/>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248" s="2"/>
+      <c r="B248" s="3"/>
+      <c r="C248" s="4"/>
+      <c r="D248" s="4"/>
+      <c r="E248" s="3"/>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249" s="2"/>
+      <c r="B249" s="3"/>
+      <c r="C249" s="4"/>
+      <c r="D249" s="4"/>
+      <c r="E249" s="3"/>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250" s="2"/>
+      <c r="B250" s="3"/>
+      <c r="C250" s="4"/>
+      <c r="D250" s="4"/>
+      <c r="E250" s="3"/>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251" s="2"/>
+      <c r="B251" s="3"/>
+      <c r="C251" s="4"/>
+      <c r="D251" s="4"/>
+      <c r="E251" s="3"/>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="A252" s="2"/>
+      <c r="B252" s="3"/>
+      <c r="C252" s="4"/>
+      <c r="D252" s="4"/>
+      <c r="E252" s="3"/>
+    </row>
+    <row r="253" spans="1:5">
+      <c r="A253" s="2"/>
+      <c r="B253" s="3"/>
+      <c r="C253" s="4"/>
+      <c r="D253" s="4"/>
+      <c r="E253" s="3"/>
+    </row>
+    <row r="254" spans="1:5">
+      <c r="A254" s="2"/>
+      <c r="B254" s="3"/>
+      <c r="C254" s="4"/>
+      <c r="D254" s="4"/>
+      <c r="E254" s="3"/>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255" s="2"/>
+      <c r="B255" s="3"/>
+      <c r="C255" s="4"/>
+      <c r="D255" s="4"/>
+      <c r="E255" s="3"/>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="A256" s="2"/>
+      <c r="B256" s="3"/>
+      <c r="C256" s="4"/>
+      <c r="D256" s="4"/>
+      <c r="E256" s="3"/>
+    </row>
+    <row r="257" spans="1:5">
+      <c r="A257" s="2"/>
+      <c r="B257" s="3"/>
+      <c r="C257" s="4"/>
+      <c r="D257" s="4"/>
+      <c r="E257" s="3"/>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="A258" s="2"/>
+      <c r="B258" s="3"/>
+      <c r="C258" s="4"/>
+      <c r="D258" s="4"/>
+      <c r="E258" s="3"/>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="A259" s="2"/>
+      <c r="B259" s="3"/>
+      <c r="C259" s="4"/>
+      <c r="D259" s="4"/>
+      <c r="E259" s="3"/>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260" s="2"/>
+      <c r="B260" s="3"/>
+      <c r="C260" s="4"/>
+      <c r="D260" s="4"/>
+      <c r="E260" s="3"/>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261" s="2"/>
+      <c r="B261" s="3"/>
+      <c r="C261" s="4"/>
+      <c r="D261" s="4"/>
+      <c r="E261" s="3"/>
+    </row>
+    <row r="262" spans="1:5">
+      <c r="A262" s="2"/>
+      <c r="B262" s="3"/>
+      <c r="C262" s="4"/>
+      <c r="D262" s="4"/>
+      <c r="E262" s="3"/>
+    </row>
+    <row r="263" spans="1:5">
+      <c r="A263" s="2"/>
+      <c r="B263" s="3"/>
+      <c r="C263" s="4"/>
+      <c r="D263" s="4"/>
+      <c r="E263" s="3"/>
+    </row>
+    <row r="264" spans="1:5">
+      <c r="A264" s="2"/>
+      <c r="B264" s="3"/>
+      <c r="C264" s="4"/>
+      <c r="D264" s="4"/>
+      <c r="E264" s="3"/>
+    </row>
+    <row r="265" spans="1:5">
+      <c r="A265" s="2"/>
+      <c r="B265" s="3"/>
+      <c r="C265" s="4"/>
+      <c r="D265" s="4"/>
+      <c r="E265" s="3"/>
+    </row>
+    <row r="266" spans="1:5">
+      <c r="A266" s="2"/>
+      <c r="B266" s="3"/>
+      <c r="C266" s="4"/>
+      <c r="D266" s="4"/>
+      <c r="E266" s="3"/>
+    </row>
+    <row r="267" spans="1:5">
+      <c r="A267" s="2"/>
+      <c r="B267" s="3"/>
+      <c r="C267" s="4"/>
+      <c r="D267" s="4"/>
+      <c r="E267" s="3"/>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268" s="2"/>
+      <c r="B268" s="3"/>
+      <c r="C268" s="4"/>
+      <c r="D268" s="4"/>
+      <c r="E268" s="3"/>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="A269" s="2"/>
+      <c r="B269" s="3"/>
+      <c r="C269" s="4"/>
+      <c r="D269" s="4"/>
+      <c r="E269" s="3"/>
+    </row>
+    <row r="270" spans="1:5">
+      <c r="A270" s="2"/>
+      <c r="B270" s="3"/>
+      <c r="C270" s="4"/>
+      <c r="D270" s="4"/>
+      <c r="E270" s="3"/>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="A271" s="2"/>
+      <c r="B271" s="3"/>
+      <c r="C271" s="4"/>
+      <c r="D271" s="4"/>
+      <c r="E271" s="3"/>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="A272" s="2"/>
+      <c r="B272" s="3"/>
+      <c r="C272" s="4"/>
+      <c r="D272" s="4"/>
+      <c r="E272" s="3"/>
+    </row>
+    <row r="273" spans="1:5">
+      <c r="A273" s="2"/>
+      <c r="B273" s="3"/>
+      <c r="C273" s="4"/>
+      <c r="D273" s="4"/>
+      <c r="E273" s="3"/>
+    </row>
+    <row r="274" spans="1:5">
+      <c r="A274" s="2"/>
+      <c r="B274" s="3"/>
+      <c r="C274" s="4"/>
+      <c r="D274" s="4"/>
+      <c r="E274" s="3"/>
+    </row>
+    <row r="275" spans="1:5">
+      <c r="A275" s="2"/>
+      <c r="B275" s="3"/>
+      <c r="C275" s="4"/>
+      <c r="D275" s="4"/>
+      <c r="E275" s="3"/>
+    </row>
+    <row r="276" spans="1:5">
+      <c r="A276" s="2"/>
+      <c r="B276" s="3"/>
+      <c r="C276" s="4"/>
+      <c r="D276" s="4"/>
+      <c r="E276" s="3"/>
+    </row>
+    <row r="277" spans="1:5">
+      <c r="A277" s="2"/>
+      <c r="B277" s="3"/>
+      <c r="C277" s="4"/>
+      <c r="D277" s="4"/>
+      <c r="E277" s="3"/>
+    </row>
+    <row r="278" spans="1:5">
+      <c r="A278" s="2"/>
+      <c r="B278" s="3"/>
+      <c r="C278" s="4"/>
+      <c r="D278" s="4"/>
+      <c r="E278" s="3"/>
+    </row>
+    <row r="279" spans="1:5">
+      <c r="A279" s="2"/>
+      <c r="B279" s="3"/>
+      <c r="C279" s="4"/>
+      <c r="D279" s="4"/>
+      <c r="E279" s="3"/>
+    </row>
+    <row r="280" spans="1:5">
+      <c r="A280" s="2"/>
+      <c r="B280" s="3"/>
+      <c r="C280" s="4"/>
+      <c r="D280" s="4"/>
+      <c r="E280" s="3"/>
+    </row>
+    <row r="281" spans="1:5">
+      <c r="A281" s="2"/>
+      <c r="B281" s="3"/>
+      <c r="C281" s="4"/>
+      <c r="D281" s="4"/>
+      <c r="E281" s="3"/>
+    </row>
+    <row r="282" spans="1:5">
+      <c r="A282" s="2"/>
+      <c r="B282" s="3"/>
+      <c r="C282" s="4"/>
+      <c r="D282" s="4"/>
+      <c r="E282" s="3"/>
+    </row>
+    <row r="283" spans="1:5">
+      <c r="A283" s="2"/>
+      <c r="B283" s="3"/>
+      <c r="C283" s="4"/>
+      <c r="D283" s="4"/>
+      <c r="E283" s="3"/>
+    </row>
+    <row r="284" spans="1:5">
+      <c r="A284" s="2"/>
+      <c r="B284" s="3"/>
+      <c r="C284" s="4"/>
+      <c r="D284" s="4"/>
+      <c r="E284" s="3"/>
+    </row>
+    <row r="285" spans="1:5">
+      <c r="A285" s="2"/>
+      <c r="B285" s="3"/>
+      <c r="C285" s="4"/>
+      <c r="D285" s="4"/>
+      <c r="E285" s="3"/>
+    </row>
+    <row r="286" spans="1:5">
+      <c r="A286" s="2"/>
+      <c r="B286" s="3"/>
+      <c r="C286" s="4"/>
+      <c r="D286" s="4"/>
+      <c r="E286" s="3"/>
+    </row>
+    <row r="287" spans="1:5">
+      <c r="A287" s="2"/>
+      <c r="B287" s="3"/>
+      <c r="C287" s="4"/>
+      <c r="D287" s="4"/>
+      <c r="E287" s="3"/>
+    </row>
+    <row r="288" spans="1:5">
+      <c r="A288" s="2"/>
+      <c r="B288" s="3"/>
+      <c r="C288" s="4"/>
+      <c r="D288" s="4"/>
+      <c r="E288" s="3"/>
+    </row>
+    <row r="289" spans="1:5">
+      <c r="A289" s="2"/>
+      <c r="B289" s="3"/>
+      <c r="C289" s="4"/>
+      <c r="D289" s="4"/>
+      <c r="E289" s="3"/>
+    </row>
+    <row r="290" spans="1:5">
+      <c r="A290" s="2"/>
+      <c r="B290" s="3"/>
+      <c r="C290" s="4"/>
+      <c r="D290" s="4"/>
+      <c r="E290" s="3"/>
+    </row>
+    <row r="291" spans="1:5">
+      <c r="A291" s="2"/>
+      <c r="B291" s="3"/>
+      <c r="C291" s="4"/>
+      <c r="D291" s="4"/>
+      <c r="E291" s="3"/>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="A292" s="2"/>
+      <c r="B292" s="3"/>
+      <c r="C292" s="4"/>
+      <c r="D292" s="4"/>
+      <c r="E292" s="3"/>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293" s="2"/>
+      <c r="B293" s="3"/>
+      <c r="C293" s="4"/>
+      <c r="D293" s="4"/>
+      <c r="E293" s="3"/>
+    </row>
+    <row r="294" spans="1:5">
+      <c r="A294" s="2"/>
+      <c r="B294" s="3"/>
+      <c r="C294" s="4"/>
+      <c r="D294" s="4"/>
+      <c r="E294" s="3"/>
+    </row>
+    <row r="295" spans="1:5">
+      <c r="A295" s="2"/>
+      <c r="B295" s="3"/>
+      <c r="C295" s="4"/>
+      <c r="D295" s="4"/>
+      <c r="E295" s="3"/>
+    </row>
+    <row r="296" spans="1:5">
+      <c r="A296" s="2"/>
+      <c r="B296" s="3"/>
+      <c r="C296" s="4"/>
+      <c r="D296" s="4"/>
+      <c r="E296" s="3"/>
+    </row>
+    <row r="297" spans="1:5">
+      <c r="A297" s="2"/>
+      <c r="B297" s="3"/>
+      <c r="C297" s="4"/>
+      <c r="D297" s="4"/>
+      <c r="E297" s="3"/>
+    </row>
+    <row r="298" spans="1:5">
+      <c r="A298" s="2"/>
+      <c r="B298" s="3"/>
+      <c r="C298" s="4"/>
+      <c r="D298" s="4"/>
+      <c r="E298" s="3"/>
+    </row>
+    <row r="299" spans="1:5">
+      <c r="A299" s="2"/>
+      <c r="B299" s="3"/>
+      <c r="C299" s="4"/>
+      <c r="D299" s="4"/>
+      <c r="E299" s="3"/>
+    </row>
+    <row r="300" spans="1:5">
+      <c r="A300" s="2"/>
+      <c r="B300" s="3"/>
+      <c r="C300" s="4"/>
+      <c r="D300" s="4"/>
+      <c r="E300" s="3"/>
+    </row>
+    <row r="301" spans="1:5">
+      <c r="A301" s="2"/>
+      <c r="B301" s="3"/>
+      <c r="C301" s="4"/>
+      <c r="D301" s="4"/>
+      <c r="E301" s="3"/>
+    </row>
+    <row r="302" spans="1:5">
+      <c r="A302" s="2"/>
+      <c r="B302" s="3"/>
+      <c r="C302" s="4"/>
+      <c r="D302" s="4"/>
+      <c r="E302" s="3"/>
+    </row>
+    <row r="303" spans="1:5">
+      <c r="A303" s="2"/>
+      <c r="B303" s="3"/>
+      <c r="C303" s="4"/>
+      <c r="D303" s="4"/>
+      <c r="E303" s="3"/>
+    </row>
+    <row r="304" spans="1:5">
+      <c r="A304" s="2"/>
+      <c r="B304" s="3"/>
+      <c r="C304" s="4"/>
+      <c r="D304" s="4"/>
+      <c r="E304" s="3"/>
+    </row>
+    <row r="305" spans="1:5">
+      <c r="A305" s="2"/>
+      <c r="B305" s="3"/>
+      <c r="C305" s="4"/>
+      <c r="D305" s="4"/>
+      <c r="E305" s="3"/>
+    </row>
+    <row r="306" spans="1:5">
+      <c r="A306" s="2"/>
+      <c r="B306" s="3"/>
+      <c r="C306" s="4"/>
+      <c r="D306" s="4"/>
+      <c r="E306" s="3"/>
+    </row>
+    <row r="307" spans="1:5">
+      <c r="A307" s="2"/>
+      <c r="B307" s="3"/>
+      <c r="C307" s="4"/>
+      <c r="D307" s="4"/>
+      <c r="E307" s="3"/>
+    </row>
+    <row r="308" spans="1:5">
+      <c r="A308" s="2"/>
+      <c r="B308" s="3"/>
+      <c r="C308" s="4"/>
+      <c r="D308" s="4"/>
+      <c r="E308" s="3"/>
+    </row>
+    <row r="309" spans="1:5">
+      <c r="A309" s="2"/>
+      <c r="B309" s="3"/>
+      <c r="C309" s="4"/>
+      <c r="D309" s="4"/>
+      <c r="E309" s="3"/>
+    </row>
+    <row r="310" spans="1:5">
+      <c r="A310" s="2"/>
+      <c r="B310" s="3"/>
+      <c r="C310" s="4"/>
+      <c r="D310" s="4"/>
+      <c r="E310" s="3"/>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311" s="2"/>
+      <c r="B311" s="3"/>
+      <c r="C311" s="4"/>
+      <c r="D311" s="4"/>
+      <c r="E311" s="3"/>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312" s="2"/>
+      <c r="B312" s="3"/>
+      <c r="C312" s="4"/>
+      <c r="D312" s="4"/>
+      <c r="E312" s="3"/>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="A313" s="2"/>
+      <c r="B313" s="3"/>
+      <c r="C313" s="4"/>
+      <c r="D313" s="4"/>
+      <c r="E313" s="3"/>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314" s="2"/>
+      <c r="B314" s="3"/>
+      <c r="C314" s="4"/>
+      <c r="D314" s="4"/>
+      <c r="E314" s="3"/>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315" s="2"/>
+      <c r="B315" s="3"/>
+      <c r="C315" s="4"/>
+      <c r="D315" s="4"/>
+      <c r="E315" s="3"/>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316" s="2"/>
+      <c r="B316" s="3"/>
+      <c r="C316" s="4"/>
+      <c r="D316" s="4"/>
+      <c r="E316" s="3"/>
+    </row>
+    <row r="317" spans="1:5">
+      <c r="A317" s="2"/>
+      <c r="B317" s="3"/>
+      <c r="C317" s="4"/>
+      <c r="D317" s="4"/>
+      <c r="E317" s="3"/>
+    </row>
+    <row r="318" spans="1:5">
+      <c r="A318" s="2"/>
+      <c r="B318" s="3"/>
+      <c r="C318" s="4"/>
+      <c r="D318" s="4"/>
+      <c r="E318" s="3"/>
+    </row>
+    <row r="319" spans="1:5">
+      <c r="A319" s="2"/>
+      <c r="B319" s="3"/>
+      <c r="C319" s="4"/>
+      <c r="D319" s="4"/>
+      <c r="E319" s="3"/>
+    </row>
+    <row r="320" spans="1:5">
+      <c r="A320" s="2"/>
+      <c r="B320" s="3"/>
+      <c r="C320" s="4"/>
+      <c r="D320" s="4"/>
+      <c r="E320" s="3"/>
+    </row>
+    <row r="321" spans="1:5">
+      <c r="A321" s="2"/>
+      <c r="B321" s="3"/>
+      <c r="C321" s="4"/>
+      <c r="D321" s="4"/>
+      <c r="E321" s="3"/>
+    </row>
+    <row r="322" spans="1:5">
+      <c r="A322" s="2"/>
+      <c r="B322" s="3"/>
+      <c r="C322" s="4"/>
+      <c r="D322" s="4"/>
+      <c r="E322" s="3"/>
+    </row>
+    <row r="323" spans="1:5">
+      <c r="A323" s="2"/>
+      <c r="B323" s="3"/>
+      <c r="C323" s="4"/>
+      <c r="D323" s="4"/>
+      <c r="E323" s="3"/>
+    </row>
+    <row r="324" spans="1:5">
+      <c r="A324" s="2"/>
+      <c r="B324" s="3"/>
+      <c r="C324" s="4"/>
+      <c r="D324" s="4"/>
+      <c r="E324" s="3"/>
+    </row>
+    <row r="325" spans="1:5">
+      <c r="A325" s="2"/>
+      <c r="B325" s="3"/>
+      <c r="C325" s="4"/>
+      <c r="D325" s="4"/>
+      <c r="E325" s="3"/>
+    </row>
+    <row r="326" spans="1:5">
+      <c r="A326" s="2"/>
+      <c r="B326" s="3"/>
+      <c r="C326" s="4"/>
+      <c r="D326" s="4"/>
+      <c r="E326" s="3"/>
+    </row>
+    <row r="327" spans="1:5">
+      <c r="A327" s="2"/>
+      <c r="B327" s="3"/>
+      <c r="C327" s="4"/>
+      <c r="D327" s="4"/>
+      <c r="E327" s="3"/>
+    </row>
+    <row r="328" spans="1:5">
+      <c r="A328" s="2"/>
+      <c r="B328" s="3"/>
+      <c r="C328" s="4"/>
+      <c r="D328" s="4"/>
+      <c r="E328" s="3"/>
+    </row>
+    <row r="329" spans="1:5">
+      <c r="A329" s="2"/>
+      <c r="B329" s="3"/>
+      <c r="C329" s="4"/>
+      <c r="D329" s="4"/>
+      <c r="E329" s="3"/>
+    </row>
+    <row r="330" spans="1:5">
+      <c r="A330" s="2"/>
+      <c r="B330" s="3"/>
+      <c r="C330" s="4"/>
+      <c r="D330" s="4"/>
+      <c r="E330" s="3"/>
+    </row>
+    <row r="331" spans="1:5">
+      <c r="A331" s="2"/>
+      <c r="B331" s="3"/>
+      <c r="C331" s="4"/>
+      <c r="D331" s="4"/>
+      <c r="E331" s="3"/>
+    </row>
+    <row r="332" spans="1:5">
+      <c r="A332" s="2"/>
+      <c r="B332" s="3"/>
+      <c r="C332" s="4"/>
+      <c r="D332" s="4"/>
+      <c r="E332" s="3"/>
+    </row>
+    <row r="333" spans="1:5">
+      <c r="A333" s="2"/>
+      <c r="B333" s="3"/>
+      <c r="C333" s="4"/>
+      <c r="D333" s="4"/>
+      <c r="E333" s="3"/>
+    </row>
+    <row r="334" spans="1:5">
+      <c r="A334" s="2"/>
+      <c r="B334" s="3"/>
+      <c r="C334" s="4"/>
+      <c r="D334" s="4"/>
+      <c r="E334" s="3"/>
+    </row>
+    <row r="335" spans="1:5">
+      <c r="A335" s="2"/>
+      <c r="B335" s="3"/>
+      <c r="C335" s="4"/>
+      <c r="D335" s="4"/>
+      <c r="E335" s="3"/>
+    </row>
+    <row r="336" spans="1:5">
+      <c r="A336" s="2"/>
+      <c r="B336" s="3"/>
+      <c r="C336" s="4"/>
+      <c r="D336" s="4"/>
+      <c r="E336" s="3"/>
+    </row>
+    <row r="337" spans="1:5">
+      <c r="A337" s="2"/>
+      <c r="B337" s="3"/>
+      <c r="C337" s="4"/>
+      <c r="D337" s="4"/>
+      <c r="E337" s="3"/>
+    </row>
+    <row r="338" spans="1:5">
+      <c r="A338" s="2"/>
+      <c r="B338" s="3"/>
+      <c r="C338" s="4"/>
+      <c r="D338" s="4"/>
+      <c r="E338" s="3"/>
+    </row>
+    <row r="339" spans="1:5">
+      <c r="A339" s="2"/>
+      <c r="B339" s="3"/>
+      <c r="C339" s="4"/>
+      <c r="D339" s="4"/>
+      <c r="E339" s="3"/>
+    </row>
+    <row r="340" spans="1:5">
+      <c r="A340" s="2"/>
+      <c r="B340" s="3"/>
+      <c r="C340" s="4"/>
+      <c r="D340" s="4"/>
+      <c r="E340" s="3"/>
+    </row>
+    <row r="341" spans="1:5">
+      <c r="A341" s="2"/>
+      <c r="B341" s="3"/>
+      <c r="C341" s="4"/>
+      <c r="D341" s="4"/>
+      <c r="E341" s="3"/>
+    </row>
+    <row r="342" spans="1:5">
+      <c r="A342" s="2"/>
+      <c r="B342" s="3"/>
+      <c r="C342" s="4"/>
+      <c r="D342" s="4"/>
+      <c r="E342" s="3"/>
+    </row>
+    <row r="343" spans="1:5">
+      <c r="A343" s="2"/>
+      <c r="B343" s="3"/>
+      <c r="C343" s="4"/>
+      <c r="D343" s="4"/>
+      <c r="E343" s="3"/>
+    </row>
+    <row r="344" spans="1:5">
+      <c r="A344" s="2"/>
+      <c r="B344" s="3"/>
+      <c r="C344" s="4"/>
+      <c r="D344" s="4"/>
+      <c r="E344" s="3"/>
+    </row>
+    <row r="345" spans="1:5">
+      <c r="A345" s="2"/>
+      <c r="B345" s="3"/>
+      <c r="C345" s="4"/>
+      <c r="D345" s="4"/>
+      <c r="E345" s="3"/>
+    </row>
+    <row r="346" spans="1:5">
+      <c r="A346" s="2"/>
+      <c r="B346" s="3"/>
+      <c r="C346" s="4"/>
+      <c r="D346" s="4"/>
+      <c r="E346" s="3"/>
+    </row>
+    <row r="347" spans="1:5">
+      <c r="A347" s="2"/>
+      <c r="B347" s="3"/>
+      <c r="C347" s="4"/>
+      <c r="D347" s="4"/>
+      <c r="E347" s="3"/>
+    </row>
+    <row r="348" spans="1:5">
+      <c r="A348" s="2"/>
+      <c r="B348" s="3"/>
+      <c r="C348" s="4"/>
+      <c r="D348" s="4"/>
+      <c r="E348" s="3"/>
+    </row>
+    <row r="349" spans="1:5">
+      <c r="A349" s="2"/>
+      <c r="B349" s="3"/>
+      <c r="C349" s="4"/>
+      <c r="D349" s="4"/>
+      <c r="E349" s="3"/>
+    </row>
+    <row r="350" spans="1:5">
+      <c r="A350" s="2"/>
+      <c r="B350" s="3"/>
+      <c r="C350" s="4"/>
+      <c r="D350" s="4"/>
+      <c r="E350" s="3"/>
+    </row>
+    <row r="351" spans="1:5">
+      <c r="A351" s="2"/>
+      <c r="B351" s="3"/>
+      <c r="C351" s="4"/>
+      <c r="D351" s="4"/>
+      <c r="E351" s="3"/>
+    </row>
+    <row r="352" spans="1:5">
+      <c r="A352" s="2"/>
+      <c r="B352" s="3"/>
+      <c r="C352" s="4"/>
+      <c r="D352" s="4"/>
+      <c r="E352" s="3"/>
+    </row>
+    <row r="353" spans="1:5">
+      <c r="A353" s="2"/>
+      <c r="B353" s="3"/>
+      <c r="C353" s="4"/>
+      <c r="D353" s="4"/>
+      <c r="E353" s="3"/>
+    </row>
+    <row r="354" spans="1:5">
+      <c r="A354" s="2"/>
+      <c r="B354" s="3"/>
+      <c r="C354" s="4"/>
+      <c r="D354" s="4"/>
+      <c r="E354" s="3"/>
+    </row>
+    <row r="355" spans="1:5">
+      <c r="A355" s="2"/>
+      <c r="B355" s="3"/>
+      <c r="C355" s="4"/>
+      <c r="D355" s="4"/>
+      <c r="E355" s="3"/>
+    </row>
+    <row r="356" spans="1:5">
+      <c r="A356" s="2"/>
+      <c r="B356" s="3"/>
+      <c r="C356" s="4"/>
+      <c r="D356" s="4"/>
+      <c r="E356" s="3"/>
+    </row>
+    <row r="357" spans="1:5">
+      <c r="A357" s="2"/>
+      <c r="B357" s="3"/>
+      <c r="C357" s="4"/>
+      <c r="D357" s="4"/>
+      <c r="E357" s="3"/>
+    </row>
+    <row r="358" spans="1:5">
+      <c r="A358" s="2"/>
+      <c r="B358" s="3"/>
+      <c r="C358" s="4"/>
+      <c r="D358" s="4"/>
+      <c r="E358" s="3"/>
+    </row>
+    <row r="359" spans="1:5">
+      <c r="A359" s="2"/>
+      <c r="B359" s="3"/>
+      <c r="C359" s="4"/>
+      <c r="D359" s="4"/>
+      <c r="E359" s="3"/>
+    </row>
+    <row r="360" spans="1:5">
+      <c r="A360" s="2"/>
+      <c r="B360" s="3"/>
+      <c r="C360" s="4"/>
+      <c r="D360" s="4"/>
+      <c r="E360" s="3"/>
+    </row>
+    <row r="361" spans="1:5">
+      <c r="A361" s="2"/>
+      <c r="B361" s="3"/>
+      <c r="C361" s="4"/>
+      <c r="D361" s="4"/>
+      <c r="E361" s="3"/>
+    </row>
+    <row r="362" spans="1:5">
+      <c r="A362" s="2"/>
+      <c r="B362" s="3"/>
+      <c r="C362" s="4"/>
+      <c r="D362" s="4"/>
+      <c r="E362" s="3"/>
+    </row>
+    <row r="363" spans="1:5">
+      <c r="A363" s="2"/>
+      <c r="B363" s="3"/>
+      <c r="C363" s="4"/>
+      <c r="D363" s="4"/>
+      <c r="E363" s="3"/>
+    </row>
+    <row r="364" spans="1:5">
+      <c r="A364" s="2"/>
+      <c r="B364" s="3"/>
+      <c r="C364" s="4"/>
+      <c r="D364" s="4"/>
+      <c r="E364" s="3"/>
+    </row>
+    <row r="365" spans="1:5">
+      <c r="A365" s="2"/>
+      <c r="B365" s="3"/>
+      <c r="C365" s="4"/>
+      <c r="D365" s="4"/>
+      <c r="E365" s="3"/>
+    </row>
+    <row r="366" spans="1:5">
+      <c r="A366" s="2"/>
+      <c r="B366" s="3"/>
+      <c r="C366" s="4"/>
+      <c r="D366" s="4"/>
+      <c r="E366" s="3"/>
+    </row>
+    <row r="367" spans="1:5">
+      <c r="A367" s="2"/>
+      <c r="B367" s="3"/>
+      <c r="C367" s="4"/>
+      <c r="D367" s="4"/>
+      <c r="E367" s="3"/>
+    </row>
+    <row r="368" spans="1:5">
+      <c r="A368" s="2"/>
+      <c r="B368" s="3"/>
+      <c r="C368" s="4"/>
+      <c r="D368" s="4"/>
+      <c r="E368" s="3"/>
+    </row>
+    <row r="369" spans="1:5">
+      <c r="A369" s="2"/>
+      <c r="B369" s="3"/>
+      <c r="C369" s="4"/>
+      <c r="D369" s="4"/>
+      <c r="E369" s="3"/>
+    </row>
+    <row r="370" spans="1:5">
+      <c r="A370" s="2"/>
+      <c r="B370" s="3"/>
+      <c r="C370" s="4"/>
+      <c r="D370" s="4"/>
+      <c r="E370" s="3"/>
+    </row>
+    <row r="371" spans="1:5">
+      <c r="A371" s="2"/>
+      <c r="B371" s="3"/>
+      <c r="C371" s="4"/>
+      <c r="D371" s="4"/>
+      <c r="E371" s="3"/>
+    </row>
+    <row r="372" spans="1:5">
+      <c r="A372" s="2"/>
+      <c r="B372" s="3"/>
+      <c r="C372" s="4"/>
+      <c r="D372" s="4"/>
+      <c r="E372" s="3"/>
+    </row>
+    <row r="373" spans="1:5">
+      <c r="A373" s="2"/>
+      <c r="B373" s="3"/>
+      <c r="C373" s="4"/>
+      <c r="D373" s="4"/>
+      <c r="E373" s="3"/>
+    </row>
+    <row r="374" spans="1:5">
+      <c r="A374" s="2"/>
+      <c r="B374" s="3"/>
+      <c r="C374" s="4"/>
+      <c r="D374" s="4"/>
+      <c r="E374" s="3"/>
+    </row>
+    <row r="375" spans="1:5">
+      <c r="A375" s="2"/>
+      <c r="B375" s="3"/>
+      <c r="C375" s="4"/>
+      <c r="D375" s="4"/>
+      <c r="E375" s="3"/>
+    </row>
+    <row r="376" spans="1:5">
+      <c r="A376" s="2"/>
+      <c r="B376" s="3"/>
+      <c r="C376" s="4"/>
+      <c r="D376" s="4"/>
+      <c r="E376" s="3"/>
+    </row>
+    <row r="377" spans="1:5">
+      <c r="A377" s="2"/>
+      <c r="B377" s="3"/>
+      <c r="C377" s="4"/>
+      <c r="D377" s="4"/>
+      <c r="E377" s="3"/>
+    </row>
+    <row r="378" spans="1:5">
+      <c r="A378" s="2"/>
+      <c r="B378" s="3"/>
+      <c r="C378" s="4"/>
+      <c r="D378" s="4"/>
+      <c r="E378" s="3"/>
+    </row>
+    <row r="379" spans="1:5">
+      <c r="A379" s="2"/>
+      <c r="B379" s="3"/>
+      <c r="C379" s="4"/>
+      <c r="D379" s="4"/>
+      <c r="E379" s="3"/>
+    </row>
+    <row r="380" spans="1:5">
+      <c r="A380" s="2"/>
+      <c r="B380" s="3"/>
+      <c r="C380" s="4"/>
+      <c r="D380" s="4"/>
+      <c r="E380" s="3"/>
+    </row>
+    <row r="381" spans="1:5">
+      <c r="A381" s="2"/>
+      <c r="B381" s="3"/>
+      <c r="C381" s="4"/>
+      <c r="D381" s="4"/>
+      <c r="E381" s="3"/>
+    </row>
+    <row r="382" spans="1:5">
+      <c r="A382" s="2"/>
+      <c r="B382" s="3"/>
+      <c r="C382" s="4"/>
+      <c r="D382" s="4"/>
+      <c r="E382" s="3"/>
+    </row>
+    <row r="383" spans="1:5">
+      <c r="A383" s="2"/>
+      <c r="B383" s="3"/>
+      <c r="C383" s="4"/>
+      <c r="D383" s="4"/>
+      <c r="E383" s="3"/>
+    </row>
+    <row r="384" spans="1:5">
+      <c r="A384" s="2"/>
+      <c r="B384" s="3"/>
+      <c r="C384" s="4"/>
+      <c r="D384" s="4"/>
+      <c r="E384" s="3"/>
+    </row>
+    <row r="385" spans="1:5">
+      <c r="A385" s="2"/>
+      <c r="B385" s="3"/>
+      <c r="C385" s="4"/>
+      <c r="D385" s="4"/>
+      <c r="E385" s="3"/>
+    </row>
+    <row r="386" spans="1:5">
+      <c r="A386" s="2"/>
+      <c r="B386" s="3"/>
+      <c r="C386" s="4"/>
+      <c r="D386" s="4"/>
+      <c r="E386" s="3"/>
+    </row>
+    <row r="387" spans="1:5">
+      <c r="A387" s="2"/>
+      <c r="B387" s="3"/>
+      <c r="C387" s="4"/>
+      <c r="D387" s="4"/>
+      <c r="E387" s="3"/>
+    </row>
+    <row r="388" spans="1:5">
+      <c r="A388" s="2"/>
+      <c r="B388" s="3"/>
+      <c r="C388" s="4"/>
+      <c r="D388" s="4"/>
+      <c r="E388" s="3"/>
+    </row>
+    <row r="389" spans="1:5">
+      <c r="A389" s="2"/>
+      <c r="B389" s="3"/>
+      <c r="C389" s="4"/>
+      <c r="D389" s="4"/>
+      <c r="E389" s="3"/>
+    </row>
+    <row r="390" spans="1:5">
+      <c r="A390" s="2"/>
+      <c r="B390" s="3"/>
+      <c r="C390" s="4"/>
+      <c r="D390" s="4"/>
+      <c r="E390" s="3"/>
+    </row>
+    <row r="391" spans="1:5">
+      <c r="A391" s="2"/>
+      <c r="B391" s="3"/>
+      <c r="C391" s="4"/>
+      <c r="D391" s="4"/>
+      <c r="E391" s="3"/>
+    </row>
+    <row r="392" spans="1:5">
+      <c r="A392" s="2"/>
+      <c r="B392" s="3"/>
+      <c r="C392" s="4"/>
+      <c r="D392" s="4"/>
+      <c r="E392" s="3"/>
+    </row>
+    <row r="393" spans="1:5">
+      <c r="A393" s="2"/>
+      <c r="B393" s="3"/>
+      <c r="C393" s="4"/>
+      <c r="D393" s="4"/>
+      <c r="E393" s="3"/>
+    </row>
+    <row r="394" spans="1:5">
+      <c r="A394" s="2"/>
+      <c r="B394" s="3"/>
+      <c r="C394" s="4"/>
+      <c r="D394" s="4"/>
+      <c r="E394" s="3"/>
+    </row>
+    <row r="395" spans="1:5">
+      <c r="A395" s="2"/>
+      <c r="B395" s="3"/>
+      <c r="C395" s="4"/>
+      <c r="D395" s="4"/>
+      <c r="E395" s="3"/>
+    </row>
+    <row r="396" spans="1:5">
+      <c r="A396" s="2"/>
+      <c r="B396" s="3"/>
+      <c r="C396" s="4"/>
+      <c r="D396" s="4"/>
+      <c r="E396" s="3"/>
+    </row>
+    <row r="397" spans="1:5">
+      <c r="A397" s="2"/>
+      <c r="B397" s="3"/>
+      <c r="C397" s="4"/>
+      <c r="D397" s="4"/>
+      <c r="E397" s="3"/>
+    </row>
+    <row r="398" spans="1:5">
+      <c r="A398" s="2"/>
+      <c r="B398" s="3"/>
+      <c r="C398" s="4"/>
+      <c r="D398" s="4"/>
+      <c r="E398" s="3"/>
+    </row>
+    <row r="399" spans="1:5">
+      <c r="A399" s="2"/>
+      <c r="B399" s="3"/>
+      <c r="C399" s="4"/>
+      <c r="D399" s="4"/>
+      <c r="E399" s="3"/>
+    </row>
+    <row r="400" spans="1:5">
+      <c r="A400" s="2"/>
+      <c r="B400" s="3"/>
+      <c r="C400" s="4"/>
+      <c r="D400" s="4"/>
+      <c r="E400" s="3"/>
+    </row>
+    <row r="401" spans="1:5">
+      <c r="A401" s="2"/>
+      <c r="B401" s="3"/>
+      <c r="C401" s="4"/>
+      <c r="D401" s="4"/>
+      <c r="E401" s="3"/>
+    </row>
+    <row r="402" spans="1:5">
+      <c r="A402" s="2"/>
+      <c r="B402" s="3"/>
+      <c r="C402" s="4"/>
+      <c r="D402" s="4"/>
+      <c r="E402" s="3"/>
+    </row>
+    <row r="403" spans="1:5">
+      <c r="A403" s="2"/>
+      <c r="B403" s="3"/>
+      <c r="C403" s="4"/>
+      <c r="D403" s="4"/>
+      <c r="E403" s="3"/>
+    </row>
+    <row r="404" spans="1:5">
+      <c r="A404" s="2"/>
+      <c r="B404" s="3"/>
+      <c r="C404" s="4"/>
+      <c r="D404" s="4"/>
+      <c r="E404" s="3"/>
+    </row>
+    <row r="405" spans="1:5">
+      <c r="A405" s="2"/>
+      <c r="B405" s="3"/>
+      <c r="C405" s="4"/>
+      <c r="D405" s="4"/>
+      <c r="E405" s="3"/>
+    </row>
+    <row r="406" spans="1:5">
+      <c r="A406" s="2"/>
+      <c r="B406" s="3"/>
+      <c r="C406" s="4"/>
+      <c r="D406" s="4"/>
+      <c r="E406" s="3"/>
+    </row>
+    <row r="407" spans="1:5">
+      <c r="A407" s="2"/>
+      <c r="B407" s="3"/>
+      <c r="C407" s="4"/>
+      <c r="D407" s="4"/>
+      <c r="E407" s="3"/>
+    </row>
+    <row r="408" spans="1:5">
+      <c r="A408" s="2"/>
+      <c r="B408" s="3"/>
+      <c r="C408" s="4"/>
+      <c r="D408" s="4"/>
+      <c r="E408" s="3"/>
+    </row>
+    <row r="409" spans="1:5">
+      <c r="A409" s="2"/>
+      <c r="B409" s="3"/>
+      <c r="C409" s="4"/>
+      <c r="D409" s="4"/>
+      <c r="E409" s="3"/>
+    </row>
+    <row r="410" spans="1:5">
+      <c r="A410" s="2"/>
+      <c r="B410" s="3"/>
+      <c r="C410" s="4"/>
+      <c r="D410" s="4"/>
+      <c r="E410" s="3"/>
+    </row>
+    <row r="411" spans="1:5">
+      <c r="A411" s="2"/>
+      <c r="B411" s="3"/>
+      <c r="C411" s="4"/>
+      <c r="D411" s="4"/>
+      <c r="E411" s="3"/>
+    </row>
+    <row r="412" spans="1:5">
+      <c r="A412" s="2"/>
+      <c r="B412" s="3"/>
+      <c r="C412" s="4"/>
+      <c r="D412" s="4"/>
+      <c r="E412" s="3"/>
+    </row>
+    <row r="413" spans="1:5">
+      <c r="A413" s="2"/>
+      <c r="B413" s="3"/>
+      <c r="C413" s="4"/>
+      <c r="D413" s="4"/>
+      <c r="E413" s="3"/>
+    </row>
+    <row r="414" spans="1:5">
+      <c r="A414" s="2"/>
+      <c r="B414" s="3"/>
+      <c r="C414" s="4"/>
+      <c r="D414" s="4"/>
+      <c r="E414" s="3"/>
+    </row>
+    <row r="415" spans="1:5">
+      <c r="A415" s="2"/>
+      <c r="B415" s="3"/>
+      <c r="C415" s="4"/>
+      <c r="D415" s="4"/>
+      <c r="E415" s="3"/>
+    </row>
+    <row r="416" spans="1:5">
+      <c r="A416" s="2"/>
+      <c r="B416" s="3"/>
+      <c r="C416" s="4"/>
+      <c r="D416" s="4"/>
+      <c r="E416" s="3"/>
+    </row>
+    <row r="417" spans="1:5">
+      <c r="A417" s="2"/>
+      <c r="B417" s="3"/>
+      <c r="C417" s="4"/>
+      <c r="D417" s="4"/>
+      <c r="E417" s="3"/>
+    </row>
+    <row r="418" spans="1:5">
+      <c r="A418" s="2"/>
+      <c r="B418" s="3"/>
+      <c r="C418" s="4"/>
+      <c r="D418" s="4"/>
+      <c r="E418" s="3"/>
+    </row>
+    <row r="419" spans="1:5">
+      <c r="A419" s="2"/>
+      <c r="B419" s="3"/>
+      <c r="C419" s="4"/>
+      <c r="D419" s="4"/>
+      <c r="E419" s="3"/>
+    </row>
+    <row r="420" spans="1:5">
+      <c r="A420" s="2"/>
+      <c r="B420" s="3"/>
+      <c r="C420" s="4"/>
+      <c r="D420" s="4"/>
+      <c r="E420" s="3"/>
+    </row>
+    <row r="421" spans="1:5">
+      <c r="A421" s="2"/>
+      <c r="B421" s="3"/>
+      <c r="C421" s="4"/>
+      <c r="D421" s="4"/>
+      <c r="E421" s="3"/>
+    </row>
+    <row r="422" spans="1:5">
+      <c r="A422" s="2"/>
+      <c r="B422" s="3"/>
+      <c r="C422" s="4"/>
+      <c r="D422" s="4"/>
+      <c r="E422" s="3"/>
+    </row>
+    <row r="423" spans="1:5">
+      <c r="A423" s="2"/>
+      <c r="B423" s="3"/>
+      <c r="C423" s="4"/>
+      <c r="D423" s="4"/>
+      <c r="E423" s="3"/>
+    </row>
+    <row r="424" spans="1:5">
+      <c r="A424" s="2"/>
+      <c r="B424" s="3"/>
+      <c r="C424" s="4"/>
+      <c r="D424" s="4"/>
+      <c r="E424" s="3"/>
+    </row>
+    <row r="425" spans="1:5">
+      <c r="A425" s="2"/>
+      <c r="B425" s="3"/>
+      <c r="C425" s="4"/>
+      <c r="D425" s="4"/>
+      <c r="E425" s="3"/>
+    </row>
+    <row r="426" spans="1:5">
+      <c r="A426" s="2"/>
+      <c r="B426" s="3"/>
+      <c r="C426" s="4"/>
+      <c r="D426" s="4"/>
+      <c r="E426" s="3"/>
+    </row>
+    <row r="427" spans="1:5">
+      <c r="A427" s="2"/>
+      <c r="B427" s="3"/>
+      <c r="C427" s="4"/>
+      <c r="D427" s="4"/>
+      <c r="E427" s="3"/>
+    </row>
+    <row r="428" spans="1:5">
+      <c r="A428" s="2"/>
+      <c r="B428" s="3"/>
+      <c r="C428" s="4"/>
+      <c r="D428" s="4"/>
+      <c r="E428" s="3"/>
+    </row>
+    <row r="429" spans="1:5">
+      <c r="A429" s="2"/>
+      <c r="B429" s="3"/>
+      <c r="C429" s="4"/>
+      <c r="D429" s="4"/>
+      <c r="E429" s="3"/>
+    </row>
+    <row r="430" spans="1:5">
+      <c r="A430" s="2"/>
+      <c r="B430" s="3"/>
+      <c r="C430" s="4"/>
+      <c r="D430" s="4"/>
+      <c r="E430" s="3"/>
+    </row>
+    <row r="431" spans="1:5">
+      <c r="A431" s="2"/>
+      <c r="B431" s="3"/>
+      <c r="C431" s="4"/>
+      <c r="D431" s="4"/>
+      <c r="E431" s="3"/>
+    </row>
+    <row r="432" spans="1:5">
+      <c r="A432" s="2"/>
+      <c r="B432" s="3"/>
+      <c r="C432" s="4"/>
+      <c r="D432" s="4"/>
+      <c r="E432" s="3"/>
+    </row>
+    <row r="433" spans="1:5">
+      <c r="A433" s="2"/>
+      <c r="B433" s="3"/>
+      <c r="C433" s="4"/>
+      <c r="D433" s="4"/>
+      <c r="E433" s="3"/>
+    </row>
+    <row r="434" spans="1:5">
+      <c r="A434" s="2"/>
+      <c r="B434" s="3"/>
+      <c r="C434" s="4"/>
+      <c r="D434" s="4"/>
+      <c r="E434" s="3"/>
+    </row>
+    <row r="435" spans="1:5">
+      <c r="A435" s="2"/>
+      <c r="B435" s="3"/>
+      <c r="C435" s="4"/>
+      <c r="D435" s="4"/>
+      <c r="E435" s="3"/>
+    </row>
+    <row r="436" spans="1:5">
+      <c r="A436" s="2"/>
+      <c r="B436" s="3"/>
+      <c r="C436" s="4"/>
+      <c r="D436" s="4"/>
+      <c r="E436" s="3"/>
+    </row>
+    <row r="437" spans="1:5">
+      <c r="A437" s="2"/>
+      <c r="B437" s="3"/>
+      <c r="C437" s="4"/>
+      <c r="D437" s="4"/>
+      <c r="E437" s="3"/>
+    </row>
+    <row r="438" spans="1:5">
+      <c r="A438" s="2"/>
+      <c r="B438" s="3"/>
+      <c r="C438" s="4"/>
+      <c r="D438" s="4"/>
+      <c r="E438" s="3"/>
+    </row>
+    <row r="439" spans="1:5">
+      <c r="A439" s="2"/>
+      <c r="B439" s="3"/>
+      <c r="C439" s="4"/>
+      <c r="D439" s="4"/>
+      <c r="E439" s="3"/>
+    </row>
+    <row r="440" spans="1:5">
+      <c r="A440" s="2"/>
+      <c r="B440" s="3"/>
+      <c r="C440" s="4"/>
+      <c r="D440" s="4"/>
+      <c r="E440" s="3"/>
+    </row>
+    <row r="441" spans="1:5">
+      <c r="A441" s="2"/>
+      <c r="B441" s="3"/>
+      <c r="C441" s="4"/>
+      <c r="D441" s="4"/>
+      <c r="E441" s="3"/>
+    </row>
+    <row r="442" spans="1:5">
+      <c r="A442" s="2"/>
+      <c r="B442" s="3"/>
+      <c r="C442" s="4"/>
+      <c r="D442" s="4"/>
+      <c r="E442" s="3"/>
+    </row>
+    <row r="443" spans="1:5">
+      <c r="A443" s="2"/>
+      <c r="B443" s="3"/>
+      <c r="C443" s="4"/>
+      <c r="D443" s="4"/>
+      <c r="E443" s="3"/>
+    </row>
+    <row r="444" spans="1:5">
+      <c r="A444" s="2"/>
+      <c r="B444" s="3"/>
+      <c r="C444" s="4"/>
+      <c r="D444" s="4"/>
+      <c r="E444" s="3"/>
+    </row>
+    <row r="445" spans="1:5">
+      <c r="A445" s="2"/>
+      <c r="B445" s="3"/>
+      <c r="C445" s="4"/>
+      <c r="D445" s="4"/>
+      <c r="E445" s="3"/>
+    </row>
+    <row r="446" spans="1:5">
+      <c r="A446" s="2"/>
+      <c r="B446" s="3"/>
+      <c r="C446" s="4"/>
+      <c r="D446" s="4"/>
+      <c r="E446" s="3"/>
+    </row>
+    <row r="447" spans="1:5">
+      <c r="A447" s="2"/>
+      <c r="B447" s="3"/>
+      <c r="C447" s="4"/>
+      <c r="D447" s="4"/>
+      <c r="E447" s="3"/>
+    </row>
+    <row r="448" spans="1:5">
+      <c r="A448" s="2"/>
+      <c r="B448" s="3"/>
+      <c r="C448" s="4"/>
+      <c r="D448" s="4"/>
+      <c r="E448" s="3"/>
+    </row>
+    <row r="449" spans="1:5">
+      <c r="A449" s="2"/>
+      <c r="B449" s="3"/>
+      <c r="C449" s="4"/>
+      <c r="D449" s="4"/>
+      <c r="E449" s="3"/>
+    </row>
+    <row r="450" spans="1:5">
+      <c r="A450" s="2"/>
+      <c r="B450" s="3"/>
+      <c r="C450" s="4"/>
+      <c r="D450" s="4"/>
+      <c r="E450" s="3"/>
+    </row>
+    <row r="451" spans="1:5">
+      <c r="A451" s="2"/>
+      <c r="B451" s="3"/>
+      <c r="C451" s="4"/>
+      <c r="D451" s="4"/>
+      <c r="E451" s="3"/>
+    </row>
+    <row r="452" spans="1:5">
+      <c r="A452" s="2"/>
+      <c r="B452" s="3"/>
+      <c r="C452" s="4"/>
+      <c r="D452" s="4"/>
+      <c r="E452" s="3"/>
+    </row>
+    <row r="453" spans="1:5">
+      <c r="A453" s="2"/>
+      <c r="B453" s="3"/>
+      <c r="C453" s="4"/>
+      <c r="D453" s="4"/>
+      <c r="E453" s="3"/>
+    </row>
+    <row r="454" spans="1:5">
+      <c r="A454" s="2"/>
+      <c r="B454" s="3"/>
+      <c r="C454" s="4"/>
+      <c r="D454" s="4"/>
+      <c r="E454" s="3"/>
+    </row>
+    <row r="455" spans="1:5">
+      <c r="A455" s="2"/>
+      <c r="B455" s="3"/>
+      <c r="C455" s="4"/>
+      <c r="D455" s="4"/>
+      <c r="E455" s="3"/>
+    </row>
+    <row r="456" spans="1:5">
+      <c r="A456" s="2"/>
+      <c r="B456" s="3"/>
+      <c r="C456" s="4"/>
+      <c r="D456" s="4"/>
+      <c r="E456" s="3"/>
+    </row>
+    <row r="457" spans="1:5">
+      <c r="A457" s="2"/>
+      <c r="B457" s="3"/>
+      <c r="C457" s="4"/>
+      <c r="D457" s="4"/>
+      <c r="E457" s="3"/>
+    </row>
+    <row r="458" spans="1:5">
+      <c r="A458" s="2"/>
+      <c r="B458" s="3"/>
+      <c r="C458" s="4"/>
+      <c r="D458" s="4"/>
+      <c r="E458" s="3"/>
+    </row>
+    <row r="459" spans="1:5">
+      <c r="A459" s="2"/>
+      <c r="B459" s="3"/>
+      <c r="C459" s="4"/>
+      <c r="D459" s="4"/>
+      <c r="E459" s="3"/>
+    </row>
+    <row r="460" spans="1:5">
+      <c r="A460" s="2"/>
+      <c r="B460" s="3"/>
+      <c r="C460" s="4"/>
+      <c r="D460" s="4"/>
+      <c r="E460" s="3"/>
+    </row>
+    <row r="461" spans="1:5">
+      <c r="A461" s="2"/>
+      <c r="B461" s="3"/>
+      <c r="C461" s="4"/>
+      <c r="D461" s="4"/>
+      <c r="E461" s="3"/>
+    </row>
+    <row r="462" spans="1:5">
+      <c r="A462" s="2"/>
+      <c r="B462" s="3"/>
+      <c r="C462" s="4"/>
+      <c r="D462" s="4"/>
+      <c r="E462" s="3"/>
+    </row>
+    <row r="463" spans="1:5">
+      <c r="A463" s="2"/>
+      <c r="B463" s="3"/>
+      <c r="C463" s="4"/>
+      <c r="D463" s="4"/>
+      <c r="E463" s="3"/>
+    </row>
+    <row r="464" spans="1:5">
+      <c r="A464" s="2"/>
+      <c r="B464" s="3"/>
+      <c r="C464" s="4"/>
+      <c r="D464" s="4"/>
+      <c r="E464" s="3"/>
+    </row>
+    <row r="465" spans="1:5">
+      <c r="A465" s="2"/>
+      <c r="B465" s="3"/>
+      <c r="C465" s="4"/>
+      <c r="D465" s="4"/>
+      <c r="E465" s="3"/>
+    </row>
+    <row r="466" spans="1:5">
+      <c r="A466" s="2"/>
+      <c r="B466" s="3"/>
+      <c r="C466" s="4"/>
+      <c r="D466" s="4"/>
+      <c r="E466" s="3"/>
+    </row>
+    <row r="467" spans="1:5">
+      <c r="A467" s="2"/>
+      <c r="B467" s="3"/>
+      <c r="C467" s="4"/>
+      <c r="D467" s="4"/>
+      <c r="E467" s="3"/>
+    </row>
+    <row r="468" spans="1:5">
+      <c r="A468" s="2"/>
+      <c r="B468" s="3"/>
+      <c r="C468" s="4"/>
+      <c r="D468" s="4"/>
+      <c r="E468" s="3"/>
+    </row>
+    <row r="469" spans="1:5">
+      <c r="A469" s="2"/>
+      <c r="B469" s="3"/>
+      <c r="C469" s="4"/>
+      <c r="D469" s="4"/>
+      <c r="E469" s="3"/>
+    </row>
+    <row r="470" spans="1:5">
+      <c r="A470" s="2"/>
+      <c r="B470" s="3"/>
+      <c r="C470" s="4"/>
+      <c r="D470" s="4"/>
+      <c r="E470" s="3"/>
+    </row>
+    <row r="471" spans="1:5">
+      <c r="A471" s="2"/>
+      <c r="B471" s="3"/>
+      <c r="C471" s="4"/>
+      <c r="D471" s="4"/>
+      <c r="E471" s="3"/>
+    </row>
+    <row r="472" spans="1:5">
+      <c r="A472" s="2"/>
+      <c r="B472" s="3"/>
+      <c r="C472" s="4"/>
+      <c r="D472" s="4"/>
+      <c r="E472" s="3"/>
+    </row>
+    <row r="473" spans="1:5">
+      <c r="A473" s="2"/>
+      <c r="B473" s="3"/>
+      <c r="C473" s="4"/>
+      <c r="D473" s="4"/>
+      <c r="E473" s="3"/>
+    </row>
+    <row r="474" spans="1:5">
+      <c r="A474" s="2"/>
+      <c r="B474" s="3"/>
+      <c r="C474" s="4"/>
+      <c r="D474" s="4"/>
+      <c r="E474" s="3"/>
+    </row>
+    <row r="475" spans="1:5">
+      <c r="A475" s="2"/>
+      <c r="B475" s="3"/>
+      <c r="C475" s="4"/>
+      <c r="D475" s="4"/>
+      <c r="E475" s="3"/>
+    </row>
+    <row r="476" spans="1:5">
+      <c r="A476" s="2"/>
+      <c r="B476" s="3"/>
+      <c r="C476" s="4"/>
+      <c r="D476" s="4"/>
+      <c r="E476" s="3"/>
+    </row>
+    <row r="477" spans="1:5">
+      <c r="A477" s="2"/>
+      <c r="B477" s="3"/>
+      <c r="C477" s="4"/>
+      <c r="D477" s="4"/>
+      <c r="E477" s="3"/>
+    </row>
+    <row r="478" spans="1:5">
+      <c r="A478" s="2"/>
+      <c r="B478" s="3"/>
+      <c r="C478" s="4"/>
+      <c r="D478" s="4"/>
+      <c r="E478" s="3"/>
+    </row>
+    <row r="479" spans="1:5">
+      <c r="A479" s="2"/>
+      <c r="B479" s="3"/>
+      <c r="C479" s="4"/>
+      <c r="D479" s="4"/>
+      <c r="E479" s="3"/>
+    </row>
+    <row r="480" spans="1:5">
+      <c r="A480" s="2"/>
+      <c r="B480" s="3"/>
+      <c r="C480" s="4"/>
+      <c r="D480" s="4"/>
+      <c r="E480" s="3"/>
+    </row>
+    <row r="481" spans="1:5">
+      <c r="A481" s="2"/>
+      <c r="B481" s="3"/>
+      <c r="C481" s="4"/>
+      <c r="D481" s="4"/>
+      <c r="E481" s="3"/>
+    </row>
+    <row r="482" spans="1:5">
+      <c r="A482" s="2"/>
+      <c r="B482" s="3"/>
+      <c r="C482" s="4"/>
+      <c r="D482" s="4"/>
+      <c r="E482" s="3"/>
+    </row>
+    <row r="483" spans="1:5">
+      <c r="A483" s="2"/>
+      <c r="B483" s="3"/>
+      <c r="C483" s="4"/>
+      <c r="D483" s="4"/>
+      <c r="E483" s="3"/>
+    </row>
+    <row r="484" spans="1:5">
+      <c r="A484" s="2"/>
+      <c r="B484" s="3"/>
+      <c r="C484" s="4"/>
+      <c r="D484" s="4"/>
+      <c r="E484" s="3"/>
+    </row>
+    <row r="485" spans="1:5">
+      <c r="A485" s="2"/>
+      <c r="B485" s="3"/>
+      <c r="C485" s="4"/>
+      <c r="D485" s="4"/>
+      <c r="E485" s="3"/>
+    </row>
+    <row r="486" spans="1:5">
+      <c r="A486" s="2"/>
+      <c r="B486" s="3"/>
+      <c r="C486" s="4"/>
+      <c r="D486" s="4"/>
+      <c r="E486" s="3"/>
+    </row>
+    <row r="487" spans="1:5">
+      <c r="A487" s="2"/>
+      <c r="B487" s="3"/>
+      <c r="C487" s="4"/>
+      <c r="D487" s="4"/>
+      <c r="E487" s="3"/>
+    </row>
+    <row r="488" spans="1:5">
+      <c r="A488" s="2"/>
+      <c r="B488" s="3"/>
+      <c r="C488" s="4"/>
+      <c r="D488" s="4"/>
+      <c r="E488" s="3"/>
+    </row>
+    <row r="489" spans="1:5">
+      <c r="A489" s="2"/>
+      <c r="B489" s="3"/>
+      <c r="C489" s="4"/>
+      <c r="D489" s="4"/>
+      <c r="E489" s="3"/>
+    </row>
+    <row r="490" spans="1:5">
+      <c r="A490" s="2"/>
+      <c r="B490" s="3"/>
+      <c r="C490" s="4"/>
+      <c r="D490" s="4"/>
+      <c r="E490" s="3"/>
+    </row>
+    <row r="491" spans="1:5">
+      <c r="A491" s="2"/>
+      <c r="B491" s="3"/>
+      <c r="C491" s="4"/>
+      <c r="D491" s="4"/>
+      <c r="E491" s="3"/>
+    </row>
+    <row r="492" spans="1:5">
+      <c r="A492" s="2"/>
+      <c r="B492" s="3"/>
+      <c r="C492" s="4"/>
+      <c r="D492" s="4"/>
+      <c r="E492" s="3"/>
+    </row>
+    <row r="493" spans="1:5">
+      <c r="A493" s="2"/>
+      <c r="B493" s="3"/>
+      <c r="C493" s="4"/>
+      <c r="D493" s="4"/>
+      <c r="E493" s="3"/>
+    </row>
+    <row r="494" spans="1:5">
+      <c r="A494" s="2"/>
+      <c r="B494" s="3"/>
+      <c r="C494" s="4"/>
+      <c r="D494" s="4"/>
+      <c r="E494" s="3"/>
+    </row>
+    <row r="495" spans="1:5">
+      <c r="A495" s="2"/>
+      <c r="B495" s="3"/>
+      <c r="C495" s="4"/>
+      <c r="D495" s="4"/>
+      <c r="E495" s="3"/>
+    </row>
+    <row r="496" spans="1:5">
+      <c r="A496" s="2"/>
+      <c r="B496" s="3"/>
+      <c r="C496" s="4"/>
+      <c r="D496" s="4"/>
+      <c r="E496" s="3"/>
+    </row>
+    <row r="497" spans="1:5">
+      <c r="A497" s="2"/>
+      <c r="B497" s="3"/>
+      <c r="C497" s="4"/>
+      <c r="D497" s="4"/>
+      <c r="E497" s="3"/>
+    </row>
+    <row r="498" spans="1:5">
+      <c r="A498" s="2"/>
+      <c r="B498" s="3"/>
+      <c r="C498" s="4"/>
+      <c r="D498" s="4"/>
+      <c r="E498" s="3"/>
+    </row>
+    <row r="499" spans="1:5">
+      <c r="A499" s="2"/>
+      <c r="B499" s="3"/>
+      <c r="C499" s="4"/>
+      <c r="D499" s="4"/>
+      <c r="E499" s="3"/>
+    </row>
+    <row r="500" spans="1:5">
+      <c r="A500" s="2"/>
+      <c r="B500" s="3"/>
+      <c r="C500" s="4"/>
+      <c r="D500" s="4"/>
+      <c r="E500" s="3"/>
+    </row>
+    <row r="501" spans="1:5">
+      <c r="A501" s="2"/>
+      <c r="B501" s="3"/>
+      <c r="C501" s="4"/>
+      <c r="D501" s="4"/>
+      <c r="E501" s="3"/>
+    </row>
+    <row r="502" spans="1:5">
+      <c r="A502" s="2"/>
+      <c r="B502" s="3"/>
+      <c r="C502" s="4"/>
+      <c r="D502" s="4"/>
+      <c r="E502" s="3"/>
+    </row>
+    <row r="503" spans="1:5">
+      <c r="A503" s="2"/>
+      <c r="B503" s="3"/>
+      <c r="C503" s="4"/>
+      <c r="D503" s="4"/>
+      <c r="E503" s="3"/>
+    </row>
+    <row r="504" spans="1:5">
+      <c r="A504" s="2"/>
+      <c r="B504" s="3"/>
+      <c r="C504" s="4"/>
+      <c r="D504" s="4"/>
+      <c r="E504" s="3"/>
+    </row>
+    <row r="505" spans="1:5">
+      <c r="A505" s="2"/>
+      <c r="B505" s="3"/>
+      <c r="C505" s="4"/>
+      <c r="D505" s="4"/>
+      <c r="E505" s="3"/>
+    </row>
+    <row r="506" spans="1:5">
+      <c r="A506" s="2"/>
+      <c r="B506" s="3"/>
+      <c r="C506" s="4"/>
+      <c r="D506" s="4"/>
+      <c r="E506" s="3"/>
+    </row>
+    <row r="507" spans="1:5">
+      <c r="A507" s="2"/>
+      <c r="B507" s="3"/>
+      <c r="C507" s="4"/>
+      <c r="D507" s="4"/>
+      <c r="E507" s="3"/>
+    </row>
+    <row r="508" spans="1:5">
+      <c r="A508" s="2"/>
+      <c r="B508" s="3"/>
+      <c r="C508" s="4"/>
+      <c r="D508" s="4"/>
+      <c r="E508" s="3"/>
+    </row>
+    <row r="509" spans="1:5">
+      <c r="A509" s="2"/>
+      <c r="B509" s="3"/>
+      <c r="C509" s="4"/>
+      <c r="D509" s="4"/>
+      <c r="E509" s="3"/>
+    </row>
+    <row r="510" spans="1:5">
+      <c r="A510" s="2"/>
+      <c r="B510" s="3"/>
+      <c r="C510" s="4"/>
+      <c r="D510" s="4"/>
+      <c r="E510" s="3"/>
+    </row>
+    <row r="511" spans="1:5">
+      <c r="A511" s="2"/>
+      <c r="B511" s="3"/>
+      <c r="C511" s="4"/>
+      <c r="D511" s="4"/>
+      <c r="E511" s="3"/>
+    </row>
+    <row r="512" spans="1:5">
+      <c r="A512" s="2"/>
+      <c r="B512" s="3"/>
+      <c r="C512" s="4"/>
+      <c r="D512" s="4"/>
+      <c r="E512" s="3"/>
+    </row>
+    <row r="513" spans="1:5">
+      <c r="A513" s="2"/>
+      <c r="B513" s="3"/>
+      <c r="C513" s="4"/>
+      <c r="D513" s="4"/>
+      <c r="E513" s="3"/>
+    </row>
+    <row r="514" spans="1:5">
+      <c r="A514" s="2"/>
+      <c r="B514" s="3"/>
+      <c r="C514" s="4"/>
+      <c r="D514" s="4"/>
+      <c r="E514" s="3"/>
+    </row>
+    <row r="515" spans="1:5">
+      <c r="A515" s="2"/>
+      <c r="B515" s="3"/>
+      <c r="C515" s="4"/>
+      <c r="D515" s="4"/>
+      <c r="E515" s="3"/>
+    </row>
+    <row r="516" spans="1:5">
+      <c r="A516" s="2"/>
+      <c r="B516" s="3"/>
+      <c r="C516" s="4"/>
+      <c r="D516" s="4"/>
+      <c r="E516" s="3"/>
+    </row>
+    <row r="517" spans="1:5">
+      <c r="A517" s="2"/>
+      <c r="B517" s="3"/>
+      <c r="C517" s="4"/>
+      <c r="D517" s="4"/>
+      <c r="E517" s="3"/>
+    </row>
+    <row r="518" spans="1:5">
+      <c r="A518" s="2"/>
+      <c r="B518" s="3"/>
+      <c r="C518" s="4"/>
+      <c r="D518" s="4"/>
+      <c r="E518" s="3"/>
+    </row>
+    <row r="519" spans="1:5">
+      <c r="A519" s="2"/>
+      <c r="B519" s="3"/>
+      <c r="C519" s="4"/>
+      <c r="D519" s="4"/>
+      <c r="E519" s="3"/>
+    </row>
+    <row r="520" spans="1:5">
+      <c r="A520" s="2"/>
+      <c r="B520" s="3"/>
+      <c r="C520" s="4"/>
+      <c r="D520" s="4"/>
+      <c r="E520" s="3"/>
+    </row>
+    <row r="521" spans="1:5">
+      <c r="A521" s="2"/>
+      <c r="B521" s="3"/>
+      <c r="C521" s="4"/>
+      <c r="D521" s="4"/>
+      <c r="E521" s="3"/>
+    </row>
+    <row r="522" spans="1:5">
+      <c r="A522" s="2"/>
+      <c r="B522" s="3"/>
+      <c r="C522" s="4"/>
+      <c r="D522" s="4"/>
+      <c r="E522" s="3"/>
+    </row>
+    <row r="523" spans="1:5">
+      <c r="A523" s="2"/>
+      <c r="B523" s="3"/>
+      <c r="C523" s="4"/>
+      <c r="D523" s="4"/>
+      <c r="E523" s="3"/>
+    </row>
+    <row r="524" spans="1:5">
+      <c r="A524" s="2"/>
+      <c r="B524" s="3"/>
+      <c r="C524" s="4"/>
+      <c r="D524" s="4"/>
+      <c r="E524" s="3"/>
+    </row>
+    <row r="525" spans="1:5">
+      <c r="A525" s="2"/>
+      <c r="B525" s="3"/>
+      <c r="C525" s="4"/>
+      <c r="D525" s="4"/>
+      <c r="E525" s="3"/>
+    </row>
+    <row r="526" spans="1:5">
+      <c r="A526" s="2"/>
+      <c r="B526" s="3"/>
+      <c r="C526" s="4"/>
+      <c r="D526" s="4"/>
+      <c r="E526" s="3"/>
+    </row>
+    <row r="527" spans="1:5">
+      <c r="A527" s="2"/>
+      <c r="B527" s="3"/>
+      <c r="C527" s="4"/>
+      <c r="D527" s="4"/>
+      <c r="E527" s="3"/>
+    </row>
+    <row r="528" spans="1:5">
+      <c r="A528" s="2"/>
+      <c r="B528" s="3"/>
+      <c r="C528" s="4"/>
+      <c r="D528" s="4"/>
+      <c r="E528" s="3"/>
+    </row>
+    <row r="529" spans="1:5">
+      <c r="A529" s="2"/>
+      <c r="B529" s="3"/>
+      <c r="C529" s="4"/>
+      <c r="D529" s="4"/>
+      <c r="E529" s="3"/>
+    </row>
+    <row r="530" spans="1:5">
+      <c r="A530" s="2"/>
+      <c r="B530" s="3"/>
+      <c r="C530" s="4"/>
+      <c r="D530" s="4"/>
+      <c r="E530" s="3"/>
+    </row>
+    <row r="531" spans="1:5">
+      <c r="A531" s="2"/>
+      <c r="B531" s="3"/>
+      <c r="C531" s="4"/>
+      <c r="D531" s="4"/>
+      <c r="E531" s="3"/>
+    </row>
+    <row r="532" spans="1:5">
+      <c r="A532" s="2"/>
+      <c r="B532" s="3"/>
+      <c r="C532" s="4"/>
+      <c r="D532" s="4"/>
+      <c r="E532" s="3"/>
+    </row>
+    <row r="533" spans="1:5">
+      <c r="A533" s="2"/>
+      <c r="B533" s="3"/>
+      <c r="C533" s="4"/>
+      <c r="D533" s="4"/>
+      <c r="E533" s="3"/>
+    </row>
+    <row r="534" spans="1:5">
+      <c r="A534" s="2"/>
+      <c r="B534" s="3"/>
+      <c r="C534" s="4"/>
+      <c r="D534" s="4"/>
+      <c r="E534" s="3"/>
+    </row>
+    <row r="535" spans="1:5">
+      <c r="A535" s="2"/>
+      <c r="B535" s="3"/>
+      <c r="C535" s="4"/>
+      <c r="D535" s="4"/>
+      <c r="E535" s="3"/>
+    </row>
+    <row r="536" spans="1:5">
+      <c r="A536" s="2"/>
+      <c r="B536" s="3"/>
+      <c r="C536" s="4"/>
+      <c r="D536" s="4"/>
+      <c r="E536" s="3"/>
+    </row>
+    <row r="537" spans="1:5">
+      <c r="A537" s="2"/>
+      <c r="B537" s="3"/>
+      <c r="C537" s="4"/>
+      <c r="D537" s="4"/>
+      <c r="E537" s="3"/>
+    </row>
+    <row r="538" spans="1:5">
+      <c r="A538" s="2"/>
+      <c r="B538" s="3"/>
+      <c r="C538" s="4"/>
+      <c r="D538" s="4"/>
+      <c r="E538" s="3"/>
+    </row>
+    <row r="539" spans="1:5">
+      <c r="A539" s="2"/>
+      <c r="B539" s="3"/>
+      <c r="C539" s="4"/>
+      <c r="D539" s="4"/>
+      <c r="E539" s="3"/>
+    </row>
+    <row r="540" spans="1:5">
+      <c r="A540" s="2"/>
+      <c r="B540" s="3"/>
+      <c r="C540" s="4"/>
+      <c r="D540" s="4"/>
+      <c r="E540" s="3"/>
+    </row>
+    <row r="541" spans="1:5">
+      <c r="A541" s="2"/>
+      <c r="B541" s="3"/>
+      <c r="C541" s="4"/>
+      <c r="D541" s="4"/>
+      <c r="E541" s="3"/>
+    </row>
+    <row r="542" spans="1:5">
+      <c r="A542" s="2"/>
+      <c r="B542" s="3"/>
+      <c r="C542" s="4"/>
+      <c r="D542" s="4"/>
+      <c r="E542" s="3"/>
+    </row>
+    <row r="543" spans="1:5">
+      <c r="A543" s="2"/>
+      <c r="B543" s="3"/>
+      <c r="C543" s="4"/>
+      <c r="D543" s="4"/>
+      <c r="E543" s="3"/>
+    </row>
+    <row r="544" spans="1:5">
+      <c r="A544" s="2"/>
+      <c r="B544" s="3"/>
+      <c r="C544" s="4"/>
+      <c r="D544" s="4"/>
+      <c r="E544" s="3"/>
+    </row>
+    <row r="545" spans="1:5">
+      <c r="A545" s="2"/>
+      <c r="B545" s="3"/>
+      <c r="C545" s="4"/>
+      <c r="D545" s="4"/>
+      <c r="E545" s="3"/>
+    </row>
+    <row r="546" spans="1:5">
+      <c r="A546" s="2"/>
+      <c r="B546" s="3"/>
+      <c r="C546" s="4"/>
+      <c r="D546" s="4"/>
+      <c r="E546" s="3"/>
+    </row>
+    <row r="547" spans="1:5">
+      <c r="A547" s="2"/>
+      <c r="B547" s="3"/>
+      <c r="C547" s="4"/>
+      <c r="D547" s="4"/>
+      <c r="E547" s="3"/>
+    </row>
+    <row r="548" spans="1:5">
+      <c r="A548" s="2"/>
+      <c r="B548" s="3"/>
+      <c r="C548" s="4"/>
+      <c r="D548" s="4"/>
+      <c r="E548" s="3"/>
+    </row>
+    <row r="549" spans="1:5">
+      <c r="A549" s="2"/>
+      <c r="B549" s="3"/>
+      <c r="C549" s="4"/>
+      <c r="D549" s="4"/>
+      <c r="E549" s="3"/>
+    </row>
+    <row r="550" spans="1:5">
+      <c r="A550" s="2"/>
+      <c r="B550" s="3"/>
+      <c r="C550" s="4"/>
+      <c r="D550" s="4"/>
+      <c r="E550" s="3"/>
+    </row>
+    <row r="551" spans="1:5">
+      <c r="A551" s="2"/>
+      <c r="B551" s="3"/>
+      <c r="C551" s="4"/>
+      <c r="D551" s="4"/>
+      <c r="E551" s="3"/>
+    </row>
+    <row r="552" spans="1:5">
+      <c r="A552" s="2"/>
+      <c r="B552" s="3"/>
+      <c r="C552" s="4"/>
+      <c r="D552" s="4"/>
+      <c r="E552" s="3"/>
+    </row>
+    <row r="553" spans="1:5">
+      <c r="A553" s="2"/>
+      <c r="B553" s="3"/>
+      <c r="C553" s="4"/>
+      <c r="D553" s="4"/>
+      <c r="E553" s="3"/>
+    </row>
+    <row r="554" spans="1:5">
+      <c r="A554" s="2"/>
+      <c r="B554" s="3"/>
+      <c r="C554" s="4"/>
+      <c r="D554" s="4"/>
+      <c r="E554" s="3"/>
+    </row>
+    <row r="555" spans="1:5">
+      <c r="A555" s="2"/>
+      <c r="B555" s="3"/>
+      <c r="C555" s="4"/>
+      <c r="D555" s="4"/>
+      <c r="E555" s="3"/>
+    </row>
+    <row r="556" spans="1:5">
+      <c r="A556" s="2"/>
+      <c r="B556" s="3"/>
+      <c r="C556" s="4"/>
+      <c r="D556" s="4"/>
+      <c r="E556" s="3"/>
+    </row>
+    <row r="557" spans="1:5">
+      <c r="A557" s="2"/>
+      <c r="B557" s="3"/>
+      <c r="C557" s="4"/>
+      <c r="D557" s="4"/>
+      <c r="E557" s="3"/>
+    </row>
+    <row r="558" spans="1:5">
+      <c r="A558" s="2"/>
+      <c r="B558" s="3"/>
+      <c r="C558" s="4"/>
+      <c r="D558" s="4"/>
+      <c r="E558" s="3"/>
+    </row>
+    <row r="559" spans="1:5">
+      <c r="A559" s="2"/>
+      <c r="B559" s="3"/>
+      <c r="C559" s="4"/>
+      <c r="D559" s="4"/>
+      <c r="E559" s="3"/>
+    </row>
+    <row r="560" spans="1:5">
+      <c r="A560" s="2"/>
+      <c r="B560" s="3"/>
+      <c r="C560" s="4"/>
+      <c r="D560" s="4"/>
+      <c r="E560" s="3"/>
+    </row>
+    <row r="561" spans="1:5">
+      <c r="A561" s="2"/>
+      <c r="B561" s="3"/>
+      <c r="C561" s="4"/>
+      <c r="D561" s="4"/>
+      <c r="E561" s="3"/>
+    </row>
+    <row r="562" spans="1:5">
+      <c r="A562" s="2"/>
+      <c r="B562" s="3"/>
+      <c r="C562" s="4"/>
+      <c r="D562" s="4"/>
+      <c r="E562" s="3"/>
+    </row>
+    <row r="563" spans="1:5">
+      <c r="A563" s="2"/>
+      <c r="B563" s="3"/>
+      <c r="C563" s="4"/>
+      <c r="D563" s="4"/>
+      <c r="E563" s="3"/>
+    </row>
+    <row r="564" spans="1:5">
+      <c r="A564" s="2"/>
+      <c r="B564" s="3"/>
+      <c r="C564" s="4"/>
+      <c r="D564" s="4"/>
+      <c r="E564" s="3"/>
+    </row>
+    <row r="565" spans="1:5">
+      <c r="A565" s="2"/>
+      <c r="B565" s="3"/>
+      <c r="C565" s="4"/>
+      <c r="D565" s="4"/>
+      <c r="E565" s="3"/>
+    </row>
+    <row r="566" spans="1:5">
+      <c r="A566" s="2"/>
+      <c r="B566" s="3"/>
+      <c r="C566" s="4"/>
+      <c r="D566" s="4"/>
+      <c r="E566" s="3"/>
+    </row>
+    <row r="567" spans="1:5">
+      <c r="A567" s="2"/>
+      <c r="B567" s="3"/>
+      <c r="C567" s="4"/>
+      <c r="D567" s="4"/>
+      <c r="E567" s="3"/>
+    </row>
+    <row r="568" spans="1:5">
+      <c r="A568" s="2"/>
+      <c r="B568" s="3"/>
+      <c r="C568" s="4"/>
+      <c r="D568" s="4"/>
+      <c r="E568" s="3"/>
+    </row>
+    <row r="569" spans="1:5">
+      <c r="A569" s="2"/>
+      <c r="B569" s="3"/>
+      <c r="C569" s="4"/>
+      <c r="D569" s="4"/>
+      <c r="E569" s="3"/>
+    </row>
+    <row r="570" spans="1:5">
+      <c r="A570" s="2"/>
+      <c r="B570" s="3"/>
+      <c r="C570" s="4"/>
+      <c r="D570" s="4"/>
+      <c r="E570" s="3"/>
+    </row>
+    <row r="571" spans="1:5">
+      <c r="A571" s="2"/>
+      <c r="B571" s="3"/>
+      <c r="C571" s="4"/>
+      <c r="D571" s="4"/>
+      <c r="E571" s="3"/>
+    </row>
+    <row r="572" spans="1:5">
+      <c r="A572" s="2"/>
+      <c r="B572" s="3"/>
+      <c r="C572" s="4"/>
+      <c r="D572" s="4"/>
+      <c r="E572" s="3"/>
+    </row>
+    <row r="573" spans="1:5">
+      <c r="A573" s="2"/>
+      <c r="B573" s="3"/>
+      <c r="C573" s="4"/>
+      <c r="D573" s="4"/>
+      <c r="E573" s="3"/>
+    </row>
+    <row r="574" spans="1:5">
+      <c r="A574" s="2"/>
+      <c r="B574" s="3"/>
+      <c r="C574" s="4"/>
+      <c r="D574" s="4"/>
+      <c r="E574" s="3"/>
+    </row>
+    <row r="575" spans="1:5">
+      <c r="A575" s="2"/>
+      <c r="B575" s="3"/>
+      <c r="C575" s="4"/>
+      <c r="D575" s="4"/>
+      <c r="E575" s="3"/>
+    </row>
+    <row r="576" spans="1:5">
+      <c r="A576" s="2"/>
+      <c r="B576" s="3"/>
+      <c r="C576" s="4"/>
+      <c r="D576" s="4"/>
+      <c r="E576" s="3"/>
+    </row>
+    <row r="577" spans="1:5">
+      <c r="A577" s="2"/>
+      <c r="B577" s="3"/>
+      <c r="C577" s="4"/>
+      <c r="D577" s="4"/>
+      <c r="E577" s="3"/>
+    </row>
+    <row r="578" spans="1:5">
+      <c r="A578" s="2"/>
+      <c r="B578" s="3"/>
+      <c r="C578" s="4"/>
+      <c r="D578" s="4"/>
+      <c r="E578" s="3"/>
+    </row>
+    <row r="579" spans="1:5">
+      <c r="A579" s="2"/>
+      <c r="B579" s="3"/>
+      <c r="C579" s="4"/>
+      <c r="D579" s="4"/>
+      <c r="E579" s="3"/>
+    </row>
+    <row r="580" spans="1:5">
+      <c r="A580" s="2"/>
+      <c r="B580" s="3"/>
+      <c r="C580" s="4"/>
+      <c r="D580" s="4"/>
+      <c r="E580" s="3"/>
+    </row>
+    <row r="581" spans="1:5">
+      <c r="A581" s="2"/>
+      <c r="B581" s="3"/>
+      <c r="C581" s="4"/>
+      <c r="D581" s="4"/>
+      <c r="E581" s="3"/>
+    </row>
+    <row r="582" spans="1:5">
+      <c r="A582" s="2"/>
+      <c r="B582" s="3"/>
+      <c r="C582" s="4"/>
+      <c r="D582" s="4"/>
+      <c r="E582" s="3"/>
+    </row>
+    <row r="583" spans="1:5">
+      <c r="A583" s="2"/>
+      <c r="B583" s="3"/>
+      <c r="C583" s="4"/>
+      <c r="D583" s="4"/>
+      <c r="E583" s="3"/>
+    </row>
+    <row r="584" spans="1:5">
+      <c r="A584" s="2"/>
+      <c r="B584" s="3"/>
+      <c r="C584" s="4"/>
+      <c r="D584" s="4"/>
+      <c r="E584" s="3"/>
+    </row>
+    <row r="585" spans="1:5">
+      <c r="A585" s="2"/>
+      <c r="B585" s="3"/>
+      <c r="C585" s="4"/>
+      <c r="D585" s="4"/>
+      <c r="E585" s="3"/>
+    </row>
+    <row r="586" spans="1:5">
+      <c r="A586" s="2"/>
+      <c r="B586" s="3"/>
+      <c r="C586" s="4"/>
+      <c r="D586" s="4"/>
+      <c r="E586" s="3"/>
+    </row>
+    <row r="587" spans="1:5">
+      <c r="A587" s="2"/>
+      <c r="B587" s="3"/>
+      <c r="C587" s="4"/>
+      <c r="D587" s="4"/>
+      <c r="E587" s="3"/>
+    </row>
+    <row r="588" spans="1:5">
+      <c r="A588" s="2"/>
+      <c r="B588" s="3"/>
+      <c r="C588" s="4"/>
+      <c r="D588" s="4"/>
+      <c r="E588" s="3"/>
+    </row>
+    <row r="589" spans="1:5">
+      <c r="A589" s="2"/>
+      <c r="B589" s="3"/>
+      <c r="C589" s="4"/>
+      <c r="D589" s="4"/>
+      <c r="E589" s="3"/>
+    </row>
+    <row r="590" spans="1:5">
+      <c r="A590" s="2"/>
+      <c r="B590" s="3"/>
+      <c r="C590" s="4"/>
+      <c r="D590" s="4"/>
+      <c r="E590" s="3"/>
+    </row>
+    <row r="591" spans="1:5">
+      <c r="A591" s="2"/>
+      <c r="B591" s="3"/>
+      <c r="C591" s="4"/>
+      <c r="D591" s="4"/>
+      <c r="E591" s="3"/>
+    </row>
+    <row r="592" spans="1:5">
+      <c r="A592" s="2"/>
+      <c r="B592" s="3"/>
+      <c r="C592" s="4"/>
+      <c r="D592" s="4"/>
+      <c r="E592" s="3"/>
+    </row>
+    <row r="593" spans="1:5">
+      <c r="A593" s="2"/>
+      <c r="B593" s="3"/>
+      <c r="C593" s="4"/>
+      <c r="D593" s="4"/>
+      <c r="E593" s="3"/>
+    </row>
+    <row r="594" spans="1:5">
+      <c r="A594" s="2"/>
+      <c r="B594" s="3"/>
+      <c r="C594" s="4"/>
+      <c r="D594" s="4"/>
+      <c r="E594" s="3"/>
+    </row>
+    <row r="595" spans="1:5">
+      <c r="A595" s="2"/>
+      <c r="B595" s="3"/>
+      <c r="C595" s="4"/>
+      <c r="D595" s="4"/>
+      <c r="E595" s="3"/>
+    </row>
+    <row r="596" spans="1:5">
+      <c r="A596" s="2"/>
+      <c r="B596" s="3"/>
+      <c r="C596" s="4"/>
+      <c r="D596" s="4"/>
+      <c r="E596" s="3"/>
+    </row>
+    <row r="597" spans="1:5">
+      <c r="A597" s="2"/>
+      <c r="B597" s="3"/>
+      <c r="C597" s="4"/>
+      <c r="D597" s="4"/>
+      <c r="E597" s="3"/>
+    </row>
+    <row r="598" spans="1:5">
+      <c r="A598" s="2"/>
+      <c r="B598" s="3"/>
+      <c r="C598" s="4"/>
+      <c r="D598" s="4"/>
+      <c r="E598" s="3"/>
+    </row>
+    <row r="599" spans="1:5">
+      <c r="A599" s="2"/>
+      <c r="B599" s="3"/>
+      <c r="C599" s="4"/>
+      <c r="D599" s="4"/>
+      <c r="E599" s="3"/>
+    </row>
+    <row r="600" spans="1:5">
+      <c r="A600" s="2"/>
+      <c r="B600" s="3"/>
+      <c r="C600" s="4"/>
+      <c r="D600" s="4"/>
+      <c r="E600" s="3"/>
+    </row>
+    <row r="601" spans="1:5">
+      <c r="A601" s="2"/>
+      <c r="B601" s="3"/>
+      <c r="C601" s="4"/>
+      <c r="D601" s="4"/>
+      <c r="E601" s="3"/>
+    </row>
+    <row r="602" spans="1:5">
+      <c r="A602" s="2"/>
+      <c r="B602" s="3"/>
+      <c r="C602" s="4"/>
+      <c r="D602" s="4"/>
+      <c r="E602" s="3"/>
+    </row>
+    <row r="603" spans="1:5">
+      <c r="A603" s="2"/>
+      <c r="B603" s="3"/>
+      <c r="C603" s="4"/>
+      <c r="D603" s="4"/>
+      <c r="E603" s="3"/>
+    </row>
+    <row r="604" spans="1:5">
+      <c r="A604" s="2"/>
+      <c r="B604" s="3"/>
+      <c r="C604" s="4"/>
+      <c r="D604" s="4"/>
+      <c r="E604" s="3"/>
+    </row>
+    <row r="605" spans="1:5">
+      <c r="A605" s="2"/>
+      <c r="B605" s="3"/>
+      <c r="C605" s="4"/>
+      <c r="D605" s="4"/>
+      <c r="E605" s="3"/>
+    </row>
+    <row r="606" spans="1:5">
+      <c r="A606" s="2"/>
+      <c r="B606" s="3"/>
+      <c r="C606" s="4"/>
+      <c r="D606" s="4"/>
+      <c r="E606" s="3"/>
+    </row>
+    <row r="607" spans="1:5">
+      <c r="A607" s="2"/>
+      <c r="B607" s="3"/>
+      <c r="C607" s="4"/>
+      <c r="D607" s="4"/>
+      <c r="E607" s="3"/>
+    </row>
+    <row r="608" spans="1:5">
+      <c r="A608" s="2"/>
+      <c r="B608" s="3"/>
+      <c r="C608" s="4"/>
+      <c r="D608" s="4"/>
+      <c r="E608" s="3"/>
+    </row>
+    <row r="609" spans="1:5">
+      <c r="A609" s="2"/>
+      <c r="B609" s="3"/>
+      <c r="C609" s="4"/>
+      <c r="D609" s="4"/>
+      <c r="E609" s="3"/>
+    </row>
+    <row r="610" spans="1:5">
+      <c r="A610" s="2"/>
+      <c r="B610" s="3"/>
+      <c r="C610" s="4"/>
+      <c r="D610" s="4"/>
+      <c r="E610" s="3"/>
+    </row>
+    <row r="611" spans="1:5">
+      <c r="A611" s="2"/>
+      <c r="B611" s="3"/>
+      <c r="C611" s="4"/>
+      <c r="D611" s="4"/>
+      <c r="E611" s="3"/>
+    </row>
+    <row r="612" spans="1:5">
+      <c r="A612" s="2"/>
+      <c r="B612" s="3"/>
+      <c r="C612" s="4"/>
+      <c r="D612" s="4"/>
+      <c r="E612" s="3"/>
+    </row>
+    <row r="613" spans="1:5">
+      <c r="A613" s="2"/>
+      <c r="B613" s="3"/>
+      <c r="C613" s="4"/>
+      <c r="D613" s="4"/>
+      <c r="E613" s="3"/>
+    </row>
+    <row r="614" spans="1:5">
+      <c r="A614" s="2"/>
+      <c r="B614" s="3"/>
+      <c r="C614" s="4"/>
+      <c r="D614" s="4"/>
+      <c r="E614" s="3"/>
+    </row>
+    <row r="615" spans="1:5">
+      <c r="A615" s="2"/>
+      <c r="B615" s="3"/>
+      <c r="C615" s="4"/>
+      <c r="D615" s="4"/>
+      <c r="E615" s="3"/>
+    </row>
+    <row r="616" spans="1:5">
+      <c r="A616" s="2"/>
+      <c r="B616" s="3"/>
+      <c r="C616" s="4"/>
+      <c r="D616" s="4"/>
+      <c r="E616" s="3"/>
+    </row>
+    <row r="617" spans="1:5">
+      <c r="A617" s="2"/>
+      <c r="B617" s="3"/>
+      <c r="C617" s="4"/>
+      <c r="D617" s="4"/>
+      <c r="E617" s="3"/>
+    </row>
+    <row r="618" spans="1:5">
+      <c r="A618" s="2"/>
+      <c r="B618" s="3"/>
+      <c r="C618" s="4"/>
+      <c r="D618" s="4"/>
+      <c r="E618" s="3"/>
+    </row>
+    <row r="619" spans="1:5">
+      <c r="A619" s="2"/>
+      <c r="B619" s="3"/>
+      <c r="C619" s="4"/>
+      <c r="D619" s="4"/>
+      <c r="E619" s="3"/>
+    </row>
+    <row r="620" spans="1:5">
+      <c r="A620" s="2"/>
+      <c r="B620" s="3"/>
+      <c r="C620" s="4"/>
+      <c r="D620" s="4"/>
+      <c r="E620" s="3"/>
+    </row>
+    <row r="621" spans="1:5">
+      <c r="A621" s="2"/>
+      <c r="B621" s="3"/>
+      <c r="C621" s="4"/>
+      <c r="D621" s="4"/>
+      <c r="E621" s="3"/>
+    </row>
+    <row r="622" spans="1:5">
+      <c r="A622" s="2"/>
+      <c r="B622" s="3"/>
+      <c r="C622" s="4"/>
+      <c r="D622" s="4"/>
+      <c r="E622" s="3"/>
+    </row>
+    <row r="623" spans="1:5">
+      <c r="A623" s="2"/>
+      <c r="B623" s="3"/>
+      <c r="C623" s="4"/>
+      <c r="D623" s="4"/>
+      <c r="E623" s="3"/>
+    </row>
+    <row r="624" spans="1:5">
+      <c r="A624" s="2"/>
+      <c r="B624" s="3"/>
+      <c r="C624" s="4"/>
+      <c r="D624" s="4"/>
+      <c r="E624" s="3"/>
+    </row>
+    <row r="625" spans="1:5">
+      <c r="A625" s="2"/>
+      <c r="B625" s="3"/>
+      <c r="C625" s="4"/>
+      <c r="D625" s="4"/>
+      <c r="E625" s="3"/>
+    </row>
+    <row r="626" spans="1:5">
+      <c r="A626" s="2"/>
+      <c r="B626" s="3"/>
+      <c r="C626" s="4"/>
+      <c r="D626" s="4"/>
+      <c r="E626" s="3"/>
+    </row>
+    <row r="627" spans="1:5">
+      <c r="A627" s="2"/>
+      <c r="B627" s="3"/>
+      <c r="C627" s="4"/>
+      <c r="D627" s="4"/>
+      <c r="E627" s="3"/>
+    </row>
+    <row r="628" spans="1:5">
+      <c r="A628" s="2"/>
+      <c r="B628" s="3"/>
+      <c r="C628" s="4"/>
+      <c r="D628" s="4"/>
+      <c r="E628" s="3"/>
+    </row>
+    <row r="629" spans="1:5">
+      <c r="A629" s="2"/>
+      <c r="B629" s="3"/>
+      <c r="C629" s="4"/>
+      <c r="D629" s="4"/>
+      <c r="E629" s="3"/>
+    </row>
+    <row r="630" spans="1:5">
+      <c r="A630" s="2"/>
+      <c r="B630" s="3"/>
+      <c r="C630" s="4"/>
+      <c r="D630" s="4"/>
+      <c r="E630" s="3"/>
+    </row>
+    <row r="631" spans="1:5">
+      <c r="A631" s="2"/>
+      <c r="B631" s="3"/>
+      <c r="C631" s="4"/>
+      <c r="D631" s="4"/>
+      <c r="E631" s="3"/>
+    </row>
+    <row r="632" spans="1:5">
+      <c r="A632" s="2"/>
+      <c r="B632" s="3"/>
+      <c r="C632" s="4"/>
+      <c r="D632" s="4"/>
+      <c r="E632" s="3"/>
+    </row>
+    <row r="633" spans="1:5">
+      <c r="A633" s="2"/>
+      <c r="B633" s="3"/>
+      <c r="C633" s="4"/>
+      <c r="D633" s="4"/>
+      <c r="E633" s="3"/>
+    </row>
+    <row r="634" spans="1:5">
+      <c r="A634" s="2"/>
+      <c r="B634" s="3"/>
+      <c r="C634" s="4"/>
+      <c r="D634" s="4"/>
+      <c r="E634" s="3"/>
+    </row>
+    <row r="635" spans="1:5">
+      <c r="A635" s="2"/>
+      <c r="B635" s="3"/>
+      <c r="C635" s="4"/>
+      <c r="D635" s="4"/>
+      <c r="E635" s="3"/>
+    </row>
+    <row r="636" spans="1:5">
+      <c r="A636" s="2"/>
+      <c r="B636" s="3"/>
+      <c r="C636" s="4"/>
+      <c r="D636" s="4"/>
+      <c r="E636" s="3"/>
+    </row>
+    <row r="637" spans="1:5">
+      <c r="A637" s="2"/>
+      <c r="B637" s="3"/>
+      <c r="C637" s="4"/>
+      <c r="D637" s="4"/>
+      <c r="E637" s="3"/>
+    </row>
+    <row r="638" spans="1:5">
+      <c r="A638" s="2"/>
+      <c r="B638" s="3"/>
+      <c r="C638" s="4"/>
+      <c r="D638" s="4"/>
+      <c r="E638" s="3"/>
+    </row>
+    <row r="639" spans="1:5">
+      <c r="A639" s="2"/>
+      <c r="B639" s="3"/>
+      <c r="C639" s="4"/>
+      <c r="D639" s="4"/>
+      <c r="E639" s="3"/>
+    </row>
+    <row r="640" spans="1:5">
+      <c r="A640" s="2"/>
+      <c r="B640" s="3"/>
+      <c r="C640" s="4"/>
+      <c r="D640" s="4"/>
+      <c r="E640" s="3"/>
+    </row>
+    <row r="641" spans="1:5">
+      <c r="A641" s="2"/>
+      <c r="B641" s="3"/>
+      <c r="C641" s="4"/>
+      <c r="D641" s="4"/>
+      <c r="E641" s="3"/>
+    </row>
+    <row r="642" spans="1:5">
+      <c r="A642" s="2"/>
+      <c r="B642" s="3"/>
+      <c r="C642" s="4"/>
+      <c r="D642" s="4"/>
+      <c r="E642" s="3"/>
+    </row>
+    <row r="643" spans="1:5">
+      <c r="A643" s="2"/>
+      <c r="B643" s="3"/>
+      <c r="C643" s="4"/>
+      <c r="D643" s="4"/>
+      <c r="E643" s="3"/>
+    </row>
+    <row r="644" spans="1:5">
+      <c r="A644" s="2"/>
+      <c r="B644" s="3"/>
+      <c r="C644" s="4"/>
+      <c r="D644" s="4"/>
+      <c r="E644" s="3"/>
+    </row>
+    <row r="645" spans="1:5">
+      <c r="A645" s="2"/>
+      <c r="B645" s="3"/>
+      <c r="C645" s="4"/>
+      <c r="D645" s="4"/>
+      <c r="E645" s="3"/>
+    </row>
+    <row r="646" spans="1:5">
+      <c r="A646" s="2"/>
+      <c r="B646" s="3"/>
+      <c r="C646" s="4"/>
+      <c r="D646" s="4"/>
+      <c r="E646" s="3"/>
+    </row>
+    <row r="647" spans="1:5">
+      <c r="A647" s="2"/>
+      <c r="B647" s="3"/>
+      <c r="C647" s="4"/>
+      <c r="D647" s="4"/>
+      <c r="E647" s="3"/>
+    </row>
+    <row r="648" spans="1:5">
+      <c r="A648" s="2"/>
+      <c r="B648" s="3"/>
+      <c r="C648" s="4"/>
+      <c r="D648" s="4"/>
+      <c r="E648" s="3"/>
+    </row>
+    <row r="649" spans="1:5">
+      <c r="A649" s="2"/>
+      <c r="B649" s="3"/>
+      <c r="C649" s="4"/>
+      <c r="D649" s="4"/>
+      <c r="E649" s="3"/>
+    </row>
+    <row r="650" spans="1:5">
+      <c r="A650" s="2"/>
+      <c r="B650" s="3"/>
+      <c r="C650" s="4"/>
+      <c r="D650" s="4"/>
+      <c r="E650" s="3"/>
+    </row>
+    <row r="651" spans="1:5">
+      <c r="A651" s="2"/>
+      <c r="B651" s="3"/>
+      <c r="C651" s="4"/>
+      <c r="D651" s="4"/>
+      <c r="E651" s="3"/>
+    </row>
+    <row r="652" spans="1:5">
+      <c r="A652" s="2"/>
+      <c r="B652" s="3"/>
+      <c r="C652" s="4"/>
+      <c r="D652" s="4"/>
+      <c r="E652" s="3"/>
+    </row>
+    <row r="653" spans="1:5">
+      <c r="A653" s="2"/>
+      <c r="B653" s="3"/>
+      <c r="C653" s="4"/>
+      <c r="D653" s="4"/>
+      <c r="E653" s="3"/>
+    </row>
+    <row r="654" spans="1:5">
+      <c r="A654" s="2"/>
+      <c r="B654" s="3"/>
+      <c r="C654" s="4"/>
+      <c r="D654" s="4"/>
+      <c r="E654" s="3"/>
+    </row>
+    <row r="655" spans="1:5">
+      <c r="A655" s="2"/>
+      <c r="B655" s="3"/>
+      <c r="C655" s="4"/>
+      <c r="D655" s="4"/>
+      <c r="E655" s="3"/>
+    </row>
+    <row r="656" spans="1:5">
+      <c r="A656" s="2"/>
+      <c r="B656" s="3"/>
+      <c r="C656" s="4"/>
+      <c r="D656" s="4"/>
+      <c r="E656" s="3"/>
+    </row>
+    <row r="657" spans="1:5">
+      <c r="A657" s="2"/>
+      <c r="B657" s="3"/>
+      <c r="C657" s="4"/>
+      <c r="D657" s="4"/>
+      <c r="E657" s="3"/>
+    </row>
+    <row r="658" spans="1:5">
+      <c r="A658" s="2"/>
+      <c r="B658" s="3"/>
+      <c r="C658" s="4"/>
+      <c r="D658" s="4"/>
+      <c r="E658" s="3"/>
+    </row>
+    <row r="659" spans="1:5">
+      <c r="A659" s="2"/>
+      <c r="B659" s="3"/>
+      <c r="C659" s="4"/>
+      <c r="D659" s="4"/>
+      <c r="E659" s="3"/>
+    </row>
+    <row r="660" spans="1:5">
+      <c r="A660" s="2"/>
+      <c r="B660" s="3"/>
+      <c r="C660" s="4"/>
+      <c r="D660" s="4"/>
+      <c r="E660" s="3"/>
+    </row>
+    <row r="661" spans="1:5">
+      <c r="A661" s="2"/>
+      <c r="B661" s="3"/>
+      <c r="C661" s="4"/>
+      <c r="D661" s="4"/>
+      <c r="E661" s="3"/>
+    </row>
+    <row r="662" spans="1:5">
+      <c r="A662" s="2"/>
+      <c r="B662" s="3"/>
+      <c r="C662" s="4"/>
+      <c r="D662" s="4"/>
+      <c r="E662" s="3"/>
+    </row>
+    <row r="663" spans="1:5">
+      <c r="A663" s="2"/>
+      <c r="B663" s="3"/>
+      <c r="C663" s="4"/>
+      <c r="D663" s="4"/>
+      <c r="E663" s="3"/>
+    </row>
+    <row r="664" spans="1:5">
+      <c r="A664" s="2"/>
+      <c r="B664" s="3"/>
+      <c r="C664" s="4"/>
+      <c r="D664" s="4"/>
+      <c r="E664" s="3"/>
+    </row>
+    <row r="665" spans="1:5">
+      <c r="A665" s="2"/>
+      <c r="B665" s="3"/>
+      <c r="C665" s="4"/>
+      <c r="D665" s="4"/>
+      <c r="E665" s="3"/>
+    </row>
+    <row r="666" spans="1:5">
+      <c r="A666" s="2"/>
+      <c r="B666" s="3"/>
+      <c r="C666" s="4"/>
+      <c r="D666" s="4"/>
+      <c r="E666" s="3"/>
+    </row>
+    <row r="667" spans="1:5">
+      <c r="A667" s="2"/>
+      <c r="B667" s="3"/>
+      <c r="C667" s="4"/>
+      <c r="D667" s="4"/>
+      <c r="E667" s="3"/>
+    </row>
+    <row r="668" spans="1:5">
+      <c r="A668" s="2"/>
+      <c r="B668" s="3"/>
+      <c r="C668" s="4"/>
+      <c r="D668" s="4"/>
+      <c r="E668" s="3"/>
+    </row>
+    <row r="669" spans="1:5">
+      <c r="A669" s="2"/>
+      <c r="B669" s="3"/>
+      <c r="C669" s="4"/>
+      <c r="D669" s="4"/>
+      <c r="E669" s="3"/>
+    </row>
+    <row r="670" spans="1:5">
+      <c r="A670" s="2"/>
+      <c r="B670" s="3"/>
+      <c r="C670" s="4"/>
+      <c r="D670" s="4"/>
+      <c r="E670" s="3"/>
+    </row>
+    <row r="671" spans="1:5">
+      <c r="A671" s="2"/>
+      <c r="B671" s="3"/>
+      <c r="C671" s="4"/>
+      <c r="D671" s="4"/>
+      <c r="E671" s="3"/>
+    </row>
+    <row r="672" spans="1:5">
+      <c r="A672" s="2"/>
+      <c r="B672" s="3"/>
+      <c r="C672" s="4"/>
+      <c r="D672" s="4"/>
+      <c r="E672" s="3"/>
+    </row>
+    <row r="673" spans="1:5">
+      <c r="A673" s="2"/>
+      <c r="B673" s="3"/>
+      <c r="C673" s="4"/>
+      <c r="D673" s="4"/>
+      <c r="E673" s="3"/>
+    </row>
+    <row r="674" spans="1:5">
+      <c r="A674" s="2"/>
+      <c r="B674" s="3"/>
+      <c r="C674" s="4"/>
+      <c r="D674" s="4"/>
+      <c r="E674" s="3"/>
+    </row>
+    <row r="675" spans="1:5">
+      <c r="A675" s="2"/>
+      <c r="B675" s="3"/>
+      <c r="C675" s="4"/>
+      <c r="D675" s="4"/>
+      <c r="E675" s="3"/>
+    </row>
+    <row r="676" spans="1:5">
+      <c r="A676" s="2"/>
+      <c r="B676" s="3"/>
+      <c r="C676" s="4"/>
+      <c r="D676" s="4"/>
+      <c r="E676" s="3"/>
+    </row>
+    <row r="677" spans="1:5">
+      <c r="A677" s="2"/>
+      <c r="B677" s="3"/>
+      <c r="C677" s="4"/>
+      <c r="D677" s="4"/>
+      <c r="E677" s="3"/>
+    </row>
+    <row r="678" spans="1:5">
+      <c r="A678" s="2"/>
+      <c r="B678" s="3"/>
+      <c r="C678" s="4"/>
+      <c r="D678" s="4"/>
+      <c r="E678" s="3"/>
+    </row>
+    <row r="679" spans="1:5">
+      <c r="A679" s="2"/>
+      <c r="B679" s="3"/>
+      <c r="C679" s="4"/>
+      <c r="D679" s="4"/>
+      <c r="E679" s="3"/>
+    </row>
+    <row r="680" spans="1:5">
+      <c r="A680" s="2"/>
+      <c r="B680" s="3"/>
+      <c r="C680" s="4"/>
+      <c r="D680" s="4"/>
+      <c r="E680" s="3"/>
+    </row>
+    <row r="681" spans="1:5">
+      <c r="A681" s="2"/>
+      <c r="B681" s="3"/>
+      <c r="C681" s="4"/>
+      <c r="D681" s="4"/>
+      <c r="E681" s="3"/>
+    </row>
+    <row r="682" spans="1:5">
+      <c r="A682" s="2"/>
+      <c r="B682" s="3"/>
+      <c r="C682" s="4"/>
+      <c r="D682" s="4"/>
+      <c r="E682" s="3"/>
+    </row>
+    <row r="683" spans="1:5">
+      <c r="A683" s="2"/>
+      <c r="B683" s="3"/>
+      <c r="C683" s="4"/>
+      <c r="D683" s="4"/>
+      <c r="E683" s="3"/>
+    </row>
+    <row r="684" spans="1:5">
+      <c r="A684" s="2"/>
+      <c r="B684" s="3"/>
+      <c r="C684" s="4"/>
+      <c r="D684" s="4"/>
+      <c r="E684" s="3"/>
+    </row>
+    <row r="685" spans="1:5">
+      <c r="A685" s="2"/>
+      <c r="B685" s="3"/>
+      <c r="C685" s="4"/>
+      <c r="D685" s="4"/>
+      <c r="E685" s="3"/>
+    </row>
+    <row r="686" spans="1:5">
+      <c r="A686" s="2"/>
+      <c r="B686" s="3"/>
+      <c r="C686" s="4"/>
+      <c r="D686" s="4"/>
+      <c r="E686" s="3"/>
+    </row>
+    <row r="687" spans="1:5">
+      <c r="A687" s="2"/>
+      <c r="B687" s="3"/>
+      <c r="C687" s="4"/>
+      <c r="D687" s="4"/>
+      <c r="E687" s="3"/>
+    </row>
+    <row r="688" spans="1:5">
+      <c r="A688" s="2"/>
+      <c r="B688" s="3"/>
+      <c r="C688" s="4"/>
+      <c r="D688" s="4"/>
+      <c r="E688" s="3"/>
+    </row>
+    <row r="689" spans="1:5">
+      <c r="A689" s="2"/>
+      <c r="B689" s="3"/>
+      <c r="C689" s="4"/>
+      <c r="D689" s="4"/>
+      <c r="E689" s="3"/>
+    </row>
+    <row r="690" spans="1:5">
+      <c r="A690" s="2"/>
+      <c r="B690" s="3"/>
+      <c r="C690" s="4"/>
+      <c r="D690" s="4"/>
+      <c r="E690" s="3"/>
+    </row>
+    <row r="691" spans="1:5">
+      <c r="A691" s="2"/>
+      <c r="B691" s="3"/>
+      <c r="C691" s="4"/>
+      <c r="D691" s="4"/>
+      <c r="E691" s="3"/>
+    </row>
+    <row r="692" spans="1:5">
+      <c r="A692" s="2"/>
+      <c r="B692" s="3"/>
+      <c r="C692" s="4"/>
+      <c r="D692" s="4"/>
+      <c r="E692" s="3"/>
+    </row>
+    <row r="693" spans="1:5">
+      <c r="A693" s="2"/>
+      <c r="B693" s="3"/>
+      <c r="C693" s="4"/>
+      <c r="D693" s="4"/>
+      <c r="E693" s="3"/>
+    </row>
+    <row r="694" spans="1:5">
+      <c r="A694" s="2"/>
+      <c r="B694" s="3"/>
+      <c r="C694" s="4"/>
+      <c r="D694" s="4"/>
+      <c r="E694" s="3"/>
+    </row>
+    <row r="695" spans="1:5">
+      <c r="A695" s="2"/>
+      <c r="B695" s="3"/>
+      <c r="C695" s="4"/>
+      <c r="D695" s="4"/>
+      <c r="E695" s="3"/>
+    </row>
+    <row r="696" spans="1:5">
+      <c r="A696" s="2"/>
+      <c r="B696" s="3"/>
+      <c r="C696" s="4"/>
+      <c r="D696" s="4"/>
+      <c r="E696" s="3"/>
+    </row>
+    <row r="697" spans="1:5">
+      <c r="A697" s="2"/>
+      <c r="B697" s="3"/>
+      <c r="C697" s="4"/>
+      <c r="D697" s="4"/>
+      <c r="E697" s="3"/>
+    </row>
+    <row r="698" spans="1:5">
+      <c r="A698" s="2"/>
+      <c r="B698" s="3"/>
+      <c r="C698" s="4"/>
+      <c r="D698" s="4"/>
+      <c r="E698" s="3"/>
+    </row>
+    <row r="699" spans="1:5">
+      <c r="A699" s="2"/>
+      <c r="B699" s="3"/>
+      <c r="C699" s="4"/>
+      <c r="D699" s="4"/>
+      <c r="E699" s="3"/>
+    </row>
+    <row r="700" spans="1:5">
+      <c r="A700" s="2"/>
+      <c r="B700" s="3"/>
+      <c r="C700" s="4"/>
+      <c r="D700" s="4"/>
+      <c r="E700" s="3"/>
+    </row>
+    <row r="701" spans="1:5">
+      <c r="A701" s="2"/>
+      <c r="B701" s="3"/>
+      <c r="C701" s="4"/>
+      <c r="D701" s="4"/>
+      <c r="E701" s="3"/>
+    </row>
+    <row r="702" spans="1:5">
+      <c r="A702" s="2"/>
+      <c r="B702" s="3"/>
+      <c r="C702" s="4"/>
+      <c r="D702" s="4"/>
+      <c r="E702" s="3"/>
+    </row>
+    <row r="703" spans="1:5">
+      <c r="A703" s="2"/>
+      <c r="B703" s="3"/>
+      <c r="C703" s="4"/>
+      <c r="D703" s="4"/>
+      <c r="E703" s="3"/>
+    </row>
+    <row r="704" spans="1:5">
+      <c r="A704" s="2"/>
+      <c r="B704" s="3"/>
+      <c r="C704" s="4"/>
+      <c r="D704" s="4"/>
+      <c r="E704" s="3"/>
+    </row>
+    <row r="705" spans="1:5">
+      <c r="A705" s="2"/>
+      <c r="B705" s="3"/>
+      <c r="C705" s="4"/>
+      <c r="D705" s="4"/>
+      <c r="E705" s="3"/>
+    </row>
+    <row r="706" spans="1:5">
+      <c r="A706" s="2"/>
+      <c r="B706" s="3"/>
+      <c r="C706" s="4"/>
+      <c r="D706" s="4"/>
+      <c r="E706" s="3"/>
+    </row>
+    <row r="707" spans="1:5">
+      <c r="A707" s="2"/>
+      <c r="B707" s="3"/>
+      <c r="C707" s="4"/>
+      <c r="D707" s="4"/>
+      <c r="E707" s="3"/>
+    </row>
+    <row r="708" spans="1:5">
+      <c r="A708" s="2"/>
+      <c r="B708" s="3"/>
+      <c r="C708" s="4"/>
+      <c r="D708" s="4"/>
+      <c r="E708" s="3"/>
+    </row>
+    <row r="709" spans="1:5">
+      <c r="A709" s="2"/>
+      <c r="B709" s="3"/>
+      <c r="C709" s="4"/>
+      <c r="D709" s="4"/>
+      <c r="E709" s="3"/>
+    </row>
+    <row r="710" spans="1:5">
+      <c r="A710" s="2"/>
+      <c r="B710" s="3"/>
+      <c r="C710" s="4"/>
+      <c r="D710" s="4"/>
+      <c r="E710" s="3"/>
+    </row>
+    <row r="711" spans="1:5">
+      <c r="A711" s="2"/>
+      <c r="B711" s="3"/>
+      <c r="C711" s="4"/>
+      <c r="D711" s="4"/>
+      <c r="E711" s="3"/>
+    </row>
+    <row r="712" spans="1:5">
+      <c r="A712" s="2"/>
+      <c r="B712" s="3"/>
+      <c r="C712" s="4"/>
+      <c r="D712" s="4"/>
+      <c r="E712" s="3"/>
+    </row>
+    <row r="713" spans="1:5">
+      <c r="A713" s="2"/>
+      <c r="B713" s="3"/>
+      <c r="C713" s="4"/>
+      <c r="D713" s="4"/>
+      <c r="E713" s="3"/>
+    </row>
+    <row r="714" spans="1:5">
+      <c r="A714" s="2"/>
+      <c r="B714" s="3"/>
+      <c r="C714" s="4"/>
+      <c r="D714" s="4"/>
+      <c r="E714" s="3"/>
+    </row>
+    <row r="715" spans="1:5">
+      <c r="A715" s="2"/>
+      <c r="B715" s="3"/>
+      <c r="C715" s="4"/>
+      <c r="D715" s="4"/>
+      <c r="E715" s="3"/>
+    </row>
+    <row r="716" spans="1:5">
+      <c r="A716" s="2"/>
+      <c r="B716" s="3"/>
+      <c r="C716" s="4"/>
+      <c r="D716" s="4"/>
+      <c r="E716" s="3"/>
+    </row>
+    <row r="717" spans="1:5">
+      <c r="A717" s="2"/>
+      <c r="B717" s="3"/>
+      <c r="C717" s="4"/>
+      <c r="D717" s="4"/>
+      <c r="E717" s="3"/>
+    </row>
+    <row r="718" spans="1:5">
+      <c r="A718" s="2"/>
+      <c r="B718" s="3"/>
+      <c r="C718" s="4"/>
+      <c r="D718" s="4"/>
+      <c r="E718" s="3"/>
+    </row>
+    <row r="719" spans="1:5">
+      <c r="A719" s="2"/>
+      <c r="B719" s="3"/>
+      <c r="C719" s="4"/>
+      <c r="D719" s="4"/>
+      <c r="E719" s="3"/>
+    </row>
+    <row r="720" spans="1:5">
+      <c r="A720" s="2"/>
+      <c r="B720" s="3"/>
+      <c r="C720" s="4"/>
+      <c r="D720" s="4"/>
+      <c r="E720" s="3"/>
+    </row>
+    <row r="721" spans="1:5">
+      <c r="A721" s="2"/>
+      <c r="B721" s="3"/>
+      <c r="C721" s="4"/>
+      <c r="D721" s="4"/>
+      <c r="E721" s="3"/>
+    </row>
+    <row r="722" spans="1:5">
+      <c r="A722" s="2"/>
+      <c r="B722" s="3"/>
+      <c r="C722" s="4"/>
+      <c r="D722" s="4"/>
+      <c r="E722" s="3"/>
+    </row>
+    <row r="723" spans="1:5">
+      <c r="A723" s="2"/>
+      <c r="B723" s="3"/>
+      <c r="C723" s="4"/>
+      <c r="D723" s="4"/>
+      <c r="E723" s="3"/>
+    </row>
+    <row r="724" spans="1:5">
+      <c r="A724" s="2"/>
+      <c r="B724" s="3"/>
+      <c r="C724" s="4"/>
+      <c r="D724" s="4"/>
+      <c r="E724" s="3"/>
+    </row>
+    <row r="725" spans="1:5">
+      <c r="A725" s="2"/>
+      <c r="B725" s="3"/>
+      <c r="C725" s="4"/>
+      <c r="D725" s="4"/>
+      <c r="E725" s="3"/>
+    </row>
+    <row r="726" spans="1:5">
+      <c r="A726" s="2"/>
+      <c r="B726" s="3"/>
+      <c r="C726" s="4"/>
+      <c r="D726" s="4"/>
+      <c r="E726" s="3"/>
+    </row>
+    <row r="727" spans="1:5">
+      <c r="A727" s="2"/>
+      <c r="B727" s="3"/>
+      <c r="C727" s="4"/>
+      <c r="D727" s="4"/>
+      <c r="E727" s="3"/>
+    </row>
+    <row r="728" spans="1:5">
+      <c r="A728" s="2"/>
+      <c r="B728" s="3"/>
+      <c r="C728" s="4"/>
+      <c r="D728" s="4"/>
+      <c r="E728" s="3"/>
+    </row>
+    <row r="729" spans="1:5">
+      <c r="A729" s="2"/>
+      <c r="B729" s="3"/>
+      <c r="C729" s="4"/>
+      <c r="D729" s="4"/>
+      <c r="E729" s="3"/>
+    </row>
+    <row r="730" spans="1:5">
+      <c r="A730" s="2"/>
+      <c r="B730" s="3"/>
+      <c r="C730" s="4"/>
+      <c r="D730" s="4"/>
+      <c r="E730" s="3"/>
+    </row>
+    <row r="731" spans="1:5">
+      <c r="A731" s="2"/>
+      <c r="B731" s="3"/>
+      <c r="C731" s="4"/>
+      <c r="D731" s="4"/>
+      <c r="E731" s="3"/>
+    </row>
+    <row r="732" spans="1:5">
+      <c r="A732" s="2"/>
+      <c r="B732" s="3"/>
+      <c r="C732" s="4"/>
+      <c r="D732" s="4"/>
+      <c r="E732" s="3"/>
+    </row>
+    <row r="733" spans="1:5">
+      <c r="A733" s="2"/>
+      <c r="B733" s="3"/>
+      <c r="C733" s="4"/>
+      <c r="D733" s="4"/>
+      <c r="E733" s="3"/>
+    </row>
+    <row r="734" spans="1:5">
+      <c r="A734" s="2"/>
+      <c r="B734" s="3"/>
+      <c r="C734" s="4"/>
+      <c r="D734" s="4"/>
+      <c r="E734" s="3"/>
+    </row>
+    <row r="735" spans="1:5">
+      <c r="A735" s="2"/>
+      <c r="B735" s="3"/>
+      <c r="C735" s="4"/>
+      <c r="D735" s="4"/>
+      <c r="E735" s="3"/>
+    </row>
+    <row r="736" spans="1:5">
+      <c r="A736" s="2"/>
+      <c r="B736" s="3"/>
+      <c r="C736" s="4"/>
+      <c r="D736" s="4"/>
+      <c r="E736" s="3"/>
+    </row>
+    <row r="737" spans="1:5">
+      <c r="A737" s="2"/>
+      <c r="B737" s="3"/>
+      <c r="C737" s="4"/>
+      <c r="D737" s="4"/>
+      <c r="E737" s="3"/>
+    </row>
+    <row r="738" spans="1:5">
+      <c r="A738" s="2"/>
+      <c r="B738" s="3"/>
+      <c r="C738" s="4"/>
+      <c r="D738" s="4"/>
+      <c r="E738" s="3"/>
+    </row>
+    <row r="739" spans="1:5">
+      <c r="A739" s="2"/>
+      <c r="B739" s="3"/>
+      <c r="C739" s="4"/>
+      <c r="D739" s="4"/>
+      <c r="E739" s="3"/>
+    </row>
+    <row r="740" spans="1:5">
+      <c r="A740" s="2"/>
+      <c r="B740" s="3"/>
+      <c r="C740" s="4"/>
+      <c r="D740" s="4"/>
+      <c r="E740" s="3"/>
+    </row>
+    <row r="741" spans="1:5">
+      <c r="A741" s="2"/>
+      <c r="B741" s="3"/>
+      <c r="C741" s="4"/>
+      <c r="D741" s="4"/>
+      <c r="E741" s="3"/>
+    </row>
+    <row r="742" spans="1:5">
+      <c r="A742" s="2"/>
+      <c r="B742" s="3"/>
+      <c r="C742" s="4"/>
+      <c r="D742" s="4"/>
+      <c r="E742" s="3"/>
+    </row>
+    <row r="743" spans="1:5">
+      <c r="A743" s="2"/>
+      <c r="B743" s="3"/>
+      <c r="C743" s="4"/>
+      <c r="D743" s="4"/>
+      <c r="E743" s="3"/>
+    </row>
+    <row r="744" spans="1:5">
+      <c r="A744" s="2"/>
+      <c r="B744" s="3"/>
+      <c r="C744" s="4"/>
+      <c r="D744" s="4"/>
+      <c r="E744" s="3"/>
+    </row>
+    <row r="745" spans="1:5">
+      <c r="A745" s="2"/>
+      <c r="B745" s="3"/>
+      <c r="C745" s="4"/>
+      <c r="D745" s="4"/>
+      <c r="E745" s="3"/>
+    </row>
+    <row r="746" spans="1:5">
+      <c r="A746" s="2"/>
+      <c r="B746" s="3"/>
+      <c r="C746" s="4"/>
+      <c r="D746" s="4"/>
+      <c r="E746" s="3"/>
+    </row>
+    <row r="747" spans="1:5">
+      <c r="A747" s="2"/>
+      <c r="B747" s="3"/>
+      <c r="C747" s="4"/>
+      <c r="D747" s="4"/>
+      <c r="E747" s="3"/>
+    </row>
+    <row r="748" spans="1:5">
+      <c r="A748" s="2"/>
+      <c r="B748" s="3"/>
+      <c r="C748" s="4"/>
+      <c r="D748" s="4"/>
+      <c r="E748" s="3"/>
+    </row>
+    <row r="749" spans="1:5">
+      <c r="A749" s="2"/>
+      <c r="B749" s="3"/>
+      <c r="C749" s="4"/>
+      <c r="D749" s="4"/>
+      <c r="E749" s="3"/>
+    </row>
+    <row r="750" spans="1:5">
+      <c r="A750" s="2"/>
+      <c r="B750" s="3"/>
+      <c r="C750" s="4"/>
+      <c r="D750" s="4"/>
+      <c r="E750" s="3"/>
+    </row>
+    <row r="751" spans="1:5">
+      <c r="A751" s="2"/>
+      <c r="B751" s="3"/>
+      <c r="C751" s="4"/>
+      <c r="D751" s="4"/>
+      <c r="E751" s="3"/>
+    </row>
+    <row r="752" spans="1:5">
+      <c r="A752" s="2"/>
+      <c r="B752" s="3"/>
+      <c r="C752" s="4"/>
+      <c r="D752" s="4"/>
+      <c r="E752" s="3"/>
+    </row>
+    <row r="753" spans="1:5">
+      <c r="A753" s="2"/>
+      <c r="B753" s="3"/>
+      <c r="C753" s="4"/>
+      <c r="D753" s="4"/>
+      <c r="E753" s="3"/>
+    </row>
+    <row r="754" spans="1:5">
+      <c r="A754" s="2"/>
+      <c r="B754" s="3"/>
+      <c r="C754" s="4"/>
+      <c r="D754" s="4"/>
+      <c r="E754" s="3"/>
+    </row>
+    <row r="755" spans="1:5">
+      <c r="A755" s="2"/>
+      <c r="B755" s="3"/>
+      <c r="C755" s="4"/>
+      <c r="D755" s="4"/>
+      <c r="E755" s="3"/>
+    </row>
+    <row r="756" spans="1:5">
+      <c r="A756" s="2"/>
+      <c r="B756" s="3"/>
+      <c r="C756" s="4"/>
+      <c r="D756" s="4"/>
+      <c r="E756" s="3"/>
+    </row>
+    <row r="757" spans="1:5">
+      <c r="A757" s="2"/>
+      <c r="B757" s="3"/>
+      <c r="C757" s="4"/>
+      <c r="D757" s="4"/>
+      <c r="E757" s="3"/>
+    </row>
+    <row r="758" spans="1:5">
+      <c r="A758" s="2"/>
+      <c r="B758" s="3"/>
+      <c r="C758" s="4"/>
+      <c r="D758" s="4"/>
+      <c r="E758" s="3"/>
+    </row>
+    <row r="759" spans="1:5">
+      <c r="A759" s="2"/>
+      <c r="B759" s="3"/>
+      <c r="C759" s="4"/>
+      <c r="D759" s="4"/>
+      <c r="E759" s="3"/>
+    </row>
+    <row r="760" spans="1:5">
+      <c r="A760" s="2"/>
+      <c r="B760" s="3"/>
+      <c r="C760" s="4"/>
+      <c r="D760" s="4"/>
+      <c r="E760" s="3"/>
+    </row>
+    <row r="761" spans="1:5">
+      <c r="A761" s="2"/>
+      <c r="B761" s="3"/>
+      <c r="C761" s="4"/>
+      <c r="D761" s="4"/>
+      <c r="E761" s="3"/>
+    </row>
+    <row r="762" spans="1:5">
+      <c r="A762" s="2"/>
+      <c r="B762" s="3"/>
+      <c r="C762" s="4"/>
+      <c r="D762" s="4"/>
+      <c r="E762" s="3"/>
+    </row>
+    <row r="763" spans="1:5">
+      <c r="A763" s="2"/>
+      <c r="B763" s="3"/>
+      <c r="C763" s="4"/>
+      <c r="D763" s="4"/>
+      <c r="E763" s="3"/>
+    </row>
+    <row r="764" spans="1:5">
+      <c r="A764" s="2"/>
+      <c r="B764" s="3"/>
+      <c r="C764" s="4"/>
+      <c r="D764" s="4"/>
+      <c r="E764" s="3"/>
+    </row>
+    <row r="765" spans="1:5">
+      <c r="A765" s="2"/>
+      <c r="B765" s="3"/>
+      <c r="C765" s="4"/>
+      <c r="D765" s="4"/>
+      <c r="E765" s="3"/>
+    </row>
+    <row r="766" spans="1:5">
+      <c r="A766" s="2"/>
+      <c r="B766" s="3"/>
+      <c r="C766" s="4"/>
+      <c r="D766" s="4"/>
+      <c r="E766" s="3"/>
+    </row>
+    <row r="767" spans="1:5">
+      <c r="A767" s="2"/>
+      <c r="B767" s="3"/>
+      <c r="C767" s="4"/>
+      <c r="D767" s="4"/>
+      <c r="E767" s="3"/>
+    </row>
+    <row r="768" spans="1:5">
+      <c r="A768" s="2"/>
+      <c r="B768" s="3"/>
+      <c r="C768" s="4"/>
+      <c r="D768" s="4"/>
+      <c r="E768" s="3"/>
+    </row>
+    <row r="769" spans="1:5">
+      <c r="A769" s="2"/>
+      <c r="B769" s="3"/>
+      <c r="C769" s="4"/>
+      <c r="D769" s="4"/>
+      <c r="E769" s="3"/>
+    </row>
+    <row r="770" spans="1:5">
+      <c r="A770" s="2"/>
+      <c r="B770" s="3"/>
+      <c r="C770" s="4"/>
+      <c r="D770" s="4"/>
+      <c r="E770" s="3"/>
+    </row>
+    <row r="771" spans="1:5">
+      <c r="A771" s="2"/>
+      <c r="B771" s="3"/>
+      <c r="C771" s="4"/>
+      <c r="D771" s="4"/>
+      <c r="E771" s="3"/>
+    </row>
+    <row r="772" spans="1:5">
+      <c r="A772" s="2"/>
+      <c r="B772" s="3"/>
+      <c r="C772" s="4"/>
+      <c r="D772" s="4"/>
+      <c r="E772" s="3"/>
+    </row>
+    <row r="773" spans="1:5">
+      <c r="A773" s="2"/>
+      <c r="B773" s="3"/>
+      <c r="C773" s="4"/>
+      <c r="D773" s="4"/>
+      <c r="E773" s="3"/>
+    </row>
+    <row r="774" spans="1:5">
+      <c r="A774" s="2"/>
+      <c r="B774" s="3"/>
+      <c r="C774" s="4"/>
+      <c r="D774" s="4"/>
+      <c r="E774" s="3"/>
+    </row>
+    <row r="775" spans="1:5">
+      <c r="A775" s="2"/>
+      <c r="B775" s="3"/>
+      <c r="C775" s="4"/>
+      <c r="D775" s="4"/>
+      <c r="E775" s="3"/>
+    </row>
+    <row r="776" spans="1:5">
+      <c r="A776" s="2"/>
+      <c r="B776" s="3"/>
+      <c r="C776" s="4"/>
+      <c r="D776" s="4"/>
+      <c r="E776" s="3"/>
+    </row>
+    <row r="777" spans="1:5">
+      <c r="A777" s="2"/>
+      <c r="B777" s="3"/>
+      <c r="C777" s="4"/>
+      <c r="D777" s="4"/>
+      <c r="E777" s="3"/>
+    </row>
+    <row r="778" spans="1:5">
+      <c r="A778" s="2"/>
+      <c r="B778" s="3"/>
+      <c r="C778" s="4"/>
+      <c r="D778" s="4"/>
+      <c r="E778" s="3"/>
+    </row>
+    <row r="779" spans="1:5">
+      <c r="A779" s="2"/>
+      <c r="B779" s="3"/>
+      <c r="C779" s="4"/>
+      <c r="D779" s="4"/>
+      <c r="E779" s="3"/>
+    </row>
+    <row r="780" spans="1:5">
+      <c r="A780" s="2"/>
+      <c r="B780" s="3"/>
+      <c r="C780" s="4"/>
+      <c r="D780" s="4"/>
+      <c r="E780" s="3"/>
+    </row>
+    <row r="781" spans="1:5">
+      <c r="A781" s="2"/>
+      <c r="B781" s="3"/>
+      <c r="C781" s="4"/>
+      <c r="D781" s="4"/>
+      <c r="E781" s="3"/>
+    </row>
+    <row r="782" spans="1:5">
+      <c r="A782" s="2"/>
+      <c r="B782" s="3"/>
+      <c r="C782" s="4"/>
+      <c r="D782" s="4"/>
+      <c r="E782" s="3"/>
+    </row>
+    <row r="783" spans="1:5">
+      <c r="A783" s="2"/>
+      <c r="B783" s="3"/>
+      <c r="C783" s="4"/>
+      <c r="D783" s="4"/>
+      <c r="E783" s="3"/>
+    </row>
+    <row r="784" spans="1:5">
+      <c r="A784" s="2"/>
+      <c r="B784" s="3"/>
+      <c r="C784" s="4"/>
+      <c r="D784" s="4"/>
+      <c r="E784" s="3"/>
+    </row>
+    <row r="785" spans="1:5">
+      <c r="A785" s="2"/>
+      <c r="B785" s="3"/>
+      <c r="C785" s="4"/>
+      <c r="D785" s="4"/>
+      <c r="E785" s="3"/>
+    </row>
+    <row r="786" spans="1:5">
+      <c r="A786" s="2"/>
+      <c r="B786" s="3"/>
+      <c r="C786" s="4"/>
+      <c r="D786" s="4"/>
+      <c r="E786" s="3"/>
+    </row>
+    <row r="787" spans="1:5">
+      <c r="A787" s="2"/>
+      <c r="B787" s="3"/>
+      <c r="C787" s="4"/>
+      <c r="D787" s="4"/>
+      <c r="E787" s="3"/>
+    </row>
+    <row r="788" spans="1:5">
+      <c r="A788" s="2"/>
+      <c r="B788" s="3"/>
+      <c r="C788" s="4"/>
+      <c r="D788" s="4"/>
+      <c r="E788" s="3"/>
+    </row>
+    <row r="789" spans="1:5">
+      <c r="A789" s="2"/>
+      <c r="B789" s="3"/>
+      <c r="C789" s="4"/>
+      <c r="D789" s="4"/>
+      <c r="E789" s="3"/>
+    </row>
+    <row r="790" spans="1:5">
+      <c r="A790" s="2"/>
+      <c r="B790" s="3"/>
+      <c r="C790" s="4"/>
+      <c r="D790" s="4"/>
+      <c r="E790" s="3"/>
+    </row>
+    <row r="791" spans="1:5">
+      <c r="A791" s="2"/>
+      <c r="B791" s="3"/>
+      <c r="C791" s="4"/>
+      <c r="D791" s="4"/>
+      <c r="E791" s="3"/>
+    </row>
+    <row r="792" spans="1:5">
+      <c r="A792" s="2"/>
+      <c r="B792" s="3"/>
+      <c r="C792" s="4"/>
+      <c r="D792" s="4"/>
+      <c r="E792" s="3"/>
+    </row>
+    <row r="793" spans="1:5">
+      <c r="A793" s="2"/>
+      <c r="B793" s="3"/>
+      <c r="C793" s="4"/>
+      <c r="D793" s="4"/>
+      <c r="E793" s="3"/>
+    </row>
+    <row r="794" spans="1:5">
+      <c r="A794" s="2"/>
+      <c r="B794" s="3"/>
+      <c r="C794" s="4"/>
+      <c r="D794" s="4"/>
+      <c r="E794" s="3"/>
+    </row>
+    <row r="795" spans="1:5">
+      <c r="A795" s="2"/>
+      <c r="B795" s="3"/>
+      <c r="C795" s="4"/>
+      <c r="D795" s="4"/>
+      <c r="E795" s="3"/>
+    </row>
+    <row r="796" spans="1:5">
+      <c r="A796" s="2"/>
+      <c r="B796" s="3"/>
+      <c r="C796" s="4"/>
+      <c r="D796" s="4"/>
+      <c r="E796" s="3"/>
+    </row>
+    <row r="797" spans="1:5">
+      <c r="A797" s="2"/>
+      <c r="B797" s="3"/>
+      <c r="C797" s="4"/>
+      <c r="D797" s="4"/>
+      <c r="E797" s="3"/>
+    </row>
+    <row r="798" spans="1:5">
+      <c r="A798" s="2"/>
+      <c r="B798" s="3"/>
+      <c r="C798" s="4"/>
+      <c r="D798" s="4"/>
+      <c r="E798" s="3"/>
+    </row>
+    <row r="799" spans="1:5">
+      <c r="A799" s="2"/>
+      <c r="B799" s="3"/>
+      <c r="C799" s="4"/>
+      <c r="D799" s="4"/>
+      <c r="E799" s="3"/>
+    </row>
+    <row r="800" spans="1:5">
+      <c r="A800" s="2"/>
+      <c r="B800" s="3"/>
+      <c r="C800" s="4"/>
+      <c r="D800" s="4"/>
+      <c r="E800" s="3"/>
+    </row>
+    <row r="801" spans="1:5">
+      <c r="A801" s="2"/>
+      <c r="B801" s="3"/>
+      <c r="C801" s="4"/>
+      <c r="D801" s="4"/>
+      <c r="E801" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E119">
-    <extLst/>
-  </autoFilter>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="店舗名エラー" error="店舗マスタの一覧にある店舗名を選択してください。" sqref="B2:B118">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="店舗名エラー" error="店舗マスタの一覧にある店舗名を選択してください。" sqref="B2:B118 B119:B801">
       <formula1>店舗マスタ!$A$2:$A$31</formula1>
     </dataValidation>
   </dataValidations>

--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12450" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12420" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$119</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,46 +203,9 @@
       <charset val="128"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -264,23 +227,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -288,7 +244,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -303,7 +266,37 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -311,15 +304,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -334,7 +334,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,55 +362,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,127 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -588,10 +588,8 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -616,25 +614,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,155 +648,175 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -828,6 +828,7 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -846,12 +847,12 @@
     <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
     <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
     <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="20% - アクセント 4" xfId="7" builtinId="42"/>
+    <cellStyle name="メモ" xfId="8" builtinId="10"/>
+    <cellStyle name="パーセント" xfId="9" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="10" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="11" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="12" builtinId="9"/>
     <cellStyle name="良い" xfId="13" builtinId="26"/>
     <cellStyle name="警告文" xfId="14" builtinId="11"/>
     <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
@@ -1190,152 +1191,152 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.25" spans="1:1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="8"/>
+      <c r="A2" s="9"/>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="9" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="9" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="8"/>
+      <c r="A5" s="9"/>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="9" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="9" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="9" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="8"/>
+      <c r="A12" s="9"/>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="8"/>
+      <c r="A16" s="9"/>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="9" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="9" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="9" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="8"/>
+      <c r="A27" s="9"/>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="10" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="9" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="9" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="9" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1486,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E121"/>
+  <dimension ref="A1:E120"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -3044,24 +3045,19 @@
         <v>3908080</v>
       </c>
     </row>
-    <row r="120" spans="1:2">
+    <row r="120" spans="1:3">
       <c r="A120" s="1">
-        <v>46281</v>
+        <v>46290</v>
       </c>
       <c r="B120" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="121" spans="1:2">
-      <c r="A121" s="1">
-        <v>46282</v>
-      </c>
-      <c r="B121" t="s">
-        <v>41</v>
+      <c r="C120" s="7">
+        <v>15012598</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E120">
+  <autoFilter ref="A1:E119">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$120</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,17 +203,31 @@
       <charset val="128"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -227,29 +241,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -265,31 +271,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -297,6 +289,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -318,8 +317,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -332,16 +332,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +410,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,25 +494,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,13 +506,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,48 +530,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -488,61 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -582,15 +591,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -612,24 +612,20 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -658,13 +654,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,161 +674,163 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1191,152 +1193,152 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.25" spans="1:1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="9"/>
+      <c r="A2" s="11"/>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="11" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="11" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="9"/>
+      <c r="A5" s="11"/>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="11" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="11" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="11" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="9"/>
+      <c r="A12" s="11"/>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="11" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="9"/>
+      <c r="A16" s="11"/>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="12" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="11" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="11" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="11" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="11" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="11" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="11" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="11" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="9"/>
+      <c r="A27" s="11"/>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="10" t="s">
+      <c r="A28" s="12" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="11" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="9" t="s">
+      <c r="A30" s="11" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="9" t="s">
+      <c r="A31" s="11" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="9" t="s">
+      <c r="A32" s="11" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1487,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E120"/>
+  <dimension ref="A1:E125"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -2944,120 +2946,175 @@
       <c r="E111" s="5"/>
     </row>
     <row r="112" spans="1:5">
-      <c r="A112" s="4">
+      <c r="A112" s="7">
         <v>46266</v>
       </c>
-      <c r="B112" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C112" s="6">
+      <c r="B112" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C112" s="9">
         <v>7508592</v>
       </c>
       <c r="D112" s="6"/>
       <c r="E112" s="5"/>
     </row>
     <row r="113" spans="1:5">
-      <c r="A113" s="4">
+      <c r="A113" s="7">
         <v>46267</v>
       </c>
-      <c r="B113" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C113" s="6">
+      <c r="B113" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C113" s="9">
         <v>1954040</v>
       </c>
       <c r="D113" s="6"/>
       <c r="E113" s="5"/>
     </row>
     <row r="114" spans="1:5">
-      <c r="A114" s="4">
+      <c r="A114" s="7">
         <v>46269</v>
       </c>
-      <c r="B114" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C114" s="6">
+      <c r="B114" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C114" s="9">
         <v>9937899</v>
       </c>
       <c r="D114" s="6"/>
       <c r="E114" s="5"/>
     </row>
     <row r="115" spans="1:5">
-      <c r="A115" s="4">
+      <c r="A115" s="7">
         <v>46270</v>
       </c>
-      <c r="B115" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C115" s="6">
+      <c r="B115" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C115" s="9">
         <v>1215900</v>
       </c>
       <c r="D115" s="6"/>
       <c r="E115" s="5"/>
     </row>
     <row r="116" spans="1:5">
-      <c r="A116" s="4">
+      <c r="A116" s="7">
         <v>46274</v>
       </c>
-      <c r="B116" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C116" s="6">
+      <c r="B116" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C116" s="9">
         <v>15012598</v>
       </c>
       <c r="D116" s="6"/>
       <c r="E116" s="5"/>
     </row>
     <row r="117" spans="1:5">
-      <c r="A117" s="4">
+      <c r="A117" s="7">
         <v>46276</v>
       </c>
-      <c r="B117" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C117" s="6">
-        <v>9462632</v>
+      <c r="B117" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C117" s="9">
+        <v>10678532</v>
       </c>
       <c r="D117" s="6"/>
       <c r="E117" s="5"/>
     </row>
     <row r="118" spans="1:5">
-      <c r="A118" s="4">
+      <c r="A118" s="7">
         <v>46279</v>
       </c>
-      <c r="B118" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C118" s="6">
-        <v>8131384</v>
+      <c r="B118" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C118" s="9">
+        <v>8131385</v>
       </c>
       <c r="D118" s="6"/>
       <c r="E118" s="5"/>
     </row>
     <row r="119" spans="1:3">
-      <c r="A119" s="1">
+      <c r="A119" s="7">
         <v>46280</v>
       </c>
-      <c r="B119" t="s">
-        <v>41</v>
-      </c>
-      <c r="C119">
-        <v>3908080</v>
+      <c r="B119" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C119" s="9">
+        <v>7508592</v>
       </c>
     </row>
     <row r="120" spans="1:3">
-      <c r="A120" s="1">
+      <c r="A120" s="7">
+        <v>46282</v>
+      </c>
+      <c r="B120" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C120" s="9">
+        <v>9915192</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" s="7">
+        <v>46283</v>
+      </c>
+      <c r="B121" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C121" s="9">
+        <v>17444398</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122" s="7">
+        <v>46287</v>
+      </c>
+      <c r="B122" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C122" s="9">
+        <v>12679980</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123" s="7">
+        <v>46288</v>
+      </c>
+      <c r="B123" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C123" s="9">
+        <v>15062598</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124" s="7">
+        <v>46289</v>
+      </c>
+      <c r="B124" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C124" s="9">
+        <v>7508592</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" s="7">
         <v>46290</v>
       </c>
-      <c r="B120" t="s">
-        <v>41</v>
-      </c>
-      <c r="C120" s="7">
-        <v>15012598</v>
+      <c r="B125" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C125" s="9">
+        <v>30025195</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E119">
+  <autoFilter ref="A1:E120">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12420" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -12,7 +12,7 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$125</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -211,10 +211,17 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -233,11 +240,72 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -250,14 +318,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -279,36 +339,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -316,36 +346,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -362,7 +362,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,24 +536,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -399,150 +543,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,9 +573,20 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -612,20 +623,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -645,15 +645,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -668,167 +659,173 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1193,152 +1190,152 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.25" spans="1:1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="11"/>
+      <c r="A2" s="8"/>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="11"/>
+      <c r="A5" s="8"/>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="8" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="8" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="8" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="11"/>
+      <c r="A12" s="8"/>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="8" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="11"/>
+      <c r="A16" s="8"/>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="9" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="8" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="8" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="8" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="8" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="8" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="11"/>
+      <c r="A27" s="8"/>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="9" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="8" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="8" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="8" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2946,179 +2943,179 @@
       <c r="E111" s="5"/>
     </row>
     <row r="112" spans="1:5">
-      <c r="A112" s="7">
+      <c r="A112" s="4">
         <v>46266</v>
       </c>
-      <c r="B112" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C112" s="9">
+      <c r="B112" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C112" s="6">
         <v>7508592</v>
       </c>
       <c r="D112" s="6"/>
       <c r="E112" s="5"/>
     </row>
     <row r="113" spans="1:5">
-      <c r="A113" s="7">
+      <c r="A113" s="4">
         <v>46267</v>
       </c>
-      <c r="B113" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C113" s="9">
+      <c r="B113" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C113" s="6">
         <v>1954040</v>
       </c>
       <c r="D113" s="6"/>
       <c r="E113" s="5"/>
     </row>
     <row r="114" spans="1:5">
-      <c r="A114" s="7">
+      <c r="A114" s="4">
         <v>46269</v>
       </c>
-      <c r="B114" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C114" s="9">
+      <c r="B114" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C114" s="6">
         <v>9937899</v>
       </c>
       <c r="D114" s="6"/>
       <c r="E114" s="5"/>
     </row>
     <row r="115" spans="1:5">
-      <c r="A115" s="7">
+      <c r="A115" s="4">
         <v>46270</v>
       </c>
-      <c r="B115" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C115" s="9">
+      <c r="B115" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C115" s="6">
         <v>1215900</v>
       </c>
       <c r="D115" s="6"/>
       <c r="E115" s="5"/>
     </row>
     <row r="116" spans="1:5">
-      <c r="A116" s="7">
+      <c r="A116" s="4">
         <v>46274</v>
       </c>
-      <c r="B116" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C116" s="9">
+      <c r="B116" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C116" s="6">
         <v>15012598</v>
       </c>
       <c r="D116" s="6"/>
       <c r="E116" s="5"/>
     </row>
     <row r="117" spans="1:5">
-      <c r="A117" s="7">
+      <c r="A117" s="4">
         <v>46276</v>
       </c>
-      <c r="B117" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C117" s="9">
+      <c r="B117" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C117" s="6">
         <v>10678532</v>
       </c>
       <c r="D117" s="6"/>
       <c r="E117" s="5"/>
     </row>
     <row r="118" spans="1:5">
-      <c r="A118" s="7">
+      <c r="A118" s="4">
         <v>46279</v>
       </c>
-      <c r="B118" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C118" s="9">
+      <c r="B118" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C118" s="6">
         <v>8131385</v>
       </c>
       <c r="D118" s="6"/>
       <c r="E118" s="5"/>
     </row>
     <row r="119" spans="1:3">
-      <c r="A119" s="7">
+      <c r="A119" s="4">
         <v>46280</v>
       </c>
-      <c r="B119" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C119" s="9">
+      <c r="B119" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C119" s="6">
         <v>7508592</v>
       </c>
     </row>
     <row r="120" spans="1:3">
-      <c r="A120" s="7">
+      <c r="A120" s="4">
         <v>46282</v>
       </c>
-      <c r="B120" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C120" s="9">
+      <c r="B120" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C120" s="6">
         <v>9915192</v>
       </c>
     </row>
     <row r="121" spans="1:3">
-      <c r="A121" s="7">
+      <c r="A121" s="4">
         <v>46283</v>
       </c>
-      <c r="B121" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C121" s="9">
+      <c r="B121" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C121" s="6">
         <v>17444398</v>
       </c>
     </row>
     <row r="122" spans="1:3">
-      <c r="A122" s="7">
+      <c r="A122" s="4">
         <v>46287</v>
       </c>
-      <c r="B122" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C122" s="9">
+      <c r="B122" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C122" s="6">
         <v>12679980</v>
       </c>
     </row>
     <row r="123" spans="1:3">
-      <c r="A123" s="7">
+      <c r="A123" s="4">
         <v>46288</v>
       </c>
-      <c r="B123" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C123" s="9">
+      <c r="B123" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C123" s="6">
         <v>15062598</v>
       </c>
     </row>
     <row r="124" spans="1:3">
-      <c r="A124" s="7">
+      <c r="A124" s="4">
         <v>46289</v>
       </c>
-      <c r="B124" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C124" s="9">
+      <c r="B124" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C124" s="6">
         <v>7508592</v>
       </c>
     </row>
     <row r="125" spans="1:3">
-      <c r="A125" s="7">
+      <c r="A125" s="4">
         <v>46290</v>
       </c>
-      <c r="B125" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C125" s="9">
+      <c r="B125" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C125" s="6">
         <v>30025195</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E120">
+  <autoFilter ref="A1:E125">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="店舗名エラー" error="店舗マスタの一覧にある店舗名を選択してください。" sqref="B2:B118">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="店舗名エラー" error="店舗マスタの一覧にある店舗名を選択してください。" sqref="B2:B101 B102:B125">
       <formula1>店舗マスタ!$A$2:$A$31</formula1>
     </dataValidation>
   </dataValidations>

--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="2"/>
+    <workbookView windowWidth="28125" windowHeight="12450" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -212,13 +212,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -234,15 +227,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -250,21 +243,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -278,8 +256,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -294,18 +287,26 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -317,17 +318,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -346,6 +339,13 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -362,7 +362,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +410,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,127 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,31 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,12 +571,45 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -602,30 +635,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -659,160 +668,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -846,12 +846,12 @@
     <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
     <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
     <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="20% - アクセント 4" xfId="7" builtinId="42"/>
-    <cellStyle name="メモ" xfId="8" builtinId="10"/>
-    <cellStyle name="パーセント" xfId="9" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="10" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="11" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="12" builtinId="9"/>
+    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
+    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
+    <cellStyle name="メモ" xfId="12" builtinId="10"/>
     <cellStyle name="良い" xfId="13" builtinId="26"/>
     <cellStyle name="警告文" xfId="14" builtinId="11"/>
     <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
@@ -1486,7 +1486,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E125"/>
+  <dimension ref="A1:E126"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -3108,6 +3108,14 @@
       </c>
       <c r="C125" s="6">
         <v>30025195</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" s="1">
+        <v>46284</v>
+      </c>
+      <c r="B126" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$126</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -204,15 +204,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,45 +226,23 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -302,11 +272,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -317,8 +286,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -329,6 +306,29 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -362,7 +362,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +500,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,151 +518,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -590,7 +590,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -602,39 +602,6 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,13 +635,46 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,7 +683,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,127 +692,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1486,7 +1486,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E126"/>
+  <dimension ref="A1:E127"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -3118,8 +3118,16 @@
         <v>41</v>
       </c>
     </row>
+    <row r="127" spans="1:2">
+      <c r="A127" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B127" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E125">
+  <autoFilter ref="A1:E126">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$127</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,15 +203,9 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,17 +213,55 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -249,46 +281,22 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -296,6 +304,13 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,6 +324,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -316,36 +346,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -362,7 +362,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,25 +416,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,19 +482,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,25 +494,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,13 +518,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,37 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,31 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,41 +567,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -636,15 +601,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -660,6 +616,41 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -668,151 +659,160 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1486,7 +1486,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E127"/>
+  <dimension ref="A1:E128"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -3126,8 +3126,16 @@
         <v>41</v>
       </c>
     </row>
+    <row r="128" spans="1:2">
+      <c r="A128" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B128" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E126">
+  <autoFilter ref="A1:E127">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$128</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,9 +203,8 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,13 +218,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -234,9 +226,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -251,30 +249,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -288,6 +277,37 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -295,20 +315,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -324,8 +331,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -333,17 +341,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +374,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +398,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,7 +446,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,7 +494,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,127 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,21 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -597,21 +582,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -633,10 +603,8 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -646,7 +614,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -662,9 +645,26 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,124 +695,124 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1486,7 +1486,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E128"/>
+  <dimension ref="A1:E129"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -3134,8 +3134,16 @@
         <v>41</v>
       </c>
     </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B129" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E127">
+  <autoFilter ref="A1:E128">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$129</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,8 +203,9 @@
       <charset val="128"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -212,15 +213,21 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -233,55 +240,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -301,8 +264,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -316,10 +294,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -333,7 +311,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -341,7 +334,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +428,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,19 +506,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,103 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,19 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,21 +572,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -597,24 +582,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -634,11 +601,59 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -653,179 +668,164 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1486,7 +1486,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E129"/>
+  <dimension ref="A1:E130"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -3142,8 +3142,16 @@
         <v>41</v>
       </c>
     </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B130" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E128">
+  <autoFilter ref="A1:E129">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$130</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,9 +203,22 @@
       <charset val="128"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,6 +232,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -226,23 +254,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -258,24 +295,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -287,31 +317,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -324,28 +346,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -362,7 +362,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +398,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +494,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,151 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,6 +586,59 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -615,217 +668,164 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1486,7 +1486,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E130"/>
+  <dimension ref="A1:E131"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -3150,8 +3150,16 @@
         <v>41</v>
       </c>
     </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B131" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E129">
+  <autoFilter ref="A1:E130">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$130</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$131</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,14 +204,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,14 +226,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -242,6 +234,22 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -256,14 +264,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -278,10 +286,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -294,8 +302,24 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -310,7 +334,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -322,30 +346,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -362,7 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +392,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,13 +428,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,13 +476,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,61 +518,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,54 +530,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -543,6 +537,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,6 +567,41 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -595,31 +630,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -639,32 +660,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1486,7 +1486,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E131"/>
+  <dimension ref="A1:E132"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -3158,8 +3158,16 @@
         <v>41</v>
       </c>
     </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="1">
+        <v>46290</v>
+      </c>
+      <c r="B132" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E130">
+  <autoFilter ref="A1:E131">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$132</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,15 +203,9 @@
       <charset val="128"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -232,14 +226,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -247,9 +241,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -262,56 +256,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -334,6 +287,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -341,11 +309,43 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -362,7 +362,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,61 +494,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,85 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,19 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,11 +571,65 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -606,21 +660,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -629,61 +668,22 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,127 +692,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1486,7 +1486,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E132"/>
+  <dimension ref="A1:E133"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -3166,8 +3166,16 @@
         <v>41</v>
       </c>
     </row>
+    <row r="133" spans="1:2">
+      <c r="A133" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B133" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E131">
+  <autoFilter ref="A1:E132">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$133</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,14 +203,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -218,11 +210,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -241,18 +240,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -263,16 +255,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -286,38 +300,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -340,12 +325,27 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -368,7 +368,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,115 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,49 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,16 +572,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -601,17 +601,28 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -620,7 +631,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -630,17 +641,6 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -664,7 +664,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,140 +692,140 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1486,7 +1486,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E133"/>
+  <dimension ref="A1:E134"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -3174,8 +3174,16 @@
         <v>41</v>
       </c>
     </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B134" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E132">
+  <autoFilter ref="A1:E133">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$139</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,13 +164,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -211,6 +211,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -218,16 +233,16 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -235,21 +250,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -264,7 +264,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -286,7 +286,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -310,14 +310,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -334,9 +334,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -346,6 +346,13 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -374,7 +381,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,13 +471,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,127 +531,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,7 +543,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +578,24 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -586,6 +611,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -597,17 +646,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -629,61 +667,30 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,25 +702,25 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -722,112 +729,116 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -838,7 +849,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="50">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="桁区切り[0]" xfId="1" builtinId="6"/>
     <cellStyle name="入力" xfId="2" builtinId="20"/>
@@ -888,6 +899,7 @@
     <cellStyle name="アクセント 5" xfId="46" builtinId="45"/>
     <cellStyle name="40% - アクセント 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - アクセント 6" xfId="48" builtinId="52"/>
+    <cellStyle name="標準 2" xfId="49"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1190,152 +1202,152 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.25" spans="1:1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="8"/>
+      <c r="A2" s="9"/>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="9" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="9" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="8"/>
+      <c r="A5" s="9"/>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="9" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="9" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="9" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="8"/>
+      <c r="A12" s="9"/>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="8"/>
+      <c r="A16" s="9"/>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="9" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="9" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="9" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="8"/>
+      <c r="A27" s="9"/>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="10" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="9" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="9" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="9" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1486,7 +1498,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E134"/>
+  <dimension ref="A1:E141"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -2942,7 +2954,7 @@
       <c r="D111" s="6"/>
       <c r="E111" s="5"/>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:3">
       <c r="A112" s="4">
         <v>46266</v>
       </c>
@@ -2952,10 +2964,8 @@
       <c r="C112" s="6">
         <v>7508592</v>
       </c>
-      <c r="D112" s="6"/>
-      <c r="E112" s="5"/>
-    </row>
-    <row r="113" spans="1:5">
+    </row>
+    <row r="113" spans="1:3">
       <c r="A113" s="4">
         <v>46267</v>
       </c>
@@ -2965,229 +2975,310 @@
       <c r="C113" s="6">
         <v>1954040</v>
       </c>
-      <c r="D113" s="6"/>
-      <c r="E113" s="5"/>
-    </row>
-    <row r="114" spans="1:5">
+    </row>
+    <row r="114" spans="1:3">
       <c r="A114" s="4">
+        <v>46268</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C114" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" s="4">
         <v>46269</v>
       </c>
-      <c r="B114" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C114" s="6">
+      <c r="B115" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C115" s="7">
         <v>9937899</v>
       </c>
-      <c r="D114" s="6"/>
-      <c r="E114" s="5"/>
-    </row>
-    <row r="115" spans="1:5">
-      <c r="A115" s="4">
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" s="4">
         <v>46270</v>
       </c>
-      <c r="B115" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C115" s="6">
+      <c r="B116" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C116" s="7">
         <v>1215900</v>
       </c>
-      <c r="D115" s="6"/>
-      <c r="E115" s="5"/>
-    </row>
-    <row r="116" spans="1:5">
-      <c r="A116" s="4">
-        <v>46274</v>
-      </c>
-      <c r="B116" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C116" s="6">
-        <v>15012598</v>
-      </c>
-      <c r="D116" s="6"/>
-      <c r="E116" s="5"/>
-    </row>
-    <row r="117" spans="1:5">
+    </row>
+    <row r="117" spans="1:3">
       <c r="A117" s="4">
-        <v>46276</v>
+        <v>46271</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C117" s="6">
-        <v>10678532</v>
-      </c>
-      <c r="D117" s="6"/>
-      <c r="E117" s="5"/>
-    </row>
-    <row r="118" spans="1:5">
+      <c r="C117" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
       <c r="A118" s="4">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C118" s="6">
-        <v>8131385</v>
-      </c>
-      <c r="D118" s="6"/>
-      <c r="E118" s="5"/>
+      <c r="C118" s="7">
+        <v>0</v>
+      </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119" s="4">
-        <v>46280</v>
+        <v>46273</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C119" s="6">
-        <v>7508592</v>
+      <c r="C119" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" s="4">
-        <v>46282</v>
+        <v>46274</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C120" s="6">
-        <v>9915192</v>
+        <v>15012598</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" s="4">
-        <v>46283</v>
+        <v>46275</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C121" s="6">
-        <v>17444398</v>
+      <c r="C121" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" s="4">
-        <v>46287</v>
+        <v>46276</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C122" s="6">
-        <v>12679980</v>
+        <v>10678532</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123" s="4">
-        <v>46288</v>
+        <v>46277</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C123" s="6">
-        <v>15062598</v>
+      <c r="C123" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" s="4">
-        <v>46289</v>
+        <v>46278</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C124" s="6">
-        <v>7508592</v>
+      <c r="C124" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" s="4">
+        <v>46279</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C125" s="6">
+        <v>8131385</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126" s="4">
+        <v>46280</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C126" s="6">
+        <v>7508592</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127" s="4">
+        <v>46281</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C127" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128" s="4">
+        <v>46282</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C128" s="6">
+        <v>9915192</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129" s="4">
+        <v>46283</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C129" s="6">
+        <v>17444398</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130" s="4">
+        <v>46284</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C130" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131" s="4">
+        <v>46285</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C131" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132" s="4">
+        <v>46286</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C132" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133" s="4">
+        <v>46287</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C133" s="6">
+        <v>12679980</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134" s="4">
+        <v>46288</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C134" s="6">
+        <v>17494397</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135" s="4">
+        <v>46289</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C135" s="6">
+        <v>7508592</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="A136" s="4">
         <v>46290</v>
       </c>
-      <c r="B125" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C125" s="6">
-        <v>30025195</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2">
-      <c r="A126" s="1">
-        <v>46284</v>
-      </c>
-      <c r="B126" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2">
-      <c r="A127" s="1">
-        <v>46285</v>
-      </c>
-      <c r="B127" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2">
-      <c r="A128" s="1">
-        <v>46286</v>
-      </c>
-      <c r="B128" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2">
-      <c r="A129" s="1">
-        <v>46287</v>
-      </c>
-      <c r="B129" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2">
-      <c r="A130" s="1">
-        <v>46288</v>
-      </c>
-      <c r="B130" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2">
-      <c r="A131" s="1">
-        <v>46289</v>
-      </c>
-      <c r="B131" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2">
-      <c r="A132" s="1">
-        <v>46290</v>
-      </c>
-      <c r="B132" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2">
-      <c r="A133" s="1">
+      <c r="B136" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C136" s="6">
+        <v>19610598</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="A137" s="4">
         <v>46291</v>
       </c>
-      <c r="B133" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2">
-      <c r="A134" s="1">
+      <c r="B137" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C137" s="7">
+        <v>2406600</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138" s="4">
         <v>46292</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B138" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C138" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139" s="4">
+        <v>46293</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C139" s="7">
+        <v>8537156</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" s="4"/>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B141" t="s">
         <v>41</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E133">
+  <autoFilter ref="A1:E139">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="店舗名エラー" error="店舗マスタの一覧にある店舗名を選択してください。" sqref="B2:B101 B102:B125">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="店舗名エラー" error="店舗マスタの一覧にある店舗名を選択してください。" sqref="B2:B101 B102:B111 B112:B139">
       <formula1>店舗マスタ!$A$2:$A$31</formula1>
     </dataValidation>
   </dataValidations>

--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -204,9 +204,70 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -217,16 +278,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -240,44 +302,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -286,31 +310,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -326,7 +333,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -334,9 +341,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -346,13 +353,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -369,7 +369,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -381,7 +393,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -393,49 +495,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -447,25 +537,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -477,79 +549,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,24 +578,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -607,45 +589,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -667,6 +610,54 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -675,154 +666,163 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1498,7 +1498,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E141"/>
+  <dimension ref="A1:E142"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -3270,6 +3270,14 @@
         <v>46293</v>
       </c>
       <c r="B141" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B142" t="s">
         <v>41</v>
       </c>
     </row>

--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -206,7 +206,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="128"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -217,8 +217,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,17 +227,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -255,9 +256,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -272,15 +286,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -295,29 +317,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -333,17 +334,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -351,6 +344,13 @@
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -369,19 +369,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -393,7 +393,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -405,13 +405,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -423,13 +435,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -447,7 +471,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -459,97 +543,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,6 +578,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -589,6 +598,56 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -611,65 +670,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
       </bottom>
@@ -681,7 +681,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -690,10 +690,10 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -702,140 +702,140 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1498,7 +1498,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E142"/>
+  <dimension ref="A1:E143"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -3278,6 +3278,14 @@
         <v>46294</v>
       </c>
       <c r="B142" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B143" t="s">
         <v>41</v>
       </c>
     </row>

--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="25">
@@ -204,22 +204,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,7 +219,44 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -242,9 +264,32 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -256,8 +301,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -277,58 +323,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -340,8 +339,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -369,7 +369,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -381,37 +507,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -423,133 +543,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -582,7 +582,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -598,6 +613,39 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -619,15 +667,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -636,190 +675,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
@@ -1498,7 +1498,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E143"/>
+  <dimension ref="A1:E144"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -3286,6 +3286,14 @@
         <v>46295</v>
       </c>
       <c r="B143" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B144" t="s">
         <v>41</v>
       </c>
     </row>

--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$156</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,9 +165,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="25">
@@ -184,6 +184,13 @@
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -204,30 +211,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -240,16 +231,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -264,32 +256,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -310,22 +279,52 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -341,16 +340,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="128"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -369,7 +369,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -381,19 +447,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -405,7 +495,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -417,13 +513,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -435,121 +543,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,30 +578,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -617,16 +593,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -667,6 +643,30 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -681,152 +681,152 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -839,13 +839,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1202,152 +1205,152 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.25" spans="1:1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="9"/>
+      <c r="A2" s="10"/>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="10" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="9"/>
+      <c r="A5" s="10"/>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="10" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="10" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="10" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="10" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="9"/>
+      <c r="A12" s="10"/>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="10" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="9"/>
+      <c r="A16" s="10"/>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="11" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="10" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="10" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="10" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="10" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="10" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="10" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="10" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="10" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="10" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="9"/>
+      <c r="A27" s="10"/>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="10" t="s">
+      <c r="A28" s="11" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="10" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="9" t="s">
+      <c r="A30" s="10" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="9" t="s">
+      <c r="A31" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="9" t="s">
+      <c r="A32" s="10" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1498,7 +1501,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E144"/>
+  <dimension ref="A1:E157"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -3262,47 +3265,210 @@
         <v>8537156</v>
       </c>
     </row>
-    <row r="140" spans="1:1">
-      <c r="A140" s="4"/>
-    </row>
-    <row r="141" spans="1:2">
+    <row r="140" spans="1:3">
+      <c r="A140" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3">
       <c r="A141" s="1">
-        <v>46293</v>
-      </c>
-      <c r="B141" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2">
+        <v>46295</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3">
       <c r="A142" s="1">
-        <v>46294</v>
-      </c>
-      <c r="B142" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2">
+        <v>46296</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C142" s="8">
+        <v>7233408</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3">
       <c r="A143" s="1">
-        <v>46295</v>
-      </c>
-      <c r="B143" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2">
+        <v>46297</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C143" s="8">
+        <v>7233408</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3">
       <c r="A144" s="1">
-        <v>46295</v>
-      </c>
-      <c r="B144" t="s">
-        <v>41</v>
+        <v>46298</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
+      <c r="A145" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C146" s="8">
+        <v>7233408</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3">
+      <c r="A147" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
+      <c r="A148" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3">
+      <c r="A149" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C149" s="8">
+        <v>7233408</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C150" s="8">
+        <v>21542072</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151" s="1">
+        <v>46305</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152" s="1">
+        <v>46306</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C154" s="8">
+        <v>7233408</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
+      <c r="A155" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C155" s="8">
+        <v>14536472</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3">
+      <c r="A156" s="1">
+        <v>46310</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C156" s="8">
+        <v>7233408</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3">
+      <c r="A157" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B157" t="s">
+        <v>41</v>
+      </c>
+      <c r="C157">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E139">
+  <autoFilter ref="A1:E156">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="店舗名エラー" error="店舗マスタの一覧にある店舗名を選択してください。" sqref="B2:B101 B102:B111 B112:B139">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="店舗名エラー" error="店舗マスタの一覧にある店舗名を選択してください。" sqref="B2:B101 B102:B111 B112:B138 B139:B156">
       <formula1>店舗マスタ!$A$2:$A$31</formula1>
     </dataValidation>
   </dataValidations>

--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$156</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$157</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="25">
@@ -224,6 +224,58 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -239,26 +291,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -278,55 +315,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -341,6 +334,13 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -369,7 +369,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -381,73 +537,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -459,97 +549,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -574,36 +574,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -637,6 +607,36 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -681,145 +681,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -1501,7 +1501,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E157"/>
+  <dimension ref="A1:E158"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -3463,8 +3463,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="158" spans="1:3">
+      <c r="A158" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B158" t="s">
+        <v>41</v>
+      </c>
+      <c r="C158">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E156">
+  <autoFilter ref="A1:E157">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$157</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$158</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,9 +165,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="25">
@@ -211,7 +211,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -224,68 +231,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -315,11 +262,64 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -369,7 +369,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -381,19 +453,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -411,7 +507,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -423,103 +531,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -531,25 +549,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,20 +578,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -611,17 +608,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -681,16 +681,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -699,127 +699,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -1501,7 +1501,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E158"/>
+  <dimension ref="A1:E159"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -3474,8 +3474,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="159" spans="1:3">
+      <c r="A159" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B159" t="s">
+        <v>41</v>
+      </c>
+      <c r="C159">
+        <v>51247017.2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E157">
+  <autoFilter ref="A1:E158">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$158</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$159</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="25">
@@ -211,7 +211,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -238,17 +238,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -262,9 +262,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -278,13 +293,14 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -293,15 +309,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -316,21 +324,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -339,16 +332,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -369,7 +369,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -381,7 +381,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -393,7 +393,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -405,31 +465,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -441,19 +483,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -465,13 +501,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -483,49 +513,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -537,13 +543,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -579,21 +579,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -611,17 +596,34 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -645,7 +647,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -667,11 +669,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -681,145 +681,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -1501,7 +1501,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E159"/>
+  <dimension ref="A1:E160"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -3485,8 +3485,19 @@
         <v>51247017.2</v>
       </c>
     </row>
+    <row r="160" spans="1:3">
+      <c r="A160" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B160" t="s">
+        <v>41</v>
+      </c>
+      <c r="C160">
+        <v>3622500</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E158">
+  <autoFilter ref="A1:E159">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$160</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="25">
@@ -210,93 +210,11 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -316,17 +234,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -341,7 +258,90 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -369,6 +369,60 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -381,19 +435,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -405,55 +501,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -465,19 +513,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -489,7 +525,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -501,7 +537,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -513,43 +549,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,26 +578,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -619,10 +606,8 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -643,11 +628,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -675,151 +666,160 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -1501,7 +1501,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E160"/>
+  <dimension ref="A1:E161"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -3496,8 +3496,19 @@
         <v>3622500</v>
       </c>
     </row>
+    <row r="161" spans="1:3">
+      <c r="A161" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B161" t="s">
+        <v>41</v>
+      </c>
+      <c r="C161">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E159">
+  <autoFilter ref="A1:E160">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$160</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$161</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,9 +165,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="25">
@@ -210,33 +210,8 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -257,8 +232,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -287,6 +293,28 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -296,7 +324,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -311,44 +347,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -369,7 +369,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -381,175 +549,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,6 +580,15 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -600,15 +609,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -643,21 +643,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -675,22 +660,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -699,127 +699,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -1501,7 +1501,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E161"/>
+  <dimension ref="A1:E162"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -3507,8 +3507,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="162" spans="1:3">
+      <c r="A162" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B162" t="s">
+        <v>41</v>
+      </c>
+      <c r="C162">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E160">
+  <autoFilter ref="A1:E161">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$161</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$162</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -211,14 +211,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -232,16 +232,48 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -264,14 +296,29 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -286,7 +333,7 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -294,61 +341,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -369,7 +369,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -381,13 +381,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -399,115 +417,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -525,7 +441,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -537,7 +477,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -549,7 +519,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,11 +578,32 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -598,32 +619,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -646,31 +655,22 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -681,7 +681,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -690,136 +690,136 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -828,14 +828,14 @@
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1501,7 +1501,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E162"/>
+  <dimension ref="A1:E163"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -3518,8 +3518,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="163" spans="1:3">
+      <c r="A163" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B163" t="s">
+        <v>41</v>
+      </c>
+      <c r="C163">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E161">
+  <autoFilter ref="A1:E162">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$162</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$163</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -224,8 +224,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -240,16 +247,15 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -263,9 +269,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -274,6 +279,13 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -288,22 +300,32 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -317,33 +339,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -369,7 +369,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -381,25 +507,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -411,13 +525,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -429,127 +549,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,6 +578,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -593,46 +602,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -661,6 +635,32 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -681,145 +681,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -828,14 +828,14 @@
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1501,7 +1501,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E163"/>
+  <dimension ref="A1:E164"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -3529,8 +3529,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="164" spans="1:3">
+      <c r="A164" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B164" t="s">
+        <v>41</v>
+      </c>
+      <c r="C164">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E162">
+  <autoFilter ref="A1:E163">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12450" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12420" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$163</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$164</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="25">
@@ -224,23 +224,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -254,8 +247,68 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -269,23 +322,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -307,50 +346,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -369,13 +369,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -393,19 +447,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -417,19 +507,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -441,37 +525,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -483,73 +543,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,6 +578,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -602,26 +617,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -631,6 +637,15 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -660,166 +675,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -828,14 +828,14 @@
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -860,12 +860,12 @@
     <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
     <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
     <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="20% - アクセント 4" xfId="7" builtinId="42"/>
+    <cellStyle name="メモ" xfId="8" builtinId="10"/>
+    <cellStyle name="パーセント" xfId="9" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="10" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="11" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="12" builtinId="9"/>
     <cellStyle name="良い" xfId="13" builtinId="26"/>
     <cellStyle name="警告文" xfId="14" builtinId="11"/>
     <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
@@ -1501,7 +1501,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E164"/>
+  <dimension ref="A1:E163"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -3454,20 +3454,20 @@
     </row>
     <row r="157" spans="1:3">
       <c r="A157" s="1">
-        <v>46296</v>
-      </c>
-      <c r="B157" t="s">
-        <v>41</v>
-      </c>
-      <c r="C157">
-        <v>0</v>
+        <v>46311</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C157" s="8">
+        <v>6980400</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158" s="1">
-        <v>46297</v>
-      </c>
-      <c r="B158" t="s">
+        <v>46312</v>
+      </c>
+      <c r="B158" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C158">
@@ -3476,31 +3476,31 @@
     </row>
     <row r="159" spans="1:3">
       <c r="A159" s="1">
-        <v>46298</v>
-      </c>
-      <c r="B159" t="s">
+        <v>46313</v>
+      </c>
+      <c r="B159" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C159">
-        <v>51247017.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160" s="1">
-        <v>46299</v>
-      </c>
-      <c r="B160" t="s">
-        <v>41</v>
-      </c>
-      <c r="C160">
-        <v>3622500</v>
+        <v>46314</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C160" s="8">
+        <v>7233408</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161" s="1">
-        <v>46300</v>
-      </c>
-      <c r="B161" t="s">
+        <v>46315</v>
+      </c>
+      <c r="B161" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C161">
@@ -3509,9 +3509,9 @@
     </row>
     <row r="162" spans="1:3">
       <c r="A162" s="1">
-        <v>46301</v>
-      </c>
-      <c r="B162" t="s">
+        <v>46316</v>
+      </c>
+      <c r="B162" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C162">
@@ -3520,32 +3520,21 @@
     </row>
     <row r="163" spans="1:3">
       <c r="A163" s="1">
-        <v>46302</v>
-      </c>
-      <c r="B163" t="s">
-        <v>41</v>
-      </c>
-      <c r="C163">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3">
-      <c r="A164" s="1">
-        <v>46303</v>
-      </c>
-      <c r="B164" t="s">
-        <v>41</v>
-      </c>
-      <c r="C164">
-        <v>0</v>
+        <v>46317</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C163" s="8">
+        <v>7233408</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E163">
+  <autoFilter ref="A1:E164">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="店舗名エラー" error="店舗マスタの一覧にある店舗名を選択してください。" sqref="B2:B101 B102:B111 B112:B138 B139:B156">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="店舗名エラー" error="店舗マスタの一覧にある店舗名を選択してください。" sqref="B2:B101 B102:B111 B112:B138 B139:B155 B156:B163">
       <formula1>店舗マスタ!$A$2:$A$31</formula1>
     </dataValidation>
   </dataValidations>

--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12420" activeTab="2"/>
+    <workbookView windowWidth="28125" windowHeight="12450" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -211,91 +211,16 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -316,15 +241,14 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -338,6 +262,36 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -347,10 +301,56 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -369,7 +369,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -381,49 +501,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -435,121 +543,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -579,6 +579,41 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -597,46 +632,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -645,17 +641,6 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -675,151 +660,166 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -828,14 +828,14 @@
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -860,12 +860,12 @@
     <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
     <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
     <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="20% - アクセント 4" xfId="7" builtinId="42"/>
-    <cellStyle name="メモ" xfId="8" builtinId="10"/>
-    <cellStyle name="パーセント" xfId="9" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="10" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="11" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="12" builtinId="9"/>
+    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
+    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
+    <cellStyle name="メモ" xfId="12" builtinId="10"/>
     <cellStyle name="良い" xfId="13" builtinId="26"/>
     <cellStyle name="警告文" xfId="14" builtinId="11"/>
     <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
@@ -1501,7 +1501,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E163"/>
+  <dimension ref="A1:E164"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -3527,6 +3527,17 @@
       </c>
       <c r="C163" s="8">
         <v>7233408</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3">
+      <c r="A164" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B164" t="s">
+        <v>41</v>
+      </c>
+      <c r="C164">
+        <v>22521190</v>
       </c>
     </row>
   </sheetData>

--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -211,6 +211,52 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -224,16 +270,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -248,7 +310,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -263,77 +325,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -348,7 +340,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -369,7 +369,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -381,31 +513,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -417,31 +525,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -453,103 +537,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,6 +578,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -596,18 +620,7 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -630,9 +643,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -640,8 +655,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -660,166 +675,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -828,14 +828,14 @@
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1501,7 +1501,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E164"/>
+  <dimension ref="A1:E165"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -3538,6 +3538,17 @@
       </c>
       <c r="C164">
         <v>22521190</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3">
+      <c r="A165" s="1">
+        <v>46305</v>
+      </c>
+      <c r="B165" t="s">
+        <v>41</v>
+      </c>
+      <c r="C165">
+        <v>1954040</v>
       </c>
     </row>
   </sheetData>

--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$165</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -211,7 +211,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -225,39 +233,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -278,24 +255,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,8 +271,53 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -324,15 +331,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -340,7 +340,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -369,7 +369,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -381,49 +393,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -435,19 +411,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -471,25 +435,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -501,7 +495,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -513,43 +549,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,15 +578,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -602,6 +593,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -613,15 +613,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -643,10 +634,17 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -654,9 +652,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -681,145 +681,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -828,14 +828,14 @@
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1501,7 +1501,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E165"/>
+  <dimension ref="A1:E166"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -3551,8 +3551,19 @@
         <v>1954040</v>
       </c>
     </row>
+    <row r="166" spans="1:3">
+      <c r="A166" s="1">
+        <v>46306</v>
+      </c>
+      <c r="B166" t="s">
+        <v>41</v>
+      </c>
+      <c r="C166">
+        <v>27742578</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E164">
+  <autoFilter ref="A1:E165">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$166</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="25">
@@ -219,7 +219,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -233,8 +233,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -247,9 +248,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -263,17 +270,33 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -294,7 +317,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -308,47 +347,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -369,7 +369,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -381,7 +381,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -399,7 +405,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -411,13 +423,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -435,7 +453,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -447,7 +465,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -459,7 +477,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -471,25 +489,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -501,13 +519,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -519,7 +531,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -531,25 +543,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,6 +578,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -596,8 +607,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -617,6 +628,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -628,35 +648,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -675,151 +666,160 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -1501,7 +1501,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E166"/>
+  <dimension ref="A1:E167"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -3562,8 +3562,19 @@
         <v>27742578</v>
       </c>
     </row>
+    <row r="167" spans="1:3">
+      <c r="A167" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B167" t="s">
+        <v>41</v>
+      </c>
+      <c r="C167">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E165">
+  <autoFilter ref="A1:E166">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12450" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$166</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$167</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -210,8 +210,39 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -220,6 +251,65 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -235,43 +325,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -279,7 +332,7 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -294,61 +347,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -369,7 +369,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -381,7 +393,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -393,13 +447,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -411,109 +513,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -531,25 +543,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,13 +578,32 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -606,24 +625,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -633,6 +639,15 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -652,26 +667,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -681,145 +681,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -828,14 +828,14 @@
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1501,7 +1501,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E167"/>
+  <dimension ref="A1:E168"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -3573,8 +3573,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="168" spans="1:3">
+      <c r="A168" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B168" t="s">
+        <v>41</v>
+      </c>
+      <c r="C168">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E166">
+  <autoFilter ref="A1:E167">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$167</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$168</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -210,21 +210,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -233,41 +218,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -285,13 +239,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -300,16 +247,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -317,9 +264,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -339,16 +286,69 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -369,7 +369,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -381,25 +393,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -417,7 +417,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -429,25 +489,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -459,19 +519,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -483,73 +543,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,17 +578,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -608,21 +602,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -630,24 +609,6 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -675,151 +636,190 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -828,14 +828,14 @@
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1501,7 +1501,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E168"/>
+  <dimension ref="A1:E169"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -3584,8 +3584,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="169" spans="1:3">
+      <c r="A169" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B169" t="s">
+        <v>41</v>
+      </c>
+      <c r="C169">
+        <v>6054300</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E167">
+  <autoFilter ref="A1:E168">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$168</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$169</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,9 +164,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
@@ -211,17 +211,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -232,6 +224,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -239,8 +248,67 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -256,15 +324,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -283,66 +343,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -369,7 +369,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -381,7 +387,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -393,13 +471,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -411,25 +507,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -441,13 +525,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -459,97 +549,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -587,21 +587,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -609,30 +594,6 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -661,6 +622,45 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -681,145 +681,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -1501,7 +1501,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E169"/>
+  <dimension ref="A1:E170"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -3595,8 +3595,19 @@
         <v>6054300</v>
       </c>
     </row>
+    <row r="170" spans="1:3">
+      <c r="A170" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B170" t="s">
+        <v>41</v>
+      </c>
+      <c r="C170">
+        <v>7508592</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E168">
+  <autoFilter ref="A1:E169">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\KYOYU-PC\Users\ビッグボス画像共有フォルダ\【迷惑メール】開いたら危険！\incoming\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A53BB2E5-0058-4338-9505-F596167348F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="2"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -19,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -162,15 +168,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -210,151 +212,14 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="6"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -367,194 +232,8 @@
         <bgColor rgb="FF4E79A7"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -577,251 +256,9 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -839,7 +276,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -852,62 +289,18 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
-    <cellStyle name="桁区切り[0]" xfId="1" builtinId="6"/>
-    <cellStyle name="入力" xfId="2" builtinId="20"/>
-    <cellStyle name="桁区切り" xfId="3" builtinId="3"/>
-    <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
-    <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
-    <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
-    <cellStyle name="良い" xfId="13" builtinId="26"/>
-    <cellStyle name="警告文" xfId="14" builtinId="11"/>
-    <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
-    <cellStyle name="タイトル" xfId="16" builtinId="15"/>
-    <cellStyle name="説明文" xfId="17" builtinId="53"/>
-    <cellStyle name="アクセント 6" xfId="18" builtinId="49"/>
-    <cellStyle name="出力" xfId="19" builtinId="21"/>
-    <cellStyle name="見出し 1" xfId="20" builtinId="16"/>
-    <cellStyle name="見出し 2" xfId="21" builtinId="17"/>
-    <cellStyle name="計算" xfId="22" builtinId="22"/>
-    <cellStyle name="見出し 3" xfId="23" builtinId="18"/>
-    <cellStyle name="見出し 4" xfId="24" builtinId="19"/>
-    <cellStyle name="60% - アクセント 5" xfId="25" builtinId="48"/>
-    <cellStyle name="チェックセル" xfId="26" builtinId="23"/>
-    <cellStyle name="40% - アクセント 1" xfId="27" builtinId="31"/>
-    <cellStyle name="集計" xfId="28" builtinId="25"/>
-    <cellStyle name="悪い" xfId="29" builtinId="27"/>
-    <cellStyle name="どちらでもない" xfId="30" builtinId="28"/>
-    <cellStyle name="アクセント 1" xfId="31" builtinId="29"/>
-    <cellStyle name="20% - アクセント 1" xfId="32" builtinId="30"/>
-    <cellStyle name="20% - アクセント 5" xfId="33" builtinId="46"/>
-    <cellStyle name="60% - アクセント 1" xfId="34" builtinId="32"/>
-    <cellStyle name="20% - アクセント 2" xfId="35" builtinId="34"/>
-    <cellStyle name="40% - アクセント 2" xfId="36" builtinId="35"/>
-    <cellStyle name="20% - アクセント 6" xfId="37" builtinId="50"/>
-    <cellStyle name="60% - アクセント 2" xfId="38" builtinId="36"/>
-    <cellStyle name="アクセント 3" xfId="39" builtinId="37"/>
-    <cellStyle name="20% - アクセント 3" xfId="40" builtinId="38"/>
-    <cellStyle name="40% - アクセント 3" xfId="41" builtinId="39"/>
-    <cellStyle name="60% - アクセント 3" xfId="42" builtinId="40"/>
-    <cellStyle name="アクセント 4" xfId="43" builtinId="41"/>
-    <cellStyle name="40% - アクセント 4" xfId="44" builtinId="43"/>
-    <cellStyle name="60% - アクセント 4" xfId="45" builtinId="44"/>
-    <cellStyle name="アクセント 5" xfId="46" builtinId="45"/>
-    <cellStyle name="40% - アクセント 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - アクセント 6" xfId="48" builtinId="52"/>
-    <cellStyle name="標準 2" xfId="49"/>
+    <cellStyle name="標準 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1192,317 +585,316 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" spans="1:1">
+    <row r="1" spans="1:1" ht="17.25" x14ac:dyDescent="0.15">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A2" s="10"/>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A4" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A5" s="10"/>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A6" s="10" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A8" s="10" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A9" s="10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A10" s="10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A11" s="10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A12" s="10"/>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A13" s="10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A14" s="10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A15" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A16" s="10"/>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A17" s="11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A18" s="10" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A19" s="10" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A20" s="10" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A21" s="10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A22" s="10" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A23" s="10" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A24" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A25" s="10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A26" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A27" s="10"/>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A28" s="11" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A29" s="10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A30" s="10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A31" s="10" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A32" s="10" t="s">
         <v>26</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A2" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A5" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A6" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A7" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A8" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A9" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A10" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A11" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A12" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A13" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A14" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A15" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A16" s="5"/>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A17" s="5"/>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A18" s="5"/>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A19" s="5"/>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A20" s="5"/>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A21" s="5"/>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A22" s="5"/>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A23" s="5"/>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A24" s="5"/>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A25" s="5"/>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A26" s="5"/>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A27" s="5"/>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A28" s="5"/>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A29" s="5"/>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A30" s="5"/>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A31" s="5"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E170"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:E163"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
     <col min="2" max="3" width="16" customWidth="1"/>
@@ -1510,7 +902,7 @@
     <col min="5" max="5" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>42</v>
       </c>
@@ -1527,7 +919,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" s="4">
         <v>45306</v>
       </c>
@@ -1540,7 +932,7 @@
       <c r="D2" s="6"/>
       <c r="E2" s="5"/>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" s="4">
         <v>45317</v>
       </c>
@@ -1553,7 +945,7 @@
       <c r="D3" s="6"/>
       <c r="E3" s="5"/>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4" s="4">
         <v>45327</v>
       </c>
@@ -1566,7 +958,7 @@
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5" s="4">
         <v>45353</v>
       </c>
@@ -1579,7 +971,7 @@
       <c r="D5" s="6"/>
       <c r="E5" s="5"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6" s="4">
         <v>45383</v>
       </c>
@@ -1592,7 +984,7 @@
       <c r="D6" s="6"/>
       <c r="E6" s="5"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" s="4">
         <v>45401</v>
       </c>
@@ -1605,7 +997,7 @@
       <c r="D7" s="6"/>
       <c r="E7" s="5"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A8" s="4">
         <v>45405</v>
       </c>
@@ -1618,7 +1010,7 @@
       <c r="D8" s="6"/>
       <c r="E8" s="5"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A9" s="4">
         <v>45428</v>
       </c>
@@ -1631,7 +1023,7 @@
       <c r="D9" s="6"/>
       <c r="E9" s="5"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A10" s="4">
         <v>45429</v>
       </c>
@@ -1644,7 +1036,7 @@
       <c r="D10" s="6"/>
       <c r="E10" s="5"/>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A11" s="4">
         <v>45432</v>
       </c>
@@ -1657,7 +1049,7 @@
       <c r="D11" s="6"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A12" s="4">
         <v>45433</v>
       </c>
@@ -1670,7 +1062,7 @@
       <c r="D12" s="6"/>
       <c r="E12" s="5"/>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A13" s="4">
         <v>45478</v>
       </c>
@@ -1683,7 +1075,7 @@
       <c r="D13" s="6"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A14" s="4">
         <v>45482</v>
       </c>
@@ -1696,7 +1088,7 @@
       <c r="D14" s="6"/>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A15" s="4">
         <v>45492</v>
       </c>
@@ -1709,7 +1101,7 @@
       <c r="D15" s="6"/>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A16" s="4">
         <v>45506</v>
       </c>
@@ -1722,7 +1114,7 @@
       <c r="D16" s="6"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A17" s="4">
         <v>45523</v>
       </c>
@@ -1735,7 +1127,7 @@
       <c r="D17" s="6"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A18" s="4">
         <v>45524</v>
       </c>
@@ -1748,7 +1140,7 @@
       <c r="D18" s="6"/>
       <c r="E18" s="5"/>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A19" s="4">
         <v>45573</v>
       </c>
@@ -1761,7 +1153,7 @@
       <c r="D19" s="6"/>
       <c r="E19" s="5"/>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A20" s="4">
         <v>45576</v>
       </c>
@@ -1774,7 +1166,7 @@
       <c r="D20" s="6"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A21" s="4">
         <v>45603</v>
       </c>
@@ -1787,7 +1179,7 @@
       <c r="D21" s="6"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A22" s="4">
         <v>45604</v>
       </c>
@@ -1800,7 +1192,7 @@
       <c r="D22" s="6"/>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A23" s="4">
         <v>45614</v>
       </c>
@@ -1813,7 +1205,7 @@
       <c r="D23" s="6"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A24" s="4">
         <v>45616</v>
       </c>
@@ -1826,7 +1218,7 @@
       <c r="D24" s="6"/>
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A25" s="4">
         <v>45622</v>
       </c>
@@ -1839,7 +1231,7 @@
       <c r="D25" s="6"/>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A26" s="4">
         <v>45623</v>
       </c>
@@ -1852,7 +1244,7 @@
       <c r="D26" s="6"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A27" s="4">
         <v>45629</v>
       </c>
@@ -1865,7 +1257,7 @@
       <c r="D27" s="6"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A28" s="4">
         <v>45638</v>
       </c>
@@ -1878,7 +1270,7 @@
       <c r="D28" s="6"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A29" s="4">
         <v>45639</v>
       </c>
@@ -1891,7 +1283,7 @@
       <c r="D29" s="6"/>
       <c r="E29" s="5"/>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A30" s="4">
         <v>45646</v>
       </c>
@@ -1904,7 +1296,7 @@
       <c r="D30" s="6"/>
       <c r="E30" s="5"/>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A31" s="4">
         <v>45649</v>
       </c>
@@ -1917,7 +1309,7 @@
       <c r="D31" s="6"/>
       <c r="E31" s="5"/>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A32" s="4">
         <v>45653</v>
       </c>
@@ -1930,7 +1322,7 @@
       <c r="D32" s="6"/>
       <c r="E32" s="5"/>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A33" s="4">
         <v>45663</v>
       </c>
@@ -1943,7 +1335,7 @@
       <c r="D33" s="6"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A34" s="4">
         <v>45681</v>
       </c>
@@ -1956,7 +1348,7 @@
       <c r="D34" s="6"/>
       <c r="E34" s="5"/>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A35" s="4">
         <v>45684</v>
       </c>
@@ -1969,7 +1361,7 @@
       <c r="D35" s="6"/>
       <c r="E35" s="5"/>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A36" s="4">
         <v>45685</v>
       </c>
@@ -1982,7 +1374,7 @@
       <c r="D36" s="6"/>
       <c r="E36" s="5"/>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A37" s="4">
         <v>45687</v>
       </c>
@@ -1995,7 +1387,7 @@
       <c r="D37" s="6"/>
       <c r="E37" s="5"/>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A38" s="4">
         <v>45698</v>
       </c>
@@ -2008,7 +1400,7 @@
       <c r="D38" s="6"/>
       <c r="E38" s="5"/>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A39" s="4">
         <v>45705</v>
       </c>
@@ -2021,7 +1413,7 @@
       <c r="D39" s="6"/>
       <c r="E39" s="5"/>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A40" s="4">
         <v>45713</v>
       </c>
@@ -2034,7 +1426,7 @@
       <c r="D40" s="6"/>
       <c r="E40" s="5"/>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A41" s="4">
         <v>45716</v>
       </c>
@@ -2047,7 +1439,7 @@
       <c r="D41" s="6"/>
       <c r="E41" s="5"/>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A42" s="4">
         <v>45722</v>
       </c>
@@ -2060,7 +1452,7 @@
       <c r="D42" s="6"/>
       <c r="E42" s="5"/>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A43" s="4">
         <v>45723</v>
       </c>
@@ -2073,7 +1465,7 @@
       <c r="D43" s="6"/>
       <c r="E43" s="5"/>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A44" s="4">
         <v>45733</v>
       </c>
@@ -2086,7 +1478,7 @@
       <c r="D44" s="6"/>
       <c r="E44" s="5"/>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A45" s="4">
         <v>45734</v>
       </c>
@@ -2099,7 +1491,7 @@
       <c r="D45" s="6"/>
       <c r="E45" s="5"/>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A46" s="4">
         <v>45735</v>
       </c>
@@ -2112,7 +1504,7 @@
       <c r="D46" s="6"/>
       <c r="E46" s="5"/>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A47" s="4">
         <v>45737</v>
       </c>
@@ -2125,7 +1517,7 @@
       <c r="D47" s="6"/>
       <c r="E47" s="5"/>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A48" s="4">
         <v>45740</v>
       </c>
@@ -2138,7 +1530,7 @@
       <c r="D48" s="6"/>
       <c r="E48" s="5"/>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A49" s="4">
         <v>45743</v>
       </c>
@@ -2151,7 +1543,7 @@
       <c r="D49" s="6"/>
       <c r="E49" s="5"/>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A50" s="4">
         <v>45756</v>
       </c>
@@ -2164,7 +1556,7 @@
       <c r="D50" s="6"/>
       <c r="E50" s="5"/>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A51" s="4">
         <v>45818</v>
       </c>
@@ -2177,7 +1569,7 @@
       <c r="D51" s="6"/>
       <c r="E51" s="5"/>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A52" s="4">
         <v>45819</v>
       </c>
@@ -2190,7 +1582,7 @@
       <c r="D52" s="6"/>
       <c r="E52" s="5"/>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A53" s="4">
         <v>45826</v>
       </c>
@@ -2203,7 +1595,7 @@
       <c r="D53" s="6"/>
       <c r="E53" s="5"/>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A54" s="4">
         <v>45835</v>
       </c>
@@ -2216,7 +1608,7 @@
       <c r="D54" s="6"/>
       <c r="E54" s="5"/>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A55" s="4">
         <v>45842</v>
       </c>
@@ -2229,7 +1621,7 @@
       <c r="D55" s="6"/>
       <c r="E55" s="5"/>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A56" s="4">
         <v>45857</v>
       </c>
@@ -2242,7 +1634,7 @@
       <c r="D56" s="6"/>
       <c r="E56" s="5"/>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A57" s="4">
         <v>45867</v>
       </c>
@@ -2255,7 +1647,7 @@
       <c r="D57" s="6"/>
       <c r="E57" s="5"/>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A58" s="4">
         <v>45879</v>
       </c>
@@ -2268,7 +1660,7 @@
       <c r="D58" s="6"/>
       <c r="E58" s="5"/>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A59" s="4">
         <v>45889</v>
       </c>
@@ -2281,7 +1673,7 @@
       <c r="D59" s="6"/>
       <c r="E59" s="5"/>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A60" s="4">
         <v>45895</v>
       </c>
@@ -2294,7 +1686,7 @@
       <c r="D60" s="6"/>
       <c r="E60" s="5"/>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A61" s="4">
         <v>45923</v>
       </c>
@@ -2307,7 +1699,7 @@
       <c r="D61" s="6"/>
       <c r="E61" s="5"/>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A62" s="4">
         <v>45937</v>
       </c>
@@ -2320,7 +1712,7 @@
       <c r="D62" s="6"/>
       <c r="E62" s="5"/>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A63" s="4">
         <v>45940</v>
       </c>
@@ -2333,7 +1725,7 @@
       <c r="D63" s="6"/>
       <c r="E63" s="5"/>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A64" s="4">
         <v>45961</v>
       </c>
@@ -2346,7 +1738,7 @@
       <c r="D64" s="6"/>
       <c r="E64" s="5"/>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A65" s="4">
         <v>45966</v>
       </c>
@@ -2359,7 +1751,7 @@
       <c r="D65" s="6"/>
       <c r="E65" s="5"/>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A66" s="4">
         <v>45971</v>
       </c>
@@ -2372,7 +1764,7 @@
       <c r="D66" s="6"/>
       <c r="E66" s="5"/>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A67" s="4">
         <v>45994</v>
       </c>
@@ -2385,7 +1777,7 @@
       <c r="D67" s="6"/>
       <c r="E67" s="5"/>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A68" s="4">
         <v>45999</v>
       </c>
@@ -2398,7 +1790,7 @@
       <c r="D68" s="6"/>
       <c r="E68" s="5"/>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A69" s="4">
         <v>46014</v>
       </c>
@@ -2411,7 +1803,7 @@
       <c r="D69" s="6"/>
       <c r="E69" s="5"/>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A70" s="4">
         <v>46056</v>
       </c>
@@ -2424,7 +1816,7 @@
       <c r="D70" s="6"/>
       <c r="E70" s="5"/>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A71" s="4">
         <v>46069</v>
       </c>
@@ -2437,7 +1829,7 @@
       <c r="D71" s="6"/>
       <c r="E71" s="5"/>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A72" s="4">
         <v>46073</v>
       </c>
@@ -2450,7 +1842,7 @@
       <c r="D72" s="6"/>
       <c r="E72" s="5"/>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A73" s="4">
         <v>46074</v>
       </c>
@@ -2463,7 +1855,7 @@
       <c r="D73" s="6"/>
       <c r="E73" s="5"/>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A74" s="4">
         <v>46080</v>
       </c>
@@ -2476,7 +1868,7 @@
       <c r="D74" s="6"/>
       <c r="E74" s="5"/>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A75" s="4">
         <v>46081</v>
       </c>
@@ -2489,7 +1881,7 @@
       <c r="D75" s="6"/>
       <c r="E75" s="5"/>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A76" s="4">
         <v>46084</v>
       </c>
@@ -2502,7 +1894,7 @@
       <c r="D76" s="6"/>
       <c r="E76" s="5"/>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A77" s="4">
         <v>46085</v>
       </c>
@@ -2515,7 +1907,7 @@
       <c r="D77" s="6"/>
       <c r="E77" s="5"/>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A78" s="4">
         <v>46087</v>
       </c>
@@ -2528,7 +1920,7 @@
       <c r="D78" s="6"/>
       <c r="E78" s="5"/>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A79" s="4">
         <v>46088</v>
       </c>
@@ -2541,7 +1933,7 @@
       <c r="D79" s="6"/>
       <c r="E79" s="5"/>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A80" s="4">
         <v>46126</v>
       </c>
@@ -2554,7 +1946,7 @@
       <c r="D80" s="6"/>
       <c r="E80" s="5"/>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A81" s="4">
         <v>46134</v>
       </c>
@@ -2567,7 +1959,7 @@
       <c r="D81" s="6"/>
       <c r="E81" s="5"/>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A82" s="4">
         <v>46140</v>
       </c>
@@ -2580,7 +1972,7 @@
       <c r="D82" s="6"/>
       <c r="E82" s="5"/>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A83" s="4">
         <v>46157</v>
       </c>
@@ -2593,7 +1985,7 @@
       <c r="D83" s="6"/>
       <c r="E83" s="5"/>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A84" s="4">
         <v>46175</v>
       </c>
@@ -2606,7 +1998,7 @@
       <c r="D84" s="6"/>
       <c r="E84" s="5"/>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A85" s="4">
         <v>46179</v>
       </c>
@@ -2619,7 +2011,7 @@
       <c r="D85" s="6"/>
       <c r="E85" s="5"/>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A86" s="4">
         <v>46181</v>
       </c>
@@ -2632,7 +2024,7 @@
       <c r="D86" s="6"/>
       <c r="E86" s="5"/>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A87" s="4">
         <v>46184</v>
       </c>
@@ -2645,7 +2037,7 @@
       <c r="D87" s="6"/>
       <c r="E87" s="5"/>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A88" s="4">
         <v>46185</v>
       </c>
@@ -2658,7 +2050,7 @@
       <c r="D88" s="6"/>
       <c r="E88" s="5"/>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A89" s="4">
         <v>46189</v>
       </c>
@@ -2671,7 +2063,7 @@
       <c r="D89" s="6"/>
       <c r="E89" s="5"/>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A90" s="4">
         <v>46196</v>
       </c>
@@ -2684,7 +2076,7 @@
       <c r="D90" s="6"/>
       <c r="E90" s="5"/>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A91" s="4">
         <v>46197</v>
       </c>
@@ -2697,7 +2089,7 @@
       <c r="D91" s="6"/>
       <c r="E91" s="5"/>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A92" s="4">
         <v>46205</v>
       </c>
@@ -2710,7 +2102,7 @@
       <c r="D92" s="6"/>
       <c r="E92" s="5"/>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A93" s="4">
         <v>46212</v>
       </c>
@@ -2723,7 +2115,7 @@
       <c r="D93" s="6"/>
       <c r="E93" s="5"/>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A94" s="4">
         <v>46214</v>
       </c>
@@ -2736,7 +2128,7 @@
       <c r="D94" s="6"/>
       <c r="E94" s="5"/>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A95" s="4">
         <v>46216</v>
       </c>
@@ -2749,7 +2141,7 @@
       <c r="D95" s="6"/>
       <c r="E95" s="5"/>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A96" s="4">
         <v>46219</v>
       </c>
@@ -2762,7 +2154,7 @@
       <c r="D96" s="6"/>
       <c r="E96" s="5"/>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A97" s="4">
         <v>46227</v>
       </c>
@@ -2775,7 +2167,7 @@
       <c r="D97" s="6"/>
       <c r="E97" s="5"/>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A98" s="4">
         <v>46239</v>
       </c>
@@ -2788,7 +2180,7 @@
       <c r="D98" s="6"/>
       <c r="E98" s="5"/>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A99" s="4">
         <v>46241</v>
       </c>
@@ -2801,7 +2193,7 @@
       <c r="D99" s="6"/>
       <c r="E99" s="5"/>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A100" s="4">
         <v>46244</v>
       </c>
@@ -2814,7 +2206,7 @@
       <c r="D100" s="6"/>
       <c r="E100" s="5"/>
     </row>
-    <row r="101" spans="1:5">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A101" s="4">
         <v>46246</v>
       </c>
@@ -2827,7 +2219,7 @@
       <c r="D101" s="6"/>
       <c r="E101" s="5"/>
     </row>
-    <row r="102" spans="1:5">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A102" s="4">
         <v>46248</v>
       </c>
@@ -2840,7 +2232,7 @@
       <c r="D102" s="6"/>
       <c r="E102" s="5"/>
     </row>
-    <row r="103" spans="1:5">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A103" s="4">
         <v>46249</v>
       </c>
@@ -2853,7 +2245,7 @@
       <c r="D103" s="6"/>
       <c r="E103" s="5"/>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A104" s="4">
         <v>46252</v>
       </c>
@@ -2866,7 +2258,7 @@
       <c r="D104" s="6"/>
       <c r="E104" s="5"/>
     </row>
-    <row r="105" spans="1:5">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A105" s="4">
         <v>46256</v>
       </c>
@@ -2879,7 +2271,7 @@
       <c r="D105" s="6"/>
       <c r="E105" s="5"/>
     </row>
-    <row r="106" spans="1:5">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A106" s="4">
         <v>46258</v>
       </c>
@@ -2892,7 +2284,7 @@
       <c r="D106" s="6"/>
       <c r="E106" s="5"/>
     </row>
-    <row r="107" spans="1:5">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A107" s="4">
         <v>46259</v>
       </c>
@@ -2905,7 +2297,7 @@
       <c r="D107" s="6"/>
       <c r="E107" s="5"/>
     </row>
-    <row r="108" spans="1:5">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A108" s="4">
         <v>46260</v>
       </c>
@@ -2918,7 +2310,7 @@
       <c r="D108" s="6"/>
       <c r="E108" s="5"/>
     </row>
-    <row r="109" spans="1:5">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A109" s="4">
         <v>46262</v>
       </c>
@@ -2931,7 +2323,7 @@
       <c r="D109" s="6"/>
       <c r="E109" s="5"/>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A110" s="4">
         <v>46263</v>
       </c>
@@ -2944,7 +2336,7 @@
       <c r="D110" s="6"/>
       <c r="E110" s="5"/>
     </row>
-    <row r="111" spans="1:5">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A111" s="4">
         <v>46265</v>
       </c>
@@ -2957,7 +2349,7 @@
       <c r="D111" s="6"/>
       <c r="E111" s="5"/>
     </row>
-    <row r="112" spans="1:3">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A112" s="4">
         <v>46266</v>
       </c>
@@ -2968,7 +2360,7 @@
         <v>7508592</v>
       </c>
     </row>
-    <row r="113" spans="1:3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A113" s="4">
         <v>46267</v>
       </c>
@@ -2979,7 +2371,7 @@
         <v>1954040</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A114" s="4">
         <v>46268</v>
       </c>
@@ -2990,7 +2382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A115" s="4">
         <v>46269</v>
       </c>
@@ -3001,7 +2393,7 @@
         <v>9937899</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A116" s="4">
         <v>46270</v>
       </c>
@@ -3012,7 +2404,7 @@
         <v>1215900</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A117" s="4">
         <v>46271</v>
       </c>
@@ -3023,7 +2415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A118" s="4">
         <v>46272</v>
       </c>
@@ -3034,7 +2426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A119" s="4">
         <v>46273</v>
       </c>
@@ -3045,7 +2437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A120" s="4">
         <v>46274</v>
       </c>
@@ -3056,7 +2448,7 @@
         <v>15012598</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A121" s="4">
         <v>46275</v>
       </c>
@@ -3067,7 +2459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A122" s="4">
         <v>46276</v>
       </c>
@@ -3078,7 +2470,7 @@
         <v>10678532</v>
       </c>
     </row>
-    <row r="123" spans="1:3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A123" s="4">
         <v>46277</v>
       </c>
@@ -3089,7 +2481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A124" s="4">
         <v>46278</v>
       </c>
@@ -3100,7 +2492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A125" s="4">
         <v>46279</v>
       </c>
@@ -3111,7 +2503,7 @@
         <v>8131385</v>
       </c>
     </row>
-    <row r="126" spans="1:3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A126" s="4">
         <v>46280</v>
       </c>
@@ -3122,7 +2514,7 @@
         <v>7508592</v>
       </c>
     </row>
-    <row r="127" spans="1:3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A127" s="4">
         <v>46281</v>
       </c>
@@ -3133,7 +2525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A128" s="4">
         <v>46282</v>
       </c>
@@ -3144,7 +2536,7 @@
         <v>9915192</v>
       </c>
     </row>
-    <row r="129" spans="1:3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A129" s="4">
         <v>46283</v>
       </c>
@@ -3155,7 +2547,7 @@
         <v>17444398</v>
       </c>
     </row>
-    <row r="130" spans="1:3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A130" s="4">
         <v>46284</v>
       </c>
@@ -3166,7 +2558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A131" s="4">
         <v>46285</v>
       </c>
@@ -3177,7 +2569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A132" s="4">
         <v>46286</v>
       </c>
@@ -3188,7 +2580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A133" s="4">
         <v>46287</v>
       </c>
@@ -3199,7 +2591,7 @@
         <v>12679980</v>
       </c>
     </row>
-    <row r="134" spans="1:3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A134" s="4">
         <v>46288</v>
       </c>
@@ -3210,7 +2602,7 @@
         <v>17494397</v>
       </c>
     </row>
-    <row r="135" spans="1:3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A135" s="4">
         <v>46289</v>
       </c>
@@ -3221,7 +2613,7 @@
         <v>7508592</v>
       </c>
     </row>
-    <row r="136" spans="1:3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A136" s="4">
         <v>46290</v>
       </c>
@@ -3232,7 +2624,7 @@
         <v>19610598</v>
       </c>
     </row>
-    <row r="137" spans="1:3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A137" s="4">
         <v>46291</v>
       </c>
@@ -3243,7 +2635,7 @@
         <v>2406600</v>
       </c>
     </row>
-    <row r="138" spans="1:3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A138" s="4">
         <v>46292</v>
       </c>
@@ -3254,7 +2646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:3">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A139" s="4">
         <v>46293</v>
       </c>
@@ -3265,7 +2657,7 @@
         <v>8537156</v>
       </c>
     </row>
-    <row r="140" spans="1:3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A140" s="1">
         <v>46294</v>
       </c>
@@ -3276,7 +2668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A141" s="1">
         <v>46295</v>
       </c>
@@ -3287,7 +2679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A142" s="1">
         <v>46296</v>
       </c>
@@ -3298,7 +2690,7 @@
         <v>7233408</v>
       </c>
     </row>
-    <row r="143" spans="1:3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A143" s="1">
         <v>46297</v>
       </c>
@@ -3309,7 +2701,7 @@
         <v>7233408</v>
       </c>
     </row>
-    <row r="144" spans="1:3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A144" s="1">
         <v>46298</v>
       </c>
@@ -3320,7 +2712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A145" s="1">
         <v>46299</v>
       </c>
@@ -3331,7 +2723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A146" s="1">
         <v>46300</v>
       </c>
@@ -3342,7 +2734,7 @@
         <v>7233408</v>
       </c>
     </row>
-    <row r="147" spans="1:3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A147" s="1">
         <v>46301</v>
       </c>
@@ -3353,7 +2745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A148" s="1">
         <v>46302</v>
       </c>
@@ -3364,7 +2756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A149" s="1">
         <v>46303</v>
       </c>
@@ -3375,7 +2767,7 @@
         <v>7233408</v>
       </c>
     </row>
-    <row r="150" spans="1:3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A150" s="1">
         <v>46304</v>
       </c>
@@ -3386,7 +2778,7 @@
         <v>21542072</v>
       </c>
     </row>
-    <row r="151" spans="1:3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A151" s="1">
         <v>46305</v>
       </c>
@@ -3397,7 +2789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A152" s="1">
         <v>46306</v>
       </c>
@@ -3408,7 +2800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A153" s="1">
         <v>46307</v>
       </c>
@@ -3419,7 +2811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A154" s="1">
         <v>46308</v>
       </c>
@@ -3430,7 +2822,7 @@
         <v>7233408</v>
       </c>
     </row>
-    <row r="155" spans="1:3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A155" s="1">
         <v>46309</v>
       </c>
@@ -3441,7 +2833,7 @@
         <v>14536472</v>
       </c>
     </row>
-    <row r="156" spans="1:3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A156" s="1">
         <v>46310</v>
       </c>
@@ -3452,7 +2844,7 @@
         <v>7233408</v>
       </c>
     </row>
-    <row r="157" spans="1:3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A157" s="1">
         <v>46311</v>
       </c>
@@ -3463,7 +2855,7 @@
         <v>6980400</v>
       </c>
     </row>
-    <row r="158" spans="1:3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A158" s="1">
         <v>46312</v>
       </c>
@@ -3474,7 +2866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A159" s="1">
         <v>46313</v>
       </c>
@@ -3485,7 +2877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:3">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A160" s="1">
         <v>46314</v>
       </c>
@@ -3496,7 +2888,7 @@
         <v>7233408</v>
       </c>
     </row>
-    <row r="161" spans="1:3">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A161" s="1">
         <v>46315</v>
       </c>
@@ -3507,7 +2899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:3">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A162" s="1">
         <v>46316</v>
       </c>
@@ -3518,7 +2910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:3">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A163" s="1">
         <v>46317</v>
       </c>
@@ -3529,93 +2921,21 @@
         <v>7233408</v>
       </c>
     </row>
-    <row r="164" spans="1:3">
-      <c r="A164" s="1">
-        <v>46304</v>
-      </c>
-      <c r="B164" t="s">
-        <v>41</v>
-      </c>
-      <c r="C164">
-        <v>22521190</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3">
-      <c r="A165" s="1">
-        <v>46305</v>
-      </c>
-      <c r="B165" t="s">
-        <v>41</v>
-      </c>
-      <c r="C165">
-        <v>1954040</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3">
-      <c r="A166" s="1">
-        <v>46306</v>
-      </c>
-      <c r="B166" t="s">
-        <v>41</v>
-      </c>
-      <c r="C166">
-        <v>27742578</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3">
-      <c r="A167" s="1">
-        <v>46307</v>
-      </c>
-      <c r="B167" t="s">
-        <v>41</v>
-      </c>
-      <c r="C167">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3">
-      <c r="A168" s="1">
-        <v>46307</v>
-      </c>
-      <c r="B168" t="s">
-        <v>41</v>
-      </c>
-      <c r="C168">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3">
-      <c r="A169" s="1">
-        <v>46308</v>
-      </c>
-      <c r="B169" t="s">
-        <v>41</v>
-      </c>
-      <c r="C169">
-        <v>6054300</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3">
-      <c r="A170" s="1">
-        <v>46309</v>
-      </c>
-      <c r="B170" t="s">
-        <v>41</v>
-      </c>
-      <c r="C170">
-        <v>7508592</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E169">
-    <extLst/>
-  </autoFilter>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="店舗名エラー" error="店舗マスタの一覧にある店舗名を選択してください。" sqref="B2:B101 B102:B111 B112:B138 B139:B155 B156:B163">
-      <formula1>店舗マスタ!$A$2:$A$31</formula1>
-    </dataValidation>
-  </dataValidations>
+  <autoFilter ref="A1:E169" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <phoneticPr fontId="6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="店舗名エラー" error="店舗マスタの一覧にある店舗名を選択してください。" xr:uid="{00000000-0002-0000-0200-000000000000}">
+          <x14:formula1>
+            <xm:f>店舗マスタ!$A$2:$A$31</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B101 B102:B111 B112:B138 B139:B155 B156:B163</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\KYOYU-PC\Users\ビッグボス画像共有フォルダ\【迷惑メール】開いたら危険！\incoming\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A53BB2E5-0058-4338-9505-F596167348F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12420" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -25,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -168,11 +162,15 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -212,14 +210,151 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="6"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -232,8 +367,194 @@
         <bgColor rgb="FF4E79A7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -256,23 +577,265 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -289,18 +852,62 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
-    <cellStyle name="標準 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="桁区切り[0]" xfId="1" builtinId="6"/>
+    <cellStyle name="入力" xfId="2" builtinId="20"/>
+    <cellStyle name="桁区切り" xfId="3" builtinId="3"/>
+    <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
+    <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
+    <cellStyle name="通貨" xfId="6" builtinId="4"/>
+    <cellStyle name="20% - アクセント 4" xfId="7" builtinId="42"/>
+    <cellStyle name="メモ" xfId="8" builtinId="10"/>
+    <cellStyle name="パーセント" xfId="9" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="10" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="11" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="12" builtinId="9"/>
+    <cellStyle name="良い" xfId="13" builtinId="26"/>
+    <cellStyle name="警告文" xfId="14" builtinId="11"/>
+    <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
+    <cellStyle name="タイトル" xfId="16" builtinId="15"/>
+    <cellStyle name="説明文" xfId="17" builtinId="53"/>
+    <cellStyle name="アクセント 6" xfId="18" builtinId="49"/>
+    <cellStyle name="出力" xfId="19" builtinId="21"/>
+    <cellStyle name="見出し 1" xfId="20" builtinId="16"/>
+    <cellStyle name="見出し 2" xfId="21" builtinId="17"/>
+    <cellStyle name="計算" xfId="22" builtinId="22"/>
+    <cellStyle name="見出し 3" xfId="23" builtinId="18"/>
+    <cellStyle name="見出し 4" xfId="24" builtinId="19"/>
+    <cellStyle name="60% - アクセント 5" xfId="25" builtinId="48"/>
+    <cellStyle name="チェックセル" xfId="26" builtinId="23"/>
+    <cellStyle name="40% - アクセント 1" xfId="27" builtinId="31"/>
+    <cellStyle name="集計" xfId="28" builtinId="25"/>
+    <cellStyle name="悪い" xfId="29" builtinId="27"/>
+    <cellStyle name="どちらでもない" xfId="30" builtinId="28"/>
+    <cellStyle name="アクセント 1" xfId="31" builtinId="29"/>
+    <cellStyle name="20% - アクセント 1" xfId="32" builtinId="30"/>
+    <cellStyle name="20% - アクセント 5" xfId="33" builtinId="46"/>
+    <cellStyle name="60% - アクセント 1" xfId="34" builtinId="32"/>
+    <cellStyle name="20% - アクセント 2" xfId="35" builtinId="34"/>
+    <cellStyle name="40% - アクセント 2" xfId="36" builtinId="35"/>
+    <cellStyle name="20% - アクセント 6" xfId="37" builtinId="50"/>
+    <cellStyle name="60% - アクセント 2" xfId="38" builtinId="36"/>
+    <cellStyle name="アクセント 3" xfId="39" builtinId="37"/>
+    <cellStyle name="20% - アクセント 3" xfId="40" builtinId="38"/>
+    <cellStyle name="40% - アクセント 3" xfId="41" builtinId="39"/>
+    <cellStyle name="60% - アクセント 3" xfId="42" builtinId="40"/>
+    <cellStyle name="アクセント 4" xfId="43" builtinId="41"/>
+    <cellStyle name="40% - アクセント 4" xfId="44" builtinId="43"/>
+    <cellStyle name="60% - アクセント 4" xfId="45" builtinId="44"/>
+    <cellStyle name="アクセント 5" xfId="46" builtinId="45"/>
+    <cellStyle name="40% - アクセント 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - アクセント 6" xfId="48" builtinId="52"/>
+    <cellStyle name="標準 2" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -585,316 +1192,318 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:A32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="17.25" x14ac:dyDescent="0.15">
+    <row r="1" ht="17.25" spans="1:1">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:1">
       <c r="A2" s="10"/>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:1">
       <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:1">
       <c r="A4" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:1">
       <c r="A5" s="10"/>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:1">
       <c r="A6" s="10" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:1">
       <c r="A7" s="10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:1">
       <c r="A8" s="10" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:1">
       <c r="A9" s="10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:1">
       <c r="A10" s="10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:1">
       <c r="A11" s="10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:1">
       <c r="A12" s="10"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:1">
       <c r="A13" s="10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:1">
       <c r="A14" s="10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:1">
       <c r="A15" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:1">
       <c r="A16" s="10"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:1">
       <c r="A17" s="11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:1">
       <c r="A18" s="10" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:1">
       <c r="A19" s="10" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:1">
       <c r="A20" s="10" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:1">
       <c r="A21" s="10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:1">
       <c r="A22" s="10" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:1">
       <c r="A23" s="10" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:1">
       <c r="A24" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:1">
       <c r="A25" s="10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:1">
       <c r="A26" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:1">
       <c r="A27" s="10"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:1">
       <c r="A28" s="11" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:1">
       <c r="A29" s="10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:1">
       <c r="A30" s="10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:1">
       <c r="A31" s="10" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:1">
       <c r="A32" s="10" t="s">
         <v>26</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:A31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:1">
       <c r="A1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:1">
       <c r="A2" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:1">
       <c r="A3" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:1">
       <c r="A4" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:1">
       <c r="A5" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:1">
       <c r="A6" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:1">
       <c r="A7" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:1">
       <c r="A8" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:1">
       <c r="A9" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:1">
       <c r="A10" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:1">
       <c r="A11" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:1">
       <c r="A12" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:1">
       <c r="A13" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:1">
       <c r="A14" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:1">
       <c r="A15" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:1">
       <c r="A16" s="5"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:1">
       <c r="A17" s="5"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:1">
       <c r="A18" s="5"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:1">
       <c r="A19" s="5"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:1">
       <c r="A20" s="5"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:1">
       <c r="A21" s="5"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:1">
       <c r="A22" s="5"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:1">
       <c r="A23" s="5"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:1">
       <c r="A24" s="5"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:1">
       <c r="A25" s="5"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:1">
       <c r="A26" s="5"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:1">
       <c r="A27" s="5"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:1">
       <c r="A28" s="5"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:1">
       <c r="A29" s="5"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:1">
       <c r="A30" s="5"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:1">
       <c r="A31" s="5"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E163"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E170"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
     <col min="2" max="3" width="16" customWidth="1"/>
@@ -902,7 +1511,7 @@
     <col min="5" max="5" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>42</v>
       </c>
@@ -919,7 +1528,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:5">
       <c r="A2" s="4">
         <v>45306</v>
       </c>
@@ -932,7 +1541,7 @@
       <c r="D2" s="6"/>
       <c r="E2" s="5"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:5">
       <c r="A3" s="4">
         <v>45317</v>
       </c>
@@ -945,7 +1554,7 @@
       <c r="D3" s="6"/>
       <c r="E3" s="5"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:5">
       <c r="A4" s="4">
         <v>45327</v>
       </c>
@@ -958,7 +1567,7 @@
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:5">
       <c r="A5" s="4">
         <v>45353</v>
       </c>
@@ -971,7 +1580,7 @@
       <c r="D5" s="6"/>
       <c r="E5" s="5"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:5">
       <c r="A6" s="4">
         <v>45383</v>
       </c>
@@ -984,7 +1593,7 @@
       <c r="D6" s="6"/>
       <c r="E6" s="5"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:5">
       <c r="A7" s="4">
         <v>45401</v>
       </c>
@@ -997,7 +1606,7 @@
       <c r="D7" s="6"/>
       <c r="E7" s="5"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:5">
       <c r="A8" s="4">
         <v>45405</v>
       </c>
@@ -1010,7 +1619,7 @@
       <c r="D8" s="6"/>
       <c r="E8" s="5"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:5">
       <c r="A9" s="4">
         <v>45428</v>
       </c>
@@ -1023,7 +1632,7 @@
       <c r="D9" s="6"/>
       <c r="E9" s="5"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:5">
       <c r="A10" s="4">
         <v>45429</v>
       </c>
@@ -1036,7 +1645,7 @@
       <c r="D10" s="6"/>
       <c r="E10" s="5"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:5">
       <c r="A11" s="4">
         <v>45432</v>
       </c>
@@ -1049,7 +1658,7 @@
       <c r="D11" s="6"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:5">
       <c r="A12" s="4">
         <v>45433</v>
       </c>
@@ -1062,7 +1671,7 @@
       <c r="D12" s="6"/>
       <c r="E12" s="5"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:5">
       <c r="A13" s="4">
         <v>45478</v>
       </c>
@@ -1075,7 +1684,7 @@
       <c r="D13" s="6"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:5">
       <c r="A14" s="4">
         <v>45482</v>
       </c>
@@ -1088,7 +1697,7 @@
       <c r="D14" s="6"/>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:5">
       <c r="A15" s="4">
         <v>45492</v>
       </c>
@@ -1101,7 +1710,7 @@
       <c r="D15" s="6"/>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:5">
       <c r="A16" s="4">
         <v>45506</v>
       </c>
@@ -1114,7 +1723,7 @@
       <c r="D16" s="6"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:5">
       <c r="A17" s="4">
         <v>45523</v>
       </c>
@@ -1127,7 +1736,7 @@
       <c r="D17" s="6"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:5">
       <c r="A18" s="4">
         <v>45524</v>
       </c>
@@ -1140,7 +1749,7 @@
       <c r="D18" s="6"/>
       <c r="E18" s="5"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:5">
       <c r="A19" s="4">
         <v>45573</v>
       </c>
@@ -1153,7 +1762,7 @@
       <c r="D19" s="6"/>
       <c r="E19" s="5"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:5">
       <c r="A20" s="4">
         <v>45576</v>
       </c>
@@ -1166,7 +1775,7 @@
       <c r="D20" s="6"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:5">
       <c r="A21" s="4">
         <v>45603</v>
       </c>
@@ -1179,7 +1788,7 @@
       <c r="D21" s="6"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:5">
       <c r="A22" s="4">
         <v>45604</v>
       </c>
@@ -1192,7 +1801,7 @@
       <c r="D22" s="6"/>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:5">
       <c r="A23" s="4">
         <v>45614</v>
       </c>
@@ -1205,7 +1814,7 @@
       <c r="D23" s="6"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:5">
       <c r="A24" s="4">
         <v>45616</v>
       </c>
@@ -1218,7 +1827,7 @@
       <c r="D24" s="6"/>
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:5">
       <c r="A25" s="4">
         <v>45622</v>
       </c>
@@ -1231,7 +1840,7 @@
       <c r="D25" s="6"/>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:5">
       <c r="A26" s="4">
         <v>45623</v>
       </c>
@@ -1244,7 +1853,7 @@
       <c r="D26" s="6"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:5">
       <c r="A27" s="4">
         <v>45629</v>
       </c>
@@ -1257,7 +1866,7 @@
       <c r="D27" s="6"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:5">
       <c r="A28" s="4">
         <v>45638</v>
       </c>
@@ -1270,7 +1879,7 @@
       <c r="D28" s="6"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:5">
       <c r="A29" s="4">
         <v>45639</v>
       </c>
@@ -1283,7 +1892,7 @@
       <c r="D29" s="6"/>
       <c r="E29" s="5"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:5">
       <c r="A30" s="4">
         <v>45646</v>
       </c>
@@ -1296,7 +1905,7 @@
       <c r="D30" s="6"/>
       <c r="E30" s="5"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:5">
       <c r="A31" s="4">
         <v>45649</v>
       </c>
@@ -1309,7 +1918,7 @@
       <c r="D31" s="6"/>
       <c r="E31" s="5"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:5">
       <c r="A32" s="4">
         <v>45653</v>
       </c>
@@ -1322,7 +1931,7 @@
       <c r="D32" s="6"/>
       <c r="E32" s="5"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:5">
       <c r="A33" s="4">
         <v>45663</v>
       </c>
@@ -1335,7 +1944,7 @@
       <c r="D33" s="6"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:5">
       <c r="A34" s="4">
         <v>45681</v>
       </c>
@@ -1348,7 +1957,7 @@
       <c r="D34" s="6"/>
       <c r="E34" s="5"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:5">
       <c r="A35" s="4">
         <v>45684</v>
       </c>
@@ -1361,7 +1970,7 @@
       <c r="D35" s="6"/>
       <c r="E35" s="5"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:5">
       <c r="A36" s="4">
         <v>45685</v>
       </c>
@@ -1374,7 +1983,7 @@
       <c r="D36" s="6"/>
       <c r="E36" s="5"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:5">
       <c r="A37" s="4">
         <v>45687</v>
       </c>
@@ -1387,7 +1996,7 @@
       <c r="D37" s="6"/>
       <c r="E37" s="5"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:5">
       <c r="A38" s="4">
         <v>45698</v>
       </c>
@@ -1400,7 +2009,7 @@
       <c r="D38" s="6"/>
       <c r="E38" s="5"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:5">
       <c r="A39" s="4">
         <v>45705</v>
       </c>
@@ -1413,7 +2022,7 @@
       <c r="D39" s="6"/>
       <c r="E39" s="5"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:5">
       <c r="A40" s="4">
         <v>45713</v>
       </c>
@@ -1426,7 +2035,7 @@
       <c r="D40" s="6"/>
       <c r="E40" s="5"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:5">
       <c r="A41" s="4">
         <v>45716</v>
       </c>
@@ -1439,7 +2048,7 @@
       <c r="D41" s="6"/>
       <c r="E41" s="5"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:5">
       <c r="A42" s="4">
         <v>45722</v>
       </c>
@@ -1452,7 +2061,7 @@
       <c r="D42" s="6"/>
       <c r="E42" s="5"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:5">
       <c r="A43" s="4">
         <v>45723</v>
       </c>
@@ -1465,7 +2074,7 @@
       <c r="D43" s="6"/>
       <c r="E43" s="5"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:5">
       <c r="A44" s="4">
         <v>45733</v>
       </c>
@@ -1478,7 +2087,7 @@
       <c r="D44" s="6"/>
       <c r="E44" s="5"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:5">
       <c r="A45" s="4">
         <v>45734</v>
       </c>
@@ -1491,7 +2100,7 @@
       <c r="D45" s="6"/>
       <c r="E45" s="5"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:5">
       <c r="A46" s="4">
         <v>45735</v>
       </c>
@@ -1504,7 +2113,7 @@
       <c r="D46" s="6"/>
       <c r="E46" s="5"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:5">
       <c r="A47" s="4">
         <v>45737</v>
       </c>
@@ -1517,7 +2126,7 @@
       <c r="D47" s="6"/>
       <c r="E47" s="5"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:5">
       <c r="A48" s="4">
         <v>45740</v>
       </c>
@@ -1530,7 +2139,7 @@
       <c r="D48" s="6"/>
       <c r="E48" s="5"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:5">
       <c r="A49" s="4">
         <v>45743</v>
       </c>
@@ -1543,7 +2152,7 @@
       <c r="D49" s="6"/>
       <c r="E49" s="5"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:5">
       <c r="A50" s="4">
         <v>45756</v>
       </c>
@@ -1556,7 +2165,7 @@
       <c r="D50" s="6"/>
       <c r="E50" s="5"/>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:5">
       <c r="A51" s="4">
         <v>45818</v>
       </c>
@@ -1569,7 +2178,7 @@
       <c r="D51" s="6"/>
       <c r="E51" s="5"/>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:5">
       <c r="A52" s="4">
         <v>45819</v>
       </c>
@@ -1582,7 +2191,7 @@
       <c r="D52" s="6"/>
       <c r="E52" s="5"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:5">
       <c r="A53" s="4">
         <v>45826</v>
       </c>
@@ -1595,7 +2204,7 @@
       <c r="D53" s="6"/>
       <c r="E53" s="5"/>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:5">
       <c r="A54" s="4">
         <v>45835</v>
       </c>
@@ -1608,7 +2217,7 @@
       <c r="D54" s="6"/>
       <c r="E54" s="5"/>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:5">
       <c r="A55" s="4">
         <v>45842</v>
       </c>
@@ -1621,7 +2230,7 @@
       <c r="D55" s="6"/>
       <c r="E55" s="5"/>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:5">
       <c r="A56" s="4">
         <v>45857</v>
       </c>
@@ -1634,7 +2243,7 @@
       <c r="D56" s="6"/>
       <c r="E56" s="5"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:5">
       <c r="A57" s="4">
         <v>45867</v>
       </c>
@@ -1647,7 +2256,7 @@
       <c r="D57" s="6"/>
       <c r="E57" s="5"/>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:5">
       <c r="A58" s="4">
         <v>45879</v>
       </c>
@@ -1660,7 +2269,7 @@
       <c r="D58" s="6"/>
       <c r="E58" s="5"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:5">
       <c r="A59" s="4">
         <v>45889</v>
       </c>
@@ -1673,7 +2282,7 @@
       <c r="D59" s="6"/>
       <c r="E59" s="5"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:5">
       <c r="A60" s="4">
         <v>45895</v>
       </c>
@@ -1686,7 +2295,7 @@
       <c r="D60" s="6"/>
       <c r="E60" s="5"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:5">
       <c r="A61" s="4">
         <v>45923</v>
       </c>
@@ -1699,7 +2308,7 @@
       <c r="D61" s="6"/>
       <c r="E61" s="5"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:5">
       <c r="A62" s="4">
         <v>45937</v>
       </c>
@@ -1712,7 +2321,7 @@
       <c r="D62" s="6"/>
       <c r="E62" s="5"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:5">
       <c r="A63" s="4">
         <v>45940</v>
       </c>
@@ -1725,7 +2334,7 @@
       <c r="D63" s="6"/>
       <c r="E63" s="5"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:5">
       <c r="A64" s="4">
         <v>45961</v>
       </c>
@@ -1738,7 +2347,7 @@
       <c r="D64" s="6"/>
       <c r="E64" s="5"/>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:5">
       <c r="A65" s="4">
         <v>45966</v>
       </c>
@@ -1751,7 +2360,7 @@
       <c r="D65" s="6"/>
       <c r="E65" s="5"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:5">
       <c r="A66" s="4">
         <v>45971</v>
       </c>
@@ -1764,7 +2373,7 @@
       <c r="D66" s="6"/>
       <c r="E66" s="5"/>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:5">
       <c r="A67" s="4">
         <v>45994</v>
       </c>
@@ -1777,7 +2386,7 @@
       <c r="D67" s="6"/>
       <c r="E67" s="5"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:5">
       <c r="A68" s="4">
         <v>45999</v>
       </c>
@@ -1790,7 +2399,7 @@
       <c r="D68" s="6"/>
       <c r="E68" s="5"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:5">
       <c r="A69" s="4">
         <v>46014</v>
       </c>
@@ -1803,7 +2412,7 @@
       <c r="D69" s="6"/>
       <c r="E69" s="5"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:5">
       <c r="A70" s="4">
         <v>46056</v>
       </c>
@@ -1816,7 +2425,7 @@
       <c r="D70" s="6"/>
       <c r="E70" s="5"/>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:5">
       <c r="A71" s="4">
         <v>46069</v>
       </c>
@@ -1829,7 +2438,7 @@
       <c r="D71" s="6"/>
       <c r="E71" s="5"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:5">
       <c r="A72" s="4">
         <v>46073</v>
       </c>
@@ -1842,7 +2451,7 @@
       <c r="D72" s="6"/>
       <c r="E72" s="5"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:5">
       <c r="A73" s="4">
         <v>46074</v>
       </c>
@@ -1855,7 +2464,7 @@
       <c r="D73" s="6"/>
       <c r="E73" s="5"/>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:5">
       <c r="A74" s="4">
         <v>46080</v>
       </c>
@@ -1868,7 +2477,7 @@
       <c r="D74" s="6"/>
       <c r="E74" s="5"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:5">
       <c r="A75" s="4">
         <v>46081</v>
       </c>
@@ -1881,7 +2490,7 @@
       <c r="D75" s="6"/>
       <c r="E75" s="5"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:5">
       <c r="A76" s="4">
         <v>46084</v>
       </c>
@@ -1894,7 +2503,7 @@
       <c r="D76" s="6"/>
       <c r="E76" s="5"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:5">
       <c r="A77" s="4">
         <v>46085</v>
       </c>
@@ -1907,7 +2516,7 @@
       <c r="D77" s="6"/>
       <c r="E77" s="5"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:5">
       <c r="A78" s="4">
         <v>46087</v>
       </c>
@@ -1920,7 +2529,7 @@
       <c r="D78" s="6"/>
       <c r="E78" s="5"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:5">
       <c r="A79" s="4">
         <v>46088</v>
       </c>
@@ -1933,7 +2542,7 @@
       <c r="D79" s="6"/>
       <c r="E79" s="5"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:5">
       <c r="A80" s="4">
         <v>46126</v>
       </c>
@@ -1946,7 +2555,7 @@
       <c r="D80" s="6"/>
       <c r="E80" s="5"/>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:5">
       <c r="A81" s="4">
         <v>46134</v>
       </c>
@@ -1959,7 +2568,7 @@
       <c r="D81" s="6"/>
       <c r="E81" s="5"/>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:5">
       <c r="A82" s="4">
         <v>46140</v>
       </c>
@@ -1972,7 +2581,7 @@
       <c r="D82" s="6"/>
       <c r="E82" s="5"/>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:5">
       <c r="A83" s="4">
         <v>46157</v>
       </c>
@@ -1985,7 +2594,7 @@
       <c r="D83" s="6"/>
       <c r="E83" s="5"/>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:5">
       <c r="A84" s="4">
         <v>46175</v>
       </c>
@@ -1998,7 +2607,7 @@
       <c r="D84" s="6"/>
       <c r="E84" s="5"/>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:5">
       <c r="A85" s="4">
         <v>46179</v>
       </c>
@@ -2011,7 +2620,7 @@
       <c r="D85" s="6"/>
       <c r="E85" s="5"/>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:5">
       <c r="A86" s="4">
         <v>46181</v>
       </c>
@@ -2024,7 +2633,7 @@
       <c r="D86" s="6"/>
       <c r="E86" s="5"/>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:5">
       <c r="A87" s="4">
         <v>46184</v>
       </c>
@@ -2037,7 +2646,7 @@
       <c r="D87" s="6"/>
       <c r="E87" s="5"/>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:5">
       <c r="A88" s="4">
         <v>46185</v>
       </c>
@@ -2050,7 +2659,7 @@
       <c r="D88" s="6"/>
       <c r="E88" s="5"/>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:5">
       <c r="A89" s="4">
         <v>46189</v>
       </c>
@@ -2063,7 +2672,7 @@
       <c r="D89" s="6"/>
       <c r="E89" s="5"/>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:5">
       <c r="A90" s="4">
         <v>46196</v>
       </c>
@@ -2076,7 +2685,7 @@
       <c r="D90" s="6"/>
       <c r="E90" s="5"/>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:5">
       <c r="A91" s="4">
         <v>46197</v>
       </c>
@@ -2089,7 +2698,7 @@
       <c r="D91" s="6"/>
       <c r="E91" s="5"/>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:5">
       <c r="A92" s="4">
         <v>46205</v>
       </c>
@@ -2102,7 +2711,7 @@
       <c r="D92" s="6"/>
       <c r="E92" s="5"/>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:5">
       <c r="A93" s="4">
         <v>46212</v>
       </c>
@@ -2115,7 +2724,7 @@
       <c r="D93" s="6"/>
       <c r="E93" s="5"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:5">
       <c r="A94" s="4">
         <v>46214</v>
       </c>
@@ -2128,7 +2737,7 @@
       <c r="D94" s="6"/>
       <c r="E94" s="5"/>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:5">
       <c r="A95" s="4">
         <v>46216</v>
       </c>
@@ -2141,7 +2750,7 @@
       <c r="D95" s="6"/>
       <c r="E95" s="5"/>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:5">
       <c r="A96" s="4">
         <v>46219</v>
       </c>
@@ -2154,7 +2763,7 @@
       <c r="D96" s="6"/>
       <c r="E96" s="5"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:5">
       <c r="A97" s="4">
         <v>46227</v>
       </c>
@@ -2167,7 +2776,7 @@
       <c r="D97" s="6"/>
       <c r="E97" s="5"/>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:5">
       <c r="A98" s="4">
         <v>46239</v>
       </c>
@@ -2180,7 +2789,7 @@
       <c r="D98" s="6"/>
       <c r="E98" s="5"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:5">
       <c r="A99" s="4">
         <v>46241</v>
       </c>
@@ -2193,7 +2802,7 @@
       <c r="D99" s="6"/>
       <c r="E99" s="5"/>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:5">
       <c r="A100" s="4">
         <v>46244</v>
       </c>
@@ -2206,7 +2815,7 @@
       <c r="D100" s="6"/>
       <c r="E100" s="5"/>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:5">
       <c r="A101" s="4">
         <v>46246</v>
       </c>
@@ -2219,7 +2828,7 @@
       <c r="D101" s="6"/>
       <c r="E101" s="5"/>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:5">
       <c r="A102" s="4">
         <v>46248</v>
       </c>
@@ -2232,7 +2841,7 @@
       <c r="D102" s="6"/>
       <c r="E102" s="5"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:5">
       <c r="A103" s="4">
         <v>46249</v>
       </c>
@@ -2245,7 +2854,7 @@
       <c r="D103" s="6"/>
       <c r="E103" s="5"/>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:5">
       <c r="A104" s="4">
         <v>46252</v>
       </c>
@@ -2258,7 +2867,7 @@
       <c r="D104" s="6"/>
       <c r="E104" s="5"/>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:5">
       <c r="A105" s="4">
         <v>46256</v>
       </c>
@@ -2271,7 +2880,7 @@
       <c r="D105" s="6"/>
       <c r="E105" s="5"/>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:5">
       <c r="A106" s="4">
         <v>46258</v>
       </c>
@@ -2284,7 +2893,7 @@
       <c r="D106" s="6"/>
       <c r="E106" s="5"/>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:5">
       <c r="A107" s="4">
         <v>46259</v>
       </c>
@@ -2297,7 +2906,7 @@
       <c r="D107" s="6"/>
       <c r="E107" s="5"/>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:5">
       <c r="A108" s="4">
         <v>46260</v>
       </c>
@@ -2310,7 +2919,7 @@
       <c r="D108" s="6"/>
       <c r="E108" s="5"/>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:5">
       <c r="A109" s="4">
         <v>46262</v>
       </c>
@@ -2323,7 +2932,7 @@
       <c r="D109" s="6"/>
       <c r="E109" s="5"/>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:5">
       <c r="A110" s="4">
         <v>46263</v>
       </c>
@@ -2336,7 +2945,7 @@
       <c r="D110" s="6"/>
       <c r="E110" s="5"/>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:5">
       <c r="A111" s="4">
         <v>46265</v>
       </c>
@@ -2349,7 +2958,7 @@
       <c r="D111" s="6"/>
       <c r="E111" s="5"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:3">
       <c r="A112" s="4">
         <v>46266</v>
       </c>
@@ -2360,7 +2969,7 @@
         <v>7508592</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:3">
       <c r="A113" s="4">
         <v>46267</v>
       </c>
@@ -2371,7 +2980,7 @@
         <v>1954040</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:3">
       <c r="A114" s="4">
         <v>46268</v>
       </c>
@@ -2382,7 +2991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:3">
       <c r="A115" s="4">
         <v>46269</v>
       </c>
@@ -2393,7 +3002,7 @@
         <v>9937899</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:3">
       <c r="A116" s="4">
         <v>46270</v>
       </c>
@@ -2404,7 +3013,7 @@
         <v>1215900</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:3">
       <c r="A117" s="4">
         <v>46271</v>
       </c>
@@ -2415,7 +3024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:3">
       <c r="A118" s="4">
         <v>46272</v>
       </c>
@@ -2426,7 +3035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:3">
       <c r="A119" s="4">
         <v>46273</v>
       </c>
@@ -2437,7 +3046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:3">
       <c r="A120" s="4">
         <v>46274</v>
       </c>
@@ -2448,7 +3057,7 @@
         <v>15012598</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:3">
       <c r="A121" s="4">
         <v>46275</v>
       </c>
@@ -2459,7 +3068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:3">
       <c r="A122" s="4">
         <v>46276</v>
       </c>
@@ -2470,7 +3079,7 @@
         <v>10678532</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:3">
       <c r="A123" s="4">
         <v>46277</v>
       </c>
@@ -2481,7 +3090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:3">
       <c r="A124" s="4">
         <v>46278</v>
       </c>
@@ -2492,7 +3101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:3">
       <c r="A125" s="4">
         <v>46279</v>
       </c>
@@ -2503,7 +3112,7 @@
         <v>8131385</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:3">
       <c r="A126" s="4">
         <v>46280</v>
       </c>
@@ -2514,7 +3123,7 @@
         <v>7508592</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:3">
       <c r="A127" s="4">
         <v>46281</v>
       </c>
@@ -2525,7 +3134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:3">
       <c r="A128" s="4">
         <v>46282</v>
       </c>
@@ -2536,7 +3145,7 @@
         <v>9915192</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:3">
       <c r="A129" s="4">
         <v>46283</v>
       </c>
@@ -2547,7 +3156,7 @@
         <v>17444398</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:3">
       <c r="A130" s="4">
         <v>46284</v>
       </c>
@@ -2558,7 +3167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:3">
       <c r="A131" s="4">
         <v>46285</v>
       </c>
@@ -2569,7 +3178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:3">
       <c r="A132" s="4">
         <v>46286</v>
       </c>
@@ -2580,7 +3189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:3">
       <c r="A133" s="4">
         <v>46287</v>
       </c>
@@ -2591,7 +3200,7 @@
         <v>12679980</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:3">
       <c r="A134" s="4">
         <v>46288</v>
       </c>
@@ -2602,7 +3211,7 @@
         <v>17494397</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:3">
       <c r="A135" s="4">
         <v>46289</v>
       </c>
@@ -2613,7 +3222,7 @@
         <v>7508592</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:3">
       <c r="A136" s="4">
         <v>46290</v>
       </c>
@@ -2624,7 +3233,7 @@
         <v>19610598</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:3">
       <c r="A137" s="4">
         <v>46291</v>
       </c>
@@ -2635,7 +3244,7 @@
         <v>2406600</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:3">
       <c r="A138" s="4">
         <v>46292</v>
       </c>
@@ -2646,7 +3255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:3">
       <c r="A139" s="4">
         <v>46293</v>
       </c>
@@ -2657,7 +3266,7 @@
         <v>8537156</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:3">
       <c r="A140" s="1">
         <v>46294</v>
       </c>
@@ -2668,7 +3277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:3">
       <c r="A141" s="1">
         <v>46295</v>
       </c>
@@ -2679,7 +3288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:3">
       <c r="A142" s="1">
         <v>46296</v>
       </c>
@@ -2690,7 +3299,7 @@
         <v>7233408</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:3">
       <c r="A143" s="1">
         <v>46297</v>
       </c>
@@ -2701,7 +3310,7 @@
         <v>7233408</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:3">
       <c r="A144" s="1">
         <v>46298</v>
       </c>
@@ -2712,7 +3321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:3">
       <c r="A145" s="1">
         <v>46299</v>
       </c>
@@ -2723,7 +3332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:3">
       <c r="A146" s="1">
         <v>46300</v>
       </c>
@@ -2734,7 +3343,7 @@
         <v>7233408</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:3">
       <c r="A147" s="1">
         <v>46301</v>
       </c>
@@ -2745,7 +3354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:3">
       <c r="A148" s="1">
         <v>46302</v>
       </c>
@@ -2756,7 +3365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:3">
       <c r="A149" s="1">
         <v>46303</v>
       </c>
@@ -2767,7 +3376,7 @@
         <v>7233408</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:3">
       <c r="A150" s="1">
         <v>46304</v>
       </c>
@@ -2778,7 +3387,7 @@
         <v>21542072</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:3">
       <c r="A151" s="1">
         <v>46305</v>
       </c>
@@ -2789,7 +3398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:3">
       <c r="A152" s="1">
         <v>46306</v>
       </c>
@@ -2800,7 +3409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:3">
       <c r="A153" s="1">
         <v>46307</v>
       </c>
@@ -2811,7 +3420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:3">
       <c r="A154" s="1">
         <v>46308</v>
       </c>
@@ -2822,7 +3431,7 @@
         <v>7233408</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:3">
       <c r="A155" s="1">
         <v>46309</v>
       </c>
@@ -2833,7 +3442,7 @@
         <v>14536472</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:3">
       <c r="A156" s="1">
         <v>46310</v>
       </c>
@@ -2844,7 +3453,7 @@
         <v>7233408</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:3">
       <c r="A157" s="1">
         <v>46311</v>
       </c>
@@ -2855,7 +3464,7 @@
         <v>6980400</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:3">
       <c r="A158" s="1">
         <v>46312</v>
       </c>
@@ -2866,7 +3475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:3">
       <c r="A159" s="1">
         <v>46313</v>
       </c>
@@ -2877,7 +3486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:3">
       <c r="A160" s="1">
         <v>46314</v>
       </c>
@@ -2888,7 +3497,7 @@
         <v>7233408</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:3">
       <c r="A161" s="1">
         <v>46315</v>
       </c>
@@ -2899,7 +3508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:3">
       <c r="A162" s="1">
         <v>46316</v>
       </c>
@@ -2910,7 +3519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:3">
       <c r="A163" s="1">
         <v>46317</v>
       </c>
@@ -2921,21 +3530,93 @@
         <v>7233408</v>
       </c>
     </row>
+    <row r="164" spans="1:3">
+      <c r="A164" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C164">
+        <v>6614640</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3">
+      <c r="A165" s="1">
+        <v>46319</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3">
+      <c r="A166" s="1">
+        <v>46320</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3">
+      <c r="A167" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C167">
+        <v>7233408</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3">
+      <c r="A168" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C168">
+        <v>11285986</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3">
+      <c r="A169" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3">
+      <c r="A170" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C170">
+        <v>7233408</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E169" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
-  <phoneticPr fontId="6"/>
+  <autoFilter ref="A1:E169">
+    <extLst/>
+  </autoFilter>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="店舗名エラー" error="店舗マスタの一覧にある店舗名を選択してください。" sqref="B2:B101 B102:B111 B112:B138 B139:B155 B156:B162 B163:B170">
+      <formula1>店舗マスタ!$A$2:$A$31</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="店舗名エラー" error="店舗マスタの一覧にある店舗名を選択してください。" xr:uid="{00000000-0002-0000-0200-000000000000}">
-          <x14:formula1>
-            <xm:f>店舗マスタ!$A$2:$A$31</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B101 B102:B111 B112:B138 B139:B155 B156:B163</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12420" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$170</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -210,13 +210,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -234,14 +227,74 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -255,26 +308,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -287,47 +332,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -343,14 +351,6 @@
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -369,7 +369,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -381,19 +501,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -405,127 +537,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -537,19 +549,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -641,8 +641,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -650,8 +650,17 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -666,167 +675,158 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -841,6 +841,12 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1205,152 +1211,152 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.25" spans="1:1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="10"/>
+      <c r="A2" s="12"/>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="12" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="10"/>
+      <c r="A5" s="12"/>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="12" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="12" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="12" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="12" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="10"/>
+      <c r="A12" s="12"/>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="12" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="12" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="12" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="10"/>
+      <c r="A16" s="12"/>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="13" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="12" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="12" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="12" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="12" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="12" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="12" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="12" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="12" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="12" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="10"/>
+      <c r="A27" s="12"/>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="10" t="s">
+      <c r="A29" s="12" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="10" t="s">
+      <c r="A30" s="12" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="10" t="s">
+      <c r="A31" s="12" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="10" t="s">
+      <c r="A32" s="12" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1502,7 +1508,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E170"/>
+  <dimension ref="A1:E171"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -3288,7 +3294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:3">
+    <row r="142" spans="1:4">
       <c r="A142" s="1">
         <v>46296</v>
       </c>
@@ -3298,8 +3304,9 @@
       <c r="C142" s="8">
         <v>7233408</v>
       </c>
-    </row>
-    <row r="143" spans="1:3">
+      <c r="D142" s="9"/>
+    </row>
+    <row r="143" spans="1:4">
       <c r="A143" s="1">
         <v>46297</v>
       </c>
@@ -3309,8 +3316,9 @@
       <c r="C143" s="8">
         <v>7233408</v>
       </c>
-    </row>
-    <row r="144" spans="1:3">
+      <c r="D143" s="9"/>
+    </row>
+    <row r="144" spans="1:4">
       <c r="A144" s="1">
         <v>46298</v>
       </c>
@@ -3320,8 +3328,9 @@
       <c r="C144">
         <v>0</v>
       </c>
-    </row>
-    <row r="145" spans="1:3">
+      <c r="D144" s="10"/>
+    </row>
+    <row r="145" spans="1:4">
       <c r="A145" s="1">
         <v>46299</v>
       </c>
@@ -3331,8 +3340,9 @@
       <c r="C145">
         <v>0</v>
       </c>
-    </row>
-    <row r="146" spans="1:3">
+      <c r="D145" s="10"/>
+    </row>
+    <row r="146" spans="1:4">
       <c r="A146" s="1">
         <v>46300</v>
       </c>
@@ -3342,8 +3352,9 @@
       <c r="C146" s="8">
         <v>7233408</v>
       </c>
-    </row>
-    <row r="147" spans="1:3">
+      <c r="D146" s="9"/>
+    </row>
+    <row r="147" spans="1:4">
       <c r="A147" s="1">
         <v>46301</v>
       </c>
@@ -3353,8 +3364,9 @@
       <c r="C147">
         <v>0</v>
       </c>
-    </row>
-    <row r="148" spans="1:3">
+      <c r="D147" s="10"/>
+    </row>
+    <row r="148" spans="1:4">
       <c r="A148" s="1">
         <v>46302</v>
       </c>
@@ -3364,8 +3376,9 @@
       <c r="C148">
         <v>0</v>
       </c>
-    </row>
-    <row r="149" spans="1:3">
+      <c r="D148" s="10"/>
+    </row>
+    <row r="149" spans="1:4">
       <c r="A149" s="1">
         <v>46303</v>
       </c>
@@ -3375,8 +3388,9 @@
       <c r="C149" s="8">
         <v>7233408</v>
       </c>
-    </row>
-    <row r="150" spans="1:3">
+      <c r="D149" s="9"/>
+    </row>
+    <row r="150" spans="1:4">
       <c r="A150" s="1">
         <v>46304</v>
       </c>
@@ -3386,8 +3400,9 @@
       <c r="C150" s="8">
         <v>21542072</v>
       </c>
-    </row>
-    <row r="151" spans="1:3">
+      <c r="D150" s="9"/>
+    </row>
+    <row r="151" spans="1:4">
       <c r="A151" s="1">
         <v>46305</v>
       </c>
@@ -3397,8 +3412,9 @@
       <c r="C151">
         <v>0</v>
       </c>
-    </row>
-    <row r="152" spans="1:3">
+      <c r="D151" s="10"/>
+    </row>
+    <row r="152" spans="1:4">
       <c r="A152" s="1">
         <v>46306</v>
       </c>
@@ -3408,8 +3424,9 @@
       <c r="C152">
         <v>0</v>
       </c>
-    </row>
-    <row r="153" spans="1:3">
+      <c r="D152" s="10"/>
+    </row>
+    <row r="153" spans="1:4">
       <c r="A153" s="1">
         <v>46307</v>
       </c>
@@ -3419,8 +3436,9 @@
       <c r="C153">
         <v>0</v>
       </c>
-    </row>
-    <row r="154" spans="1:3">
+      <c r="D153" s="10"/>
+    </row>
+    <row r="154" spans="1:4">
       <c r="A154" s="1">
         <v>46308</v>
       </c>
@@ -3430,19 +3448,21 @@
       <c r="C154" s="8">
         <v>7233408</v>
       </c>
-    </row>
-    <row r="155" spans="1:3">
+      <c r="D154" s="9"/>
+    </row>
+    <row r="155" spans="1:4">
       <c r="A155" s="1">
         <v>46309</v>
       </c>
       <c r="B155" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C155" s="8">
-        <v>14536472</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3">
+      <c r="C155">
+        <v>0</v>
+      </c>
+      <c r="D155" s="10"/>
+    </row>
+    <row r="156" spans="1:4">
       <c r="A156" s="1">
         <v>46310</v>
       </c>
@@ -3452,19 +3472,21 @@
       <c r="C156" s="8">
         <v>7233408</v>
       </c>
-    </row>
-    <row r="157" spans="1:3">
+      <c r="D156" s="9"/>
+    </row>
+    <row r="157" spans="1:4">
       <c r="A157" s="1">
         <v>46311</v>
       </c>
       <c r="B157" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C157" s="8">
-        <v>6980400</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3">
+      <c r="C157" s="9">
+        <v>21516872</v>
+      </c>
+      <c r="D157" s="9"/>
+    </row>
+    <row r="158" spans="1:4">
       <c r="A158" s="1">
         <v>46312</v>
       </c>
@@ -3474,8 +3496,9 @@
       <c r="C158">
         <v>0</v>
       </c>
-    </row>
-    <row r="159" spans="1:3">
+      <c r="D158" s="10"/>
+    </row>
+    <row r="159" spans="1:4">
       <c r="A159" s="1">
         <v>46313</v>
       </c>
@@ -3485,8 +3508,9 @@
       <c r="C159">
         <v>0</v>
       </c>
-    </row>
-    <row r="160" spans="1:3">
+      <c r="D159" s="10"/>
+    </row>
+    <row r="160" spans="1:4">
       <c r="A160" s="1">
         <v>46314</v>
       </c>
@@ -3496,8 +3520,9 @@
       <c r="C160" s="8">
         <v>7233408</v>
       </c>
-    </row>
-    <row r="161" spans="1:3">
+      <c r="D160" s="9"/>
+    </row>
+    <row r="161" spans="1:4">
       <c r="A161" s="1">
         <v>46315</v>
       </c>
@@ -3507,8 +3532,9 @@
       <c r="C161">
         <v>0</v>
       </c>
-    </row>
-    <row r="162" spans="1:3">
+      <c r="D161" s="10"/>
+    </row>
+    <row r="162" spans="1:4">
       <c r="A162" s="1">
         <v>46316</v>
       </c>
@@ -3518,8 +3544,9 @@
       <c r="C162">
         <v>0</v>
       </c>
-    </row>
-    <row r="163" spans="1:3">
+      <c r="D162" s="10"/>
+    </row>
+    <row r="163" spans="1:4">
       <c r="A163" s="1">
         <v>46317</v>
       </c>
@@ -3529,8 +3556,9 @@
       <c r="C163" s="8">
         <v>7233408</v>
       </c>
-    </row>
-    <row r="164" spans="1:3">
+      <c r="D163" s="9"/>
+    </row>
+    <row r="164" spans="1:4">
       <c r="A164" s="1">
         <v>46318</v>
       </c>
@@ -3540,8 +3568,9 @@
       <c r="C164">
         <v>6614640</v>
       </c>
-    </row>
-    <row r="165" spans="1:3">
+      <c r="D164" s="9"/>
+    </row>
+    <row r="165" spans="1:4">
       <c r="A165" s="1">
         <v>46319</v>
       </c>
@@ -3551,8 +3580,9 @@
       <c r="C165">
         <v>0</v>
       </c>
-    </row>
-    <row r="166" spans="1:3">
+      <c r="D165" s="10"/>
+    </row>
+    <row r="166" spans="1:4">
       <c r="A166" s="1">
         <v>46320</v>
       </c>
@@ -3562,19 +3592,21 @@
       <c r="C166">
         <v>0</v>
       </c>
-    </row>
-    <row r="167" spans="1:3">
+      <c r="D166" s="10"/>
+    </row>
+    <row r="167" spans="1:4">
       <c r="A167" s="1">
         <v>46321</v>
       </c>
       <c r="B167" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C167">
-        <v>7233408</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3">
+      <c r="C167" s="9">
+        <v>11946744</v>
+      </c>
+      <c r="D167" s="9"/>
+    </row>
+    <row r="168" spans="1:4">
       <c r="A168" s="1">
         <v>46322</v>
       </c>
@@ -3584,8 +3616,9 @@
       <c r="C168">
         <v>11285986</v>
       </c>
-    </row>
-    <row r="169" spans="1:3">
+      <c r="D168" s="9"/>
+    </row>
+    <row r="169" spans="1:4">
       <c r="A169" s="1">
         <v>46323</v>
       </c>
@@ -3595,8 +3628,9 @@
       <c r="C169">
         <v>0</v>
       </c>
-    </row>
-    <row r="170" spans="1:3">
+      <c r="D169" s="10"/>
+    </row>
+    <row r="170" spans="1:4">
       <c r="A170" s="1">
         <v>46324</v>
       </c>
@@ -3606,13 +3640,26 @@
       <c r="C170">
         <v>7233408</v>
       </c>
+      <c r="D170" s="9"/>
+    </row>
+    <row r="171" spans="1:4">
+      <c r="A171" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C171" s="9">
+        <v>6993000</v>
+      </c>
+      <c r="D171" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E169">
+  <autoFilter ref="A1:E170">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="店舗名エラー" error="店舗マスタの一覧にある店舗名を選択してください。" sqref="B2:B101 B102:B111 B112:B138 B139:B155 B156:B162 B163:B170">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="店舗名エラー" error="店舗マスタの一覧にある店舗名を選択してください。" sqref="B171 B2:B101 B102:B111 B112:B138 B139:B155 B156:B162 B163:B170">
       <formula1>店舗マスタ!$A$2:$A$31</formula1>
     </dataValidation>
   </dataValidations>

--- a/dashboard/data/incoming/外販.xlsx
+++ b/dashboard/data/incoming/外販.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12420" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$170</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$171</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -211,15 +211,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -227,15 +219,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -250,21 +250,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -284,6 +286,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -294,38 +303,37 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -339,16 +347,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -369,6 +369,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -381,25 +387,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -411,31 +405,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -453,7 +429,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -465,7 +477,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -477,49 +501,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -531,19 +519,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,17 +578,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -608,17 +602,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -640,9 +634,26 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -659,19 +670,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -681,142 +681,142 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -828,14 +828,14 @@
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1508,7 +1508,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E171"/>
+  <dimension ref="A1:E202"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -3602,7 +3602,7 @@
         <v>41</v>
       </c>
       <c r="C167" s="9">
-        <v>11946744</v>
+        <v>7233408</v>
       </c>
       <c r="D167" s="9"/>
     </row>
@@ -3650,16 +3650,357 @@
         <v>41</v>
       </c>
       <c r="C171" s="9">
-        <v>6993000</v>
+        <v>6657936</v>
       </c>
       <c r="D171" s="9"/>
     </row>
+    <row r="172" spans="1:3">
+      <c r="A172" s="1">
+        <v>46326</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3">
+      <c r="A173" s="1">
+        <v>46327</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3">
+      <c r="A174" s="1">
+        <v>46328</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3">
+      <c r="A175" s="1">
+        <v>46329</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3">
+      <c r="A176" s="1">
+        <v>46330</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3">
+      <c r="A177" s="1">
+        <v>46331</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3">
+      <c r="A178" s="1">
+        <v>46332</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3">
+      <c r="A179" s="1">
+        <v>46333</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3">
+      <c r="A180" s="1">
+        <v>46334</v>
+      </c>
+      <c r="B180" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3">
+      <c r="A181" s="1">
+        <v>46335</v>
+      </c>
+      <c r="B181" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3">
+      <c r="A182" s="1">
+        <v>46336</v>
+      </c>
+      <c r="B182" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3">
+      <c r="A183" s="1">
+        <v>46337</v>
+      </c>
+      <c r="B183" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3">
+      <c r="A184" s="1">
+        <v>46338</v>
+      </c>
+      <c r="B184" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3">
+      <c r="A185" s="1">
+        <v>46339</v>
+      </c>
+      <c r="B185" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3">
+      <c r="A186" s="1">
+        <v>46340</v>
+      </c>
+      <c r="B186" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3">
+      <c r="A187" s="1">
+        <v>46341</v>
+      </c>
+      <c r="B187" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3">
+      <c r="A188" s="1">
+        <v>46342</v>
+      </c>
+      <c r="B188" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3">
+      <c r="A189" s="1">
+        <v>46343</v>
+      </c>
+      <c r="B189" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3">
+      <c r="A190" s="1">
+        <v>46344</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3">
+      <c r="A191" s="1">
+        <v>46345</v>
+      </c>
+      <c r="B191" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3">
+      <c r="A192" s="1">
+        <v>46346</v>
+      </c>
+      <c r="B192" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3">
+      <c r="A193" s="1">
+        <v>46347</v>
+      </c>
+      <c r="B193" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C193">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3">
+      <c r="A194" s="1">
+        <v>46348</v>
+      </c>
+      <c r="B194" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C194">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3">
+      <c r="A195" s="1">
+        <v>46349</v>
+      </c>
+      <c r="B195" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C195">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3">
+      <c r="A196" s="1">
+        <v>46350</v>
+      </c>
+      <c r="B196" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3">
+      <c r="A197" s="1">
+        <v>46351</v>
+      </c>
+      <c r="B197" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3">
+      <c r="A198" s="1">
+        <v>46352</v>
+      </c>
+      <c r="B198" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3">
+      <c r="A199" s="1">
+        <v>46353</v>
+      </c>
+      <c r="B199" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3">
+      <c r="A200" s="1">
+        <v>46354</v>
+      </c>
+      <c r="B200" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C200">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3">
+      <c r="A201" s="1">
+        <v>46355</v>
+      </c>
+      <c r="B201" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C201">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3">
+      <c r="A202" s="1">
+        <v>46356</v>
+      </c>
+      <c r="B202" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C202">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E170">
+  <autoFilter ref="A1:E171">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="店舗名エラー" error="店舗マスタの一覧にある店舗名を選択してください。" sqref="B171 B2:B101 B102:B111 B112:B138 B139:B155 B156:B162 B163:B170">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="店舗名エラー" error="店舗マスタの一覧にある店舗名を選択してください。" sqref="B171 B2:B101 B102:B111 B112:B138 B139:B155 B156:B162 B163:B170 B172:B202">
       <formula1>店舗マスタ!$A$2:$A$31</formula1>
     </dataValidation>
   </dataValidations>
